--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="1126">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3418,7 +3418,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3436,6 +3436,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3522,7 +3528,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4921,7 +4927,7 @@
         <v>147</v>
       </c>
       <c r="G2" s="5">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H2" s="5">
         <f>MROUND(G2*1.03, 0.5)</f>
@@ -5958,7 +5964,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="5">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H2" s="6">
         <f>MROUND(G2*1.03, 0.5)</f>
@@ -6276,7 +6282,7 @@
         <f>MROUND(G14*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>529</v>
       </c>
@@ -6374,7 +6380,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="5">
-        <v>850</v>
+        <v>337.5</v>
       </c>
       <c r="H18" s="6">
         <f>MROUND(G17*1.03, 0.5)</f>
@@ -6400,7 +6406,7 @@
         <v>11</v>
       </c>
       <c r="G19" s="6">
-        <v>425</v>
+        <v>675.5</v>
       </c>
       <c r="H19" s="5">
         <f>MROUND(G18*1.03, 0.5)</f>
@@ -6813,7 +6819,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="6">
-        <v>108.5</v>
+        <v>103.5</v>
       </c>
       <c r="H9" s="5">
         <f>MROUND(G9*1.03, 0.5)</f>
@@ -6839,7 +6845,7 @@
         <v>147</v>
       </c>
       <c r="G10" s="5">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="H10" s="5">
         <f>MROUND(G10*1.03, 0.5)</f>
@@ -7073,7 +7079,7 @@
         <v>11</v>
       </c>
       <c r="G19" s="6">
-        <v>202.5</v>
+        <v>162.5</v>
       </c>
       <c r="H19" s="6">
         <f>MROUND(G19*1.03, 0.5)</f>
@@ -7099,7 +7105,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="5">
-        <v>405</v>
+        <v>325</v>
       </c>
       <c r="H20" s="5">
         <f>MROUND(G20*1.03, 0.5)</f>
@@ -7385,7 +7391,7 @@
         <v>147</v>
       </c>
       <c r="G31" s="5">
-        <v>1850</v>
+        <v>1725</v>
       </c>
       <c r="H31" s="5">
         <f>MROUND(G31*1.03, 0.5)</f>
@@ -7411,7 +7417,7 @@
         <v>147</v>
       </c>
       <c r="G32" s="6">
-        <v>373.5</v>
+        <v>348.5</v>
       </c>
       <c r="H32" s="6">
         <f>MROUND(G32*1.03, 0.5)</f>
@@ -7505,7 +7511,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -8006,7 +8012,7 @@
         <v>147</v>
       </c>
       <c r="G19" s="5">
-        <v>575</v>
+        <v>450</v>
       </c>
       <c r="H19" s="6">
         <f>MROUND(G19*1.03, 0.5)</f>
@@ -8032,7 +8038,7 @@
         <v>11</v>
       </c>
       <c r="G20" s="5">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H20" s="5">
         <f>MROUND(G20*1.03, 0.5)</f>
@@ -8110,7 +8116,7 @@
         <v>147</v>
       </c>
       <c r="G23" s="5">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H23" s="6">
         <f>MROUND(G23*1.03, 0.5)</f>
@@ -8136,7 +8142,7 @@
         <v>11</v>
       </c>
       <c r="G24" s="5">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="H24" s="5">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -8266,7 +8272,7 @@
         <v>147</v>
       </c>
       <c r="G29" s="5">
-        <v>595</v>
+        <v>627.5</v>
       </c>
       <c r="H29" s="5">
         <f>MROUND(G29*1.03, 0.5)</f>
@@ -9722,7 +9728,7 @@
         <v>11</v>
       </c>
       <c r="G85" s="6">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H85" s="5">
         <f>MROUND(G85*1.03, 0.5)</f>
@@ -9748,7 +9754,7 @@
         <v>147</v>
       </c>
       <c r="G86" s="5">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="H86" s="6">
         <f>MROUND(G86*1.03, 0.5)</f>
@@ -9756,28 +9762,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C87" s="5">
-        <v>4225</v>
+        <v>4378</v>
       </c>
       <c r="D87" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G87" s="5">
-        <v>775</v>
-      </c>
-      <c r="H87" s="6">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <v>430</v>
+      </c>
+      <c r="H87" s="5">
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -9788,10 +9794,10 @@
         <v>434</v>
       </c>
       <c r="C88" s="5">
-        <v>4378</v>
+        <v>4379</v>
       </c>
       <c r="D88" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
@@ -9800,36 +9806,36 @@
         <v>147</v>
       </c>
       <c r="G88" s="5">
-        <v>430</v>
-      </c>
-      <c r="H88" s="5">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <v>43</v>
+      </c>
+      <c r="H88" s="6">
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C89" s="5">
-        <v>4379</v>
+        <v>3524</v>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="G89" s="5">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="H89" s="6">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -9840,10 +9846,10 @@
         <v>436</v>
       </c>
       <c r="C90" s="5">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D90" s="5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -9852,36 +9858,36 @@
         <v>10</v>
       </c>
       <c r="G90" s="5">
-        <v>350</v>
-      </c>
-      <c r="H90" s="6">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <v>72</v>
+      </c>
+      <c r="H90" s="5">
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C91" s="5">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="D91" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>30</v>
+        <v>439</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G91" s="5">
-        <v>72</v>
-      </c>
-      <c r="H91" s="5">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <v>158</v>
+      </c>
+      <c r="H91" s="6">
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -9892,59 +9898,59 @@
         <v>438</v>
       </c>
       <c r="C92" s="5">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="D92" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>439</v>
+        <v>115</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G92" s="5">
-        <v>158</v>
-      </c>
-      <c r="H92" s="6">
-        <f>MROUND(G92*1.03, 0.5)</f>
+      <c r="G92" s="6">
+        <v>216.5</v>
+      </c>
+      <c r="H92" s="5">
+        <f>MROUND(G93*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C93" s="5">
-        <v>3522</v>
+        <v>64</v>
       </c>
       <c r="D93" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G93" s="6">
-        <v>216.5</v>
+      <c r="G93" s="5">
+        <v>132</v>
       </c>
       <c r="H93" s="5">
-        <f>MROUND(G93*1.03, 0.5)</f>
+        <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C94" s="5">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D94" s="5">
         <v>8</v>
@@ -9959,33 +9965,33 @@
         <v>132</v>
       </c>
       <c r="H94" s="5">
-        <f>MROUND(G94*1.03, 0.5)</f>
+        <f>MROUND(G95*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C95" s="5">
-        <v>90</v>
+        <v>3637</v>
       </c>
       <c r="D95" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G95" s="5">
-        <v>132</v>
-      </c>
-      <c r="H95" s="5">
-        <f>MROUND(G95*1.03, 0.5)</f>
+        <v>375</v>
+      </c>
+      <c r="H95" s="6">
+        <f>MROUND(G96*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
@@ -9996,10 +10002,10 @@
         <v>445</v>
       </c>
       <c r="C96" s="5">
-        <v>3637</v>
+        <v>2805</v>
       </c>
       <c r="D96" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>30</v>
@@ -10008,10 +10014,10 @@
         <v>147</v>
       </c>
       <c r="G96" s="5">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="H96" s="6">
-        <f>MROUND(G96*1.03, 0.5)</f>
+        <f>MROUND(G97*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
@@ -10022,48 +10028,48 @@
         <v>445</v>
       </c>
       <c r="C97" s="5">
-        <v>2805</v>
+        <v>2427</v>
       </c>
       <c r="D97" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G97" s="5">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="H97" s="6">
-        <f>MROUND(G97*1.03, 0.5)</f>
+        <f>MROUND(G98*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C98" s="5">
-        <v>2427</v>
+        <v>3437</v>
       </c>
       <c r="D98" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G98" s="5">
-        <v>46</v>
+        <v>350</v>
       </c>
       <c r="H98" s="6">
-        <f>MROUND(G98*1.03, 0.5)</f>
+        <f>MROUND(G99*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
@@ -10074,59 +10080,59 @@
         <v>447</v>
       </c>
       <c r="C99" s="5">
-        <v>3437</v>
+        <v>3396</v>
       </c>
       <c r="D99" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G99" s="5">
-        <v>350</v>
-      </c>
-      <c r="H99" s="6">
-        <f>MROUND(G99*1.03, 0.5)</f>
+        <v>178.5</v>
+      </c>
+      <c r="H99" s="5">
+        <f>MROUND(G100*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C100" s="5">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="D100" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>30</v>
+        <v>450</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G100" s="5">
-        <v>178.5</v>
-      </c>
-      <c r="H100" s="5">
-        <f>MROUND(G100*1.03, 0.5)</f>
+        <v>54</v>
+      </c>
+      <c r="H100" s="6">
+        <f>MROUND(G101*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="4" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C101" s="5">
-        <v>3395</v>
+        <v>3490</v>
       </c>
       <c r="D101" s="5">
         <v>12</v>
@@ -10138,47 +10144,47 @@
         <v>16</v>
       </c>
       <c r="G101" s="5">
-        <v>54</v>
-      </c>
-      <c r="H101" s="6">
-        <f>MROUND(G101*1.03, 0.5)</f>
+        <v>169</v>
+      </c>
+      <c r="H101" s="5">
+        <f>MROUND(G102*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C102" s="5">
-        <v>3490</v>
+        <v>458</v>
       </c>
       <c r="D102" s="5">
         <v>12</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>450</v>
+        <v>302</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G102" s="5">
-        <v>169</v>
-      </c>
-      <c r="H102" s="5">
-        <f>MROUND(G102*1.03, 0.5)</f>
+      <c r="G102" s="6">
+        <v>269.5</v>
+      </c>
+      <c r="H102" s="6">
+        <f>MROUND(G103*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C103" s="5">
-        <v>458</v>
+        <v>2641</v>
       </c>
       <c r="D103" s="5">
         <v>12</v>
@@ -10189,22 +10195,22 @@
       <c r="F103" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G103" s="6">
-        <v>269.5</v>
+      <c r="G103" s="5">
+        <v>222</v>
       </c>
       <c r="H103" s="6">
-        <f>MROUND(G103*1.03, 0.5)</f>
+        <f>MROUND(G104*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C104" s="5">
-        <v>2641</v>
+        <v>4293</v>
       </c>
       <c r="D104" s="5">
         <v>12</v>
@@ -10216,36 +10222,36 @@
         <v>16</v>
       </c>
       <c r="G104" s="5">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="H104" s="6">
-        <f>MROUND(G104*1.03, 0.5)</f>
+        <f>MROUND(G105*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C105" s="5">
-        <v>4293</v>
+        <v>2396</v>
       </c>
       <c r="D105" s="5">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G105" s="5">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="H105" s="6">
-        <f>MROUND(G105*1.03, 0.5)</f>
+        <f>MROUND(G106*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -10256,36 +10262,36 @@
         <v>460</v>
       </c>
       <c r="C106" s="5">
-        <v>2396</v>
+        <v>2426</v>
       </c>
       <c r="D106" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G106" s="5">
-        <v>675</v>
-      </c>
-      <c r="H106" s="6">
-        <f>MROUND(G106*1.03, 0.5)</f>
+        <v>118.5</v>
+      </c>
+      <c r="H106" s="5">
+        <f>MROUND(G107*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C107" s="5">
-        <v>2426</v>
+        <v>4335</v>
       </c>
       <c r="D107" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>30</v>
@@ -10294,21 +10300,21 @@
         <v>11</v>
       </c>
       <c r="G107" s="5">
-        <v>137</v>
-      </c>
-      <c r="H107" s="5">
-        <f>MROUND(G107*1.03, 0.5)</f>
+        <v>510</v>
+      </c>
+      <c r="H107" s="6">
+        <f>MROUND(G108*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C108" s="5">
-        <v>4335</v>
+        <v>4477</v>
       </c>
       <c r="D108" s="5">
         <v>3</v>
@@ -10320,21 +10326,21 @@
         <v>11</v>
       </c>
       <c r="G108" s="5">
-        <v>510</v>
+        <v>252</v>
       </c>
       <c r="H108" s="6">
-        <f>MROUND(G108*1.03, 0.5)</f>
+        <f>MROUND(G109*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C109" s="5">
-        <v>4477</v>
+        <v>4479</v>
       </c>
       <c r="D109" s="5">
         <v>3</v>
@@ -10349,18 +10355,18 @@
         <v>252</v>
       </c>
       <c r="H109" s="6">
-        <f>MROUND(G109*1.03, 0.5)</f>
+        <f>MROUND(G110*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C110" s="5">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="D110" s="5">
         <v>3</v>
@@ -10375,33 +10381,33 @@
         <v>252</v>
       </c>
       <c r="H110" s="6">
-        <f>MROUND(G110*1.03, 0.5)</f>
+        <f>MROUND(G111*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C111" s="5">
-        <v>4478</v>
+        <v>2646</v>
       </c>
       <c r="D111" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>30</v>
+        <v>471</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="G111" s="5">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="H111" s="6">
-        <f>MROUND(G111*1.03, 0.5)</f>
+        <f>MROUND(G112*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -10412,22 +10418,22 @@
         <v>470</v>
       </c>
       <c r="C112" s="5">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="D112" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G112" s="5">
-        <v>53</v>
-      </c>
-      <c r="H112" s="6">
-        <f>MROUND(G112*1.03, 0.5)</f>
+      <c r="G112" s="6">
+        <v>81.5</v>
+      </c>
+      <c r="H112" s="5">
+        <f>MROUND(G113*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
@@ -10438,125 +10444,99 @@
         <v>470</v>
       </c>
       <c r="C113" s="5">
-        <v>2645</v>
+        <v>2638</v>
       </c>
       <c r="D113" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G113" s="6">
-        <v>81.5</v>
+      <c r="G113" s="5">
+        <v>70</v>
       </c>
       <c r="H113" s="5">
-        <f>MROUND(G113*1.03, 0.5)</f>
+        <f>MROUND(G114*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C114" s="5">
-        <v>2638</v>
+        <v>4294</v>
       </c>
       <c r="D114" s="5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>90</v>
       </c>
       <c r="G114" s="5">
-        <v>70</v>
-      </c>
-      <c r="H114" s="5">
-        <f>MROUND(G114*1.03, 0.5)</f>
+        <v>150</v>
+      </c>
+      <c r="H114" s="6">
+        <f>MROUND(G115*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="4" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C115" s="5">
-        <v>4294</v>
+        <v>4314</v>
       </c>
       <c r="D115" s="5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>476</v>
+        <v>115</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="G115" s="5">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="H115" s="6">
-        <f>MROUND(G115*1.03, 0.5)</f>
+        <f>MROUND(G116*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C116" s="5">
-        <v>4314</v>
+        <v>4315</v>
       </c>
       <c r="D116" s="5">
         <v>15</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>115</v>
+        <v>481</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G116" s="5">
-        <v>252</v>
+        <v>450</v>
       </c>
       <c r="H116" s="6">
-        <f>MROUND(G116*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
-      <c r="A117" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C117" s="5">
-        <v>4315</v>
-      </c>
-      <c r="D117" s="5">
-        <v>15</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G117" s="5">
-        <v>450</v>
-      </c>
-      <c r="H117" s="6">
         <f>MROUND(G117*1.03, 0.5)</f>
       </c>
     </row>
@@ -16704,7 +16684,7 @@
         <v>147</v>
       </c>
       <c r="G37" s="5">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="H37" s="6">
         <f>MROUND(G37*1.03, 0.5)</f>
@@ -16730,7 +16710,7 @@
         <v>11</v>
       </c>
       <c r="G38" s="5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H38" s="6">
         <f>MROUND(G38*1.03, 0.5)</f>
@@ -16756,7 +16736,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="5">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H39" s="6">
         <f>MROUND(G39*1.03, 0.5)</f>
@@ -16782,7 +16762,7 @@
         <v>147</v>
       </c>
       <c r="G40" s="5">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H40" s="6">
         <f>MROUND(G40*1.03, 0.5)</f>
@@ -16808,7 +16788,7 @@
         <v>11</v>
       </c>
       <c r="G41" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H41" s="5">
         <f>MROUND(G41*1.03, 0.5)</f>
@@ -16834,7 +16814,7 @@
         <v>11</v>
       </c>
       <c r="G42" s="5">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H42" s="6">
         <f>MROUND(G42*1.03, 0.5)</f>
@@ -16860,7 +16840,7 @@
         <v>147</v>
       </c>
       <c r="G43" s="5">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H43" s="6">
         <f>MROUND(G43*1.03, 0.5)</f>
@@ -16886,7 +16866,7 @@
         <v>11</v>
       </c>
       <c r="G44" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H44" s="5">
         <f>MROUND(G44*1.03, 0.5)</f>
@@ -17146,7 +17126,7 @@
         <v>16</v>
       </c>
       <c r="G54" s="6">
-        <v>850.5</v>
+        <v>833.5</v>
       </c>
       <c r="H54" s="5">
         <f>MROUND(G52*1.03, 0.5)</f>
@@ -17172,7 +17152,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="5">
-        <v>1701</v>
+        <v>1667</v>
       </c>
       <c r="H55" s="5">
         <f>MROUND(G53*1.03, 0.5)</f>
@@ -17198,7 +17178,7 @@
         <v>11</v>
       </c>
       <c r="G56" s="5">
-        <v>378.5</v>
+        <v>371</v>
       </c>
       <c r="H56" s="5">
         <f>MROUND(G54*1.03, 0.5)</f>
@@ -17224,7 +17204,7 @@
         <v>16</v>
       </c>
       <c r="G57" s="6">
-        <v>850.5</v>
+        <v>833.5</v>
       </c>
       <c r="H57" s="5">
         <f>MROUND(G55*1.03, 0.5)</f>
@@ -17250,7 +17230,7 @@
         <v>16</v>
       </c>
       <c r="G58" s="5">
-        <v>1701</v>
+        <v>1667</v>
       </c>
       <c r="H58" s="5">
         <f>MROUND(G56*1.03, 0.5)</f>
@@ -17276,7 +17256,7 @@
         <v>11</v>
       </c>
       <c r="G59" s="5">
-        <v>378.5</v>
+        <v>371</v>
       </c>
       <c r="H59" s="5">
         <f>MROUND(G57*1.03, 0.5)</f>
@@ -20871,7 +20851,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -21528,7 +21508,7 @@
         <v>11</v>
       </c>
       <c r="G25" s="5">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="H25" s="5">
         <f>MROUND(G25*1.03, 0.5)</f>
@@ -21554,7 +21534,7 @@
         <v>11</v>
       </c>
       <c r="G26" s="5">
-        <v>165</v>
+        <v>138.5</v>
       </c>
       <c r="H26" s="5">
         <f>MROUND(G26*1.03, 0.5)</f>
@@ -21632,7 +21612,7 @@
         <v>147</v>
       </c>
       <c r="G29" s="5">
-        <v>925</v>
+        <v>675</v>
       </c>
       <c r="H29" s="5">
         <f>MROUND(G29*1.03, 0.5)</f>
@@ -21646,10 +21626,10 @@
         <v>878</v>
       </c>
       <c r="C30" s="5">
-        <v>4163</v>
+        <v>4676</v>
       </c>
       <c r="D30" s="5">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>30</v>
@@ -21658,7 +21638,7 @@
         <v>147</v>
       </c>
       <c r="G30" s="5">
-        <v>370</v>
+        <v>337.5</v>
       </c>
       <c r="H30" s="5">
         <f>MROUND(G30*1.03, 0.5)</f>
@@ -21672,36 +21652,36 @@
         <v>878</v>
       </c>
       <c r="C31" s="5">
-        <v>4117</v>
+        <v>4163</v>
       </c>
       <c r="D31" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G31" s="5">
-        <v>187</v>
-      </c>
-      <c r="H31" s="6">
-        <f>MROUND(G31*1.03, 0.5)</f>
+        <v>270</v>
+      </c>
+      <c r="H31" s="5">
+        <f>MROUND(G30*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C32" s="5">
-        <v>3738</v>
+        <v>4117</v>
       </c>
       <c r="D32" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>30</v>
@@ -21710,10 +21690,10 @@
         <v>11</v>
       </c>
       <c r="G32" s="5">
-        <v>100</v>
-      </c>
-      <c r="H32" s="5">
-        <f>MROUND(G32*1.03, 0.5)</f>
+        <v>138.5</v>
+      </c>
+      <c r="H32" s="6">
+        <f>MROUND(G31*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -21724,10 +21704,10 @@
         <v>880</v>
       </c>
       <c r="C33" s="5">
-        <v>4317</v>
+        <v>3738</v>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>30</v>
@@ -21736,24 +21716,24 @@
         <v>11</v>
       </c>
       <c r="G33" s="5">
-        <v>52</v>
-      </c>
-      <c r="H33" s="6">
-        <f>MROUND(G33*1.03, 0.5)</f>
+        <v>100</v>
+      </c>
+      <c r="H33" s="5">
+        <f>MROUND(G32*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C34" s="5">
-        <v>2924</v>
+        <v>4317</v>
       </c>
       <c r="D34" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>30</v>
@@ -21762,10 +21742,10 @@
         <v>11</v>
       </c>
       <c r="G34" s="5">
-        <v>168</v>
-      </c>
-      <c r="H34" s="5">
-        <f>MROUND(G34*1.03, 0.5)</f>
+        <v>52</v>
+      </c>
+      <c r="H34" s="6">
+        <f>MROUND(G33*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -21776,10 +21756,10 @@
         <v>882</v>
       </c>
       <c r="C35" s="5">
-        <v>3078</v>
+        <v>2924</v>
       </c>
       <c r="D35" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>30</v>
@@ -21788,36 +21768,36 @@
         <v>11</v>
       </c>
       <c r="G35" s="5">
-        <v>86</v>
-      </c>
-      <c r="H35" s="6">
-        <f>MROUND(G35*1.03, 0.5)</f>
+        <v>168</v>
+      </c>
+      <c r="H35" s="5">
+        <f>MROUND(G34*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C36" s="5">
-        <v>2348</v>
+        <v>3078</v>
       </c>
       <c r="D36" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G36" s="5">
-        <v>140</v>
-      </c>
-      <c r="H36" s="5">
-        <f>MROUND(G36*1.03, 0.5)</f>
+        <v>86</v>
+      </c>
+      <c r="H36" s="6">
+        <f>MROUND(G35*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
@@ -21828,10 +21808,10 @@
         <v>884</v>
       </c>
       <c r="C37" s="5">
-        <v>2538</v>
+        <v>2348</v>
       </c>
       <c r="D37" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>30</v>
@@ -21840,21 +21820,21 @@
         <v>147</v>
       </c>
       <c r="G37" s="5">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="H37" s="5">
-        <f>MROUND(G37*1.03, 0.5)</f>
+        <f>MROUND(G36*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C38" s="5">
-        <v>2811</v>
+        <v>2538</v>
       </c>
       <c r="D38" s="5">
         <v>5</v>
@@ -21863,13 +21843,13 @@
         <v>30</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="6">
-        <v>104.5</v>
-      </c>
-      <c r="H38" s="6">
-        <f>MROUND(G38*1.03, 0.5)</f>
+        <v>147</v>
+      </c>
+      <c r="G38" s="5">
+        <v>35</v>
+      </c>
+      <c r="H38" s="5">
+        <f>MROUND(G37*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
@@ -21880,10 +21860,10 @@
         <v>886</v>
       </c>
       <c r="C39" s="5">
-        <v>2820</v>
+        <v>2811</v>
       </c>
       <c r="D39" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>30</v>
@@ -21891,25 +21871,25 @@
       <c r="F39" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G39" s="5">
-        <v>205</v>
-      </c>
-      <c r="H39" s="5">
-        <f>MROUND(G39*1.03, 0.5)</f>
+      <c r="G39" s="6">
+        <v>104.5</v>
+      </c>
+      <c r="H39" s="6">
+        <f>MROUND(G38*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C40" s="5">
-        <v>3722</v>
+        <v>2820</v>
       </c>
       <c r="D40" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>30</v>
@@ -21918,10 +21898,10 @@
         <v>11</v>
       </c>
       <c r="G40" s="5">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="H40" s="5">
-        <f>MROUND(G40*1.03, 0.5)</f>
+        <f>MROUND(G39*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -21932,33 +21912,33 @@
         <v>888</v>
       </c>
       <c r="C41" s="5">
-        <v>4050</v>
+        <v>3722</v>
       </c>
       <c r="D41" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G41" s="5">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="H41" s="5">
-        <f>MROUND(G41*1.03, 0.5)</f>
+        <f>MROUND(G40*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C42" s="5">
-        <v>415</v>
+        <v>4050</v>
       </c>
       <c r="D42" s="5">
         <v>10</v>
@@ -21967,24 +21947,24 @@
         <v>30</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G42" s="5">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H42" s="5">
-        <f>MROUND(G42*1.03, 0.5)</f>
+        <f>MROUND(G41*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C43" s="5">
-        <v>93</v>
+        <v>415</v>
       </c>
       <c r="D43" s="5">
         <v>10</v>
@@ -21996,36 +21976,36 @@
         <v>11</v>
       </c>
       <c r="G43" s="5">
-        <v>90</v>
-      </c>
-      <c r="H43" s="6">
-        <f>MROUND(G43*1.03, 0.5)</f>
+        <v>105</v>
+      </c>
+      <c r="H43" s="5">
+        <f>MROUND(G42*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C44" s="5">
-        <v>261</v>
+        <v>93</v>
       </c>
       <c r="D44" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G44" s="5">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H44" s="6">
-        <f>MROUND(G44*1.03, 0.5)</f>
+        <f>MROUND(G43*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -22036,48 +22016,48 @@
         <v>894</v>
       </c>
       <c r="C45" s="5">
-        <v>2475</v>
+        <v>261</v>
       </c>
       <c r="D45" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" s="6">
-        <v>18.5</v>
-      </c>
-      <c r="H45" s="5">
-        <f>MROUND(G45*1.03, 0.5)</f>
+        <v>147</v>
+      </c>
+      <c r="G45" s="5">
+        <v>83</v>
+      </c>
+      <c r="H45" s="6">
+        <f>MROUND(G44*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C46" s="5">
-        <v>92</v>
+        <v>2475</v>
       </c>
       <c r="D46" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G46" s="5">
-        <v>67</v>
+        <v>11</v>
+      </c>
+      <c r="G46" s="6">
+        <v>18.5</v>
       </c>
       <c r="H46" s="5">
-        <f>MROUND(G46*1.03, 0.5)</f>
+        <f>MROUND(G45*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -22088,48 +22068,48 @@
         <v>896</v>
       </c>
       <c r="C47" s="5">
-        <v>2476</v>
+        <v>92</v>
       </c>
       <c r="D47" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" s="6">
-        <v>11.5</v>
+        <v>147</v>
+      </c>
+      <c r="G47" s="5">
+        <v>67</v>
       </c>
       <c r="H47" s="5">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G46*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C48" s="5">
-        <v>18</v>
+        <v>2476</v>
       </c>
       <c r="D48" s="5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G48" s="5">
-        <v>96</v>
-      </c>
-      <c r="H48" s="6">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G48" s="6">
+        <v>11.5</v>
+      </c>
+      <c r="H48" s="5">
+        <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -22140,48 +22120,48 @@
         <v>898</v>
       </c>
       <c r="C49" s="5">
-        <v>2477</v>
+        <v>18</v>
       </c>
       <c r="D49" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G49" s="5">
-        <v>22.5</v>
+        <v>96</v>
       </c>
       <c r="H49" s="6">
-        <f>MROUND(G49*1.03, 0.5)</f>
+        <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C50" s="5">
-        <v>4164</v>
+        <v>2477</v>
       </c>
       <c r="D50" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G50" s="5">
-        <v>180</v>
+        <v>22.5</v>
       </c>
       <c r="H50" s="6">
-        <f>MROUND(G50*1.03, 0.5)</f>
+        <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -22192,48 +22172,48 @@
         <v>900</v>
       </c>
       <c r="C51" s="5">
-        <v>3706</v>
+        <v>4164</v>
       </c>
       <c r="D51" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G51" s="5">
-        <v>92</v>
-      </c>
-      <c r="H51" s="5">
-        <f>MROUND(G51*1.03, 0.5)</f>
+        <v>170</v>
+      </c>
+      <c r="H51" s="6">
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C52" s="5">
-        <v>19</v>
+        <v>3706</v>
       </c>
       <c r="D52" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G52" s="5">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="H52" s="5">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -22244,22 +22224,22 @@
         <v>902</v>
       </c>
       <c r="C53" s="5">
-        <v>2246</v>
+        <v>19</v>
       </c>
       <c r="D53" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>332</v>
+        <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="G53" s="5">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="H53" s="5">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -22270,48 +22250,48 @@
         <v>902</v>
       </c>
       <c r="C54" s="5">
-        <v>575</v>
+        <v>2246</v>
       </c>
       <c r="D54" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>30</v>
+        <v>332</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="G54" s="5">
-        <v>48</v>
-      </c>
-      <c r="H54" s="6">
-        <f>MROUND(G54*1.03, 0.5)</f>
+        <v>192</v>
+      </c>
+      <c r="H54" s="5">
+        <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C55" s="5">
-        <v>221</v>
+        <v>575</v>
       </c>
       <c r="D55" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G55" s="5">
-        <v>300</v>
-      </c>
-      <c r="H55" s="5">
-        <f>MROUND(G55*1.03, 0.5)</f>
+        <v>48</v>
+      </c>
+      <c r="H55" s="6">
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -22322,22 +22302,22 @@
         <v>904</v>
       </c>
       <c r="C56" s="5">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="D56" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>332</v>
+        <v>30</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="G56" s="5">
-        <v>324</v>
-      </c>
-      <c r="H56" s="6">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <v>300</v>
+      </c>
+      <c r="H56" s="5">
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -22348,33 +22328,33 @@
         <v>904</v>
       </c>
       <c r="C57" s="5">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="D57" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>30</v>
+        <v>332</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="G57" s="5">
-        <v>77</v>
+        <v>324</v>
       </c>
       <c r="H57" s="6">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C58" s="5">
-        <v>2520</v>
+        <v>20</v>
       </c>
       <c r="D58" s="5">
         <v>5</v>
@@ -22386,10 +22366,10 @@
         <v>11</v>
       </c>
       <c r="G58" s="5">
-        <v>29</v>
-      </c>
-      <c r="H58" s="5">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <v>77</v>
+      </c>
+      <c r="H58" s="6">
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -22400,33 +22380,33 @@
         <v>906</v>
       </c>
       <c r="C59" s="5">
-        <v>4089</v>
+        <v>2520</v>
       </c>
       <c r="D59" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G59" s="5">
-        <v>130</v>
-      </c>
-      <c r="H59" s="6">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <v>29</v>
+      </c>
+      <c r="H59" s="5">
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C60" s="5">
-        <v>21</v>
+        <v>4089</v>
       </c>
       <c r="D60" s="5">
         <v>25</v>
@@ -22438,21 +22418,21 @@
         <v>147</v>
       </c>
       <c r="G60" s="5">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H60" s="6">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C61" s="5">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="D61" s="5">
         <v>25</v>
@@ -22464,10 +22444,10 @@
         <v>147</v>
       </c>
       <c r="G61" s="5">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H61" s="6">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -22478,48 +22458,48 @@
         <v>910</v>
       </c>
       <c r="C62" s="5">
-        <v>2513</v>
+        <v>262</v>
       </c>
       <c r="D62" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G62" s="5">
-        <v>26</v>
-      </c>
-      <c r="H62" s="5">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <v>119</v>
+      </c>
+      <c r="H62" s="6">
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C63" s="5">
-        <v>16</v>
+        <v>2513</v>
       </c>
       <c r="D63" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G63" s="5">
-        <v>180</v>
-      </c>
-      <c r="H63" s="6">
-        <f>MROUND(G63*1.03, 0.5)</f>
+        <v>26</v>
+      </c>
+      <c r="H63" s="5">
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -22530,74 +22510,74 @@
         <v>912</v>
       </c>
       <c r="C64" s="5">
-        <v>3114</v>
+        <v>16</v>
       </c>
       <c r="D64" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G64" s="5">
-        <v>38</v>
-      </c>
-      <c r="H64" s="5">
-        <f>MROUND(G64*1.03, 0.5)</f>
+        <v>180</v>
+      </c>
+      <c r="H64" s="6">
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C65" s="5">
-        <v>4086</v>
+        <v>3114</v>
       </c>
       <c r="D65" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="G65" s="5">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="H65" s="5">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C66" s="5">
-        <v>15</v>
+        <v>4086</v>
       </c>
       <c r="D66" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="G66" s="5">
-        <v>190</v>
-      </c>
-      <c r="H66" s="6">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <v>170</v>
+      </c>
+      <c r="H66" s="5">
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -22608,48 +22588,48 @@
         <v>916</v>
       </c>
       <c r="C67" s="5">
-        <v>3115</v>
+        <v>15</v>
       </c>
       <c r="D67" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G67" s="5">
-        <v>40</v>
-      </c>
-      <c r="H67" s="5">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <v>190</v>
+      </c>
+      <c r="H67" s="6">
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C68" s="5">
-        <v>4165</v>
+        <v>3115</v>
       </c>
       <c r="D68" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G68" s="5">
-        <v>280</v>
-      </c>
-      <c r="H68" s="6">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <v>40</v>
+      </c>
+      <c r="H68" s="5">
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -22660,48 +22640,48 @@
         <v>918</v>
       </c>
       <c r="C69" s="5">
-        <v>4100</v>
+        <v>4165</v>
       </c>
       <c r="D69" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G69" s="5">
-        <v>143.5</v>
-      </c>
-      <c r="H69" s="5">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <v>240</v>
+      </c>
+      <c r="H69" s="6">
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C70" s="5">
-        <v>4280</v>
+        <v>4100</v>
       </c>
       <c r="D70" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G70" s="5">
-        <v>360</v>
+        <v>123.5</v>
       </c>
       <c r="H70" s="5">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -22712,10 +22692,10 @@
         <v>920</v>
       </c>
       <c r="C71" s="5">
-        <v>4281</v>
+        <v>4280</v>
       </c>
       <c r="D71" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>30</v>
@@ -22724,9 +22704,35 @@
         <v>147</v>
       </c>
       <c r="G71" s="5">
+        <v>360</v>
+      </c>
+      <c r="H71" s="5">
+        <f>MROUND(G70*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C72" s="5">
+        <v>4281</v>
+      </c>
+      <c r="D72" s="5">
+        <v>5</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="5">
         <v>183.5</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H72" s="5">
         <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
@@ -22740,7 +22746,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -22851,7 +22857,7 @@
         <v>147</v>
       </c>
       <c r="G4" s="5">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H4" s="5">
         <f>MROUND(G4*1.03, 0.5)</f>
@@ -22877,7 +22883,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="5">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="H5" s="6">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -23319,7 +23325,7 @@
         <v>147</v>
       </c>
       <c r="G22" s="5">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H22" s="5">
         <f>MROUND(G22*1.03, 0.5)</f>
@@ -23345,7 +23351,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H23" s="5">
         <f>MROUND(G23*1.03, 0.5)</f>
@@ -23371,7 +23377,7 @@
         <v>11</v>
       </c>
       <c r="G24" s="5">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H24" s="5">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -23397,7 +23403,7 @@
         <v>147</v>
       </c>
       <c r="G25" s="5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H25" s="5">
         <f>MROUND(G25*1.03, 0.5)</f>
@@ -23423,7 +23429,7 @@
         <v>147</v>
       </c>
       <c r="G26" s="5">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H26" s="5">
         <f>MROUND(G26*1.03, 0.5)</f>
@@ -23449,7 +23455,7 @@
         <v>11</v>
       </c>
       <c r="G27" s="5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H27" s="5">
         <f>MROUND(G27*1.03, 0.5)</f>
@@ -23475,7 +23481,7 @@
         <v>147</v>
       </c>
       <c r="G28" s="5">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H28" s="5">
         <f>MROUND(G28*1.03, 0.5)</f>
@@ -23501,7 +23507,7 @@
         <v>11</v>
       </c>
       <c r="G29" s="5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H29" s="5">
         <f>MROUND(G29*1.03, 0.5)</f>
@@ -24229,7 +24235,7 @@
         <v>147</v>
       </c>
       <c r="G57" s="5">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="H57" s="6">
         <f>MROUND(G57*1.03, 0.5)</f>
@@ -24255,7 +24261,7 @@
         <v>147</v>
       </c>
       <c r="G58" s="5">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H58" s="6">
         <f>MROUND(G58*1.03, 0.5)</f>
@@ -24281,7 +24287,7 @@
         <v>11</v>
       </c>
       <c r="G59" s="5">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="H59" s="5">
         <f>MROUND(G59*1.03, 0.5)</f>
@@ -24723,7 +24729,7 @@
         <v>147</v>
       </c>
       <c r="G76" s="6">
-        <v>187.5</v>
+        <v>179</v>
       </c>
       <c r="H76" s="5">
         <f>MROUND(G76*1.03, 0.5)</f>
@@ -24749,7 +24755,7 @@
         <v>147</v>
       </c>
       <c r="G77" s="5">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="H77" s="6">
         <f>MROUND(G77*1.03, 0.5)</f>
@@ -24775,7 +24781,7 @@
         <v>11</v>
       </c>
       <c r="G78" s="6">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="H78" s="5">
         <f>MROUND(G78*1.03, 0.5)</f>
@@ -25087,7 +25093,7 @@
         <v>147</v>
       </c>
       <c r="G90" s="5">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H90" s="6">
         <f>MROUND(G90*1.03, 0.5)</f>
@@ -25113,7 +25119,7 @@
         <v>147</v>
       </c>
       <c r="G91" s="5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H91" s="5">
         <f>MROUND(G91*1.03, 0.5)</f>
@@ -25121,16 +25127,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C92" s="5">
-        <v>201</v>
+        <v>4223</v>
       </c>
       <c r="D92" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>30</v>
@@ -25139,10 +25145,10 @@
         <v>147</v>
       </c>
       <c r="G92" s="5">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="H92" s="5">
-        <f>MROUND(G92*1.03, 0.5)</f>
+        <f>MROUND(G93*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -25153,47 +25159,21 @@
         <v>848</v>
       </c>
       <c r="C93" s="5">
-        <v>4223</v>
+        <v>4224</v>
       </c>
       <c r="D93" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G93" s="5">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="H93" s="5">
-        <f>MROUND(G93*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="C94" s="5">
-        <v>4224</v>
-      </c>
-      <c r="D94" s="5">
-        <v>5</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="5">
-        <v>27</v>
-      </c>
-      <c r="H94" s="5">
         <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
@@ -25292,7 +25272,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="5">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H3" s="5">
         <f>MROUND(G3*1.03, 0.5)</f>
@@ -25734,7 +25714,7 @@
         <v>147</v>
       </c>
       <c r="G20" s="5">
-        <v>1875</v>
+        <v>1750</v>
       </c>
       <c r="H20" s="6">
         <f>MROUND(G20*1.03, 0.5)</f>
@@ -25760,7 +25740,7 @@
         <v>11</v>
       </c>
       <c r="G21" s="5">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="H21" s="6">
         <f>MROUND(G21*1.03, 0.5)</f>
@@ -26020,7 +26000,7 @@
         <v>147</v>
       </c>
       <c r="G31" s="6">
-        <v>77.5</v>
+        <v>73</v>
       </c>
       <c r="H31" s="5">
         <f>MROUND(G31*1.03, 0.5)</f>
@@ -26046,7 +26026,7 @@
         <v>147</v>
       </c>
       <c r="G32" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H32" s="5">
         <f>MROUND(G32*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="1126">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3418,7 +3418,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3436,12 +3436,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3493,7 +3487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3526,9 +3520,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -6289,10 +6280,10 @@
       <c r="B15" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="5">
         <v>4700</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -6301,7 +6292,7 @@
       <c r="F15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="5">
         <v>280</v>
       </c>
       <c r="H15" s="6">
@@ -6380,7 +6371,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="5">
-        <v>337.5</v>
+        <v>675.5</v>
       </c>
       <c r="H18" s="6">
         <f>MROUND(G17*1.03, 0.5)</f>
@@ -6406,7 +6397,7 @@
         <v>11</v>
       </c>
       <c r="G19" s="6">
-        <v>675.5</v>
+        <v>337.5</v>
       </c>
       <c r="H19" s="5">
         <f>MROUND(G18*1.03, 0.5)</f>
@@ -11994,7 +11985,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -13704,10 +13695,10 @@
       <c r="B66" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="5">
         <v>4699</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="5">
         <v>50</v>
       </c>
       <c r="E66" s="4" t="s">
@@ -13716,7 +13707,7 @@
       <c r="F66" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G66" s="12">
+      <c r="G66" s="5">
         <v>30</v>
       </c>
       <c r="H66" s="6">
@@ -13731,10 +13722,10 @@
         <v>174</v>
       </c>
       <c r="C67" s="5">
-        <v>4629</v>
+        <v>4643</v>
       </c>
       <c r="D67" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>154</v>
@@ -13742,22 +13733,22 @@
       <c r="F67" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G67" s="5">
-        <v>195</v>
-      </c>
-      <c r="H67" s="5">
-        <f>MROUND(G66*1.03, 0.5)</f>
+      <c r="G67" s="6">
+        <v>97.5</v>
+      </c>
+      <c r="H67" s="6">
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C68" s="5">
-        <v>4643</v>
+        <v>4687</v>
       </c>
       <c r="D68" s="5">
         <v>6</v>
@@ -13769,24 +13760,24 @@
         <v>16</v>
       </c>
       <c r="G68" s="6">
-        <v>97.5</v>
+        <v>64</v>
       </c>
       <c r="H68" s="6">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C69" s="5">
-        <v>4630</v>
+        <v>4644</v>
       </c>
       <c r="D69" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>154</v>
@@ -13794,74 +13785,74 @@
       <c r="F69" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G69" s="6">
-        <v>127.5</v>
+      <c r="G69" s="5">
+        <v>57</v>
       </c>
       <c r="H69" s="6">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C70" s="5">
-        <v>4687</v>
+        <v>4547</v>
       </c>
       <c r="D70" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G70" s="6">
-        <v>64</v>
+        <v>90</v>
+      </c>
+      <c r="G70" s="5">
+        <v>77</v>
       </c>
       <c r="H70" s="6">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C71" s="5">
-        <v>4644</v>
+        <v>4104</v>
       </c>
       <c r="D71" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="G71" s="5">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="H71" s="6">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C72" s="5">
-        <v>4547</v>
+        <v>4101</v>
       </c>
       <c r="D72" s="5">
         <v>10</v>
@@ -13876,122 +13867,122 @@
         <v>77</v>
       </c>
       <c r="H72" s="6">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C73" s="5">
-        <v>4104</v>
+        <v>4641</v>
       </c>
       <c r="D73" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="G73" s="5">
-        <v>77</v>
-      </c>
-      <c r="H73" s="6">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <v>72</v>
+      </c>
+      <c r="H73" s="5">
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C74" s="5">
-        <v>4101</v>
+        <v>4583</v>
       </c>
       <c r="D74" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="G74" s="5">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="H74" s="6">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C75" s="5">
-        <v>4641</v>
+        <v>4105</v>
       </c>
       <c r="D75" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="G75" s="5">
-        <v>72</v>
-      </c>
-      <c r="H75" s="5">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <v>77</v>
+      </c>
+      <c r="H75" s="6">
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C76" s="5">
-        <v>4583</v>
+        <v>3705</v>
       </c>
       <c r="D76" s="5">
         <v>12</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G76" s="5">
-        <v>144</v>
-      </c>
-      <c r="H76" s="6">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <v>90</v>
+      </c>
+      <c r="G76" s="6">
+        <v>123.5</v>
+      </c>
+      <c r="H76" s="5">
+        <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C77" s="5">
-        <v>4105</v>
+        <v>3823</v>
       </c>
       <c r="D77" s="5">
         <v>10</v>
@@ -14000,180 +13991,180 @@
         <v>154</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="G77" s="5">
         <v>77</v>
       </c>
       <c r="H77" s="6">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C78" s="5">
-        <v>3705</v>
+        <v>4308</v>
       </c>
       <c r="D78" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="G78" s="6">
-        <v>123.5</v>
-      </c>
-      <c r="H78" s="5">
-        <f>MROUND(G77*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
+        <v>68.5</v>
+      </c>
+      <c r="H78" s="6">
+        <f>MROUND(G79*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C79" s="5">
-        <v>3823</v>
+        <v>4309</v>
       </c>
       <c r="D79" s="5">
         <v>10</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" s="5">
-        <v>77</v>
+        <v>138</v>
+      </c>
+      <c r="G79" s="6">
+        <v>68.5</v>
       </c>
       <c r="H79" s="6">
-        <f>MROUND(G78*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
+        <f>MROUND(G80*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C80" s="5">
-        <v>4308</v>
+        <v>4635</v>
       </c>
       <c r="D80" s="5">
         <v>10</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="6">
-        <v>68.5</v>
+        <v>138</v>
+      </c>
+      <c r="G80" s="5">
+        <v>177</v>
       </c>
       <c r="H80" s="6">
-        <f>MROUND(G79*1.03, 0.5)</f>
+        <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C81" s="5">
-        <v>4309</v>
-      </c>
-      <c r="D81" s="5">
-        <v>10</v>
+        <v>4412</v>
+      </c>
+      <c r="D81" s="6">
+        <v>2.5</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>138</v>
       </c>
       <c r="G81" s="6">
-        <v>68.5</v>
-      </c>
-      <c r="H81" s="6">
-        <f>MROUND(G80*1.03, 0.5)</f>
+        <v>75.5</v>
+      </c>
+      <c r="H81" s="5">
+        <f>MROUND(G82*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C82" s="5">
-        <v>4635</v>
+        <v>4413</v>
       </c>
       <c r="D82" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G82" s="5">
-        <v>177</v>
-      </c>
-      <c r="H82" s="6">
-        <f>MROUND(G81*1.03, 0.5)</f>
+        <v>496</v>
+      </c>
+      <c r="H82" s="5">
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C83" s="5">
-        <v>4412</v>
-      </c>
-      <c r="D83" s="6">
-        <v>2.5</v>
+        <v>4414</v>
+      </c>
+      <c r="D83" s="5">
+        <v>5</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G83" s="6">
-        <v>75.5</v>
+        <v>11</v>
+      </c>
+      <c r="G83" s="5">
+        <v>101</v>
       </c>
       <c r="H83" s="5">
-        <f>MROUND(G82*1.03, 0.5)</f>
+        <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C84" s="5">
-        <v>4413</v>
+        <v>4415</v>
       </c>
       <c r="D84" s="5">
         <v>25</v>
@@ -14185,21 +14176,21 @@
         <v>11</v>
       </c>
       <c r="G84" s="5">
-        <v>496</v>
-      </c>
-      <c r="H84" s="5">
-        <f>MROUND(G83*1.03, 0.5)</f>
+        <v>424</v>
+      </c>
+      <c r="H84" s="6">
+        <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C85" s="5">
-        <v>4414</v>
+        <v>4416</v>
       </c>
       <c r="D85" s="5">
         <v>5</v>
@@ -14211,99 +14202,99 @@
         <v>11</v>
       </c>
       <c r="G85" s="5">
-        <v>101</v>
-      </c>
-      <c r="H85" s="5">
-        <f>MROUND(G84*1.03, 0.5)</f>
+        <v>88</v>
+      </c>
+      <c r="H85" s="6">
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C86" s="5">
-        <v>4415</v>
+        <v>4475</v>
       </c>
       <c r="D86" s="5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G86" s="5">
-        <v>424</v>
+        <v>9</v>
       </c>
       <c r="H86" s="6">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C87" s="5">
-        <v>4416</v>
+        <v>4354</v>
       </c>
       <c r="D87" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" s="5">
-        <v>88</v>
-      </c>
-      <c r="H87" s="6">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <v>10</v>
+      </c>
+      <c r="G87" s="6">
+        <v>79.5</v>
+      </c>
+      <c r="H87" s="5">
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C88" s="5">
-        <v>4475</v>
+        <v>4445</v>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>210</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="5">
-        <v>9</v>
-      </c>
-      <c r="H88" s="6">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <v>16</v>
+      </c>
+      <c r="G88" s="6">
+        <v>79.5</v>
+      </c>
+      <c r="H88" s="5">
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C89" s="5">
-        <v>4354</v>
+        <v>4353</v>
       </c>
       <c r="D89" s="5">
         <v>12</v>
@@ -14312,24 +14303,24 @@
         <v>210</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G89" s="6">
         <v>79.5</v>
       </c>
       <c r="H89" s="5">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C90" s="5">
-        <v>4445</v>
+        <v>4350</v>
       </c>
       <c r="D90" s="5">
         <v>12</v>
@@ -14344,18 +14335,18 @@
         <v>79.5</v>
       </c>
       <c r="H90" s="5">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C91" s="5">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="D91" s="5">
         <v>12</v>
@@ -14370,18 +14361,18 @@
         <v>79.5</v>
       </c>
       <c r="H91" s="5">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C92" s="5">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="D92" s="5">
         <v>12</v>
@@ -14396,18 +14387,18 @@
         <v>79.5</v>
       </c>
       <c r="H92" s="5">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <f>MROUND(G93*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C93" s="5">
-        <v>4352</v>
+        <v>4351</v>
       </c>
       <c r="D93" s="5">
         <v>12</v>
@@ -14422,18 +14413,18 @@
         <v>79.5</v>
       </c>
       <c r="H93" s="5">
-        <f>MROUND(G92*1.03, 0.5)</f>
+        <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C94" s="5">
-        <v>4349</v>
+        <v>4581</v>
       </c>
       <c r="D94" s="5">
         <v>12</v>
@@ -14448,266 +14439,214 @@
         <v>79.5</v>
       </c>
       <c r="H94" s="5">
-        <f>MROUND(G93*1.03, 0.5)</f>
+        <f>MROUND(G95*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C95" s="5">
-        <v>4351</v>
+        <v>4096</v>
       </c>
       <c r="D95" s="5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" s="6">
-        <v>79.5</v>
-      </c>
-      <c r="H95" s="5">
-        <f>MROUND(G94*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G95" s="5">
+        <v>79</v>
+      </c>
+      <c r="H95" s="6">
+        <f>MROUND(G96*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C96" s="5">
-        <v>4581</v>
+        <v>4582</v>
       </c>
       <c r="D96" s="5">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="6">
-        <v>79.5</v>
-      </c>
-      <c r="H96" s="5">
-        <f>MROUND(G95*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G96" s="5">
+        <v>45</v>
+      </c>
+      <c r="H96" s="6">
+        <f>MROUND(G97*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C97" s="5">
-        <v>4096</v>
+        <v>4123</v>
       </c>
       <c r="D97" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>30</v>
+        <v>191</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G97" s="5">
-        <v>79</v>
-      </c>
-      <c r="H97" s="6">
-        <f>MROUND(G96*1.03, 0.5)</f>
+        <v>60</v>
+      </c>
+      <c r="H97" s="5">
+        <f>MROUND(G98*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C98" s="5">
-        <v>4582</v>
+        <v>4306</v>
       </c>
       <c r="D98" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="G98" s="5">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="H98" s="6">
-        <f>MROUND(G97*1.03, 0.5)</f>
+        <f>MROUND(G99*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C99" s="5">
-        <v>4123</v>
+        <v>4307</v>
       </c>
       <c r="D99" s="5">
         <v>10</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="G99" s="5">
-        <v>60</v>
-      </c>
-      <c r="H99" s="5">
-        <f>MROUND(G98*1.03, 0.5)</f>
+        <v>81</v>
+      </c>
+      <c r="H99" s="6">
+        <f>MROUND(G100*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C100" s="5">
-        <v>4306</v>
+        <v>2659</v>
       </c>
       <c r="D100" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="G100" s="5">
-        <v>81</v>
-      </c>
-      <c r="H100" s="6">
-        <f>MROUND(G99*1.03, 0.5)</f>
+        <v>30</v>
+      </c>
+      <c r="H100" s="5">
+        <f>MROUND(G101*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C101" s="5">
-        <v>4307</v>
+        <v>2621</v>
       </c>
       <c r="D101" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G101" s="5">
-        <v>81</v>
+        <v>90</v>
+      </c>
+      <c r="G101" s="6">
+        <v>25.5</v>
       </c>
       <c r="H101" s="6">
-        <f>MROUND(G100*1.03, 0.5)</f>
+        <f>MROUND(G102*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C102" s="5">
-        <v>2659</v>
+        <v>3656</v>
       </c>
       <c r="D102" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>90</v>
       </c>
       <c r="G102" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H102" s="5">
-        <f>MROUND(G101*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
-      <c r="A103" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C103" s="5">
-        <v>2621</v>
-      </c>
-      <c r="D103" s="5">
-        <v>5</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G103" s="6">
-        <v>25.5</v>
-      </c>
-      <c r="H103" s="6">
-        <f>MROUND(G102*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
-      <c r="A104" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C104" s="5">
-        <v>3656</v>
-      </c>
-      <c r="D104" s="5">
-        <v>5</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G104" s="5">
-        <v>27</v>
-      </c>
-      <c r="H104" s="5">
         <f>MROUND(G103*1.03, 0.5)</f>
       </c>
     </row>
@@ -20864,7 +20803,7 @@
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20890,7 +20829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>849</v>
       </c>
@@ -20916,7 +20855,7 @@
         <f>MROUND(G2*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>851</v>
       </c>
@@ -20942,7 +20881,7 @@
         <f>MROUND(G3*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>851</v>
       </c>
@@ -20968,7 +20907,7 @@
         <f>MROUND(G4*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>853</v>
       </c>
@@ -20994,7 +20933,7 @@
         <f>MROUND(G5*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>855</v>
       </c>
@@ -21020,7 +20959,7 @@
         <f>MROUND(G6*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>857</v>
       </c>
@@ -21046,7 +20985,7 @@
         <f>MROUND(G7*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>857</v>
       </c>
@@ -21072,7 +21011,7 @@
         <f>MROUND(G8*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>859</v>
       </c>
@@ -21098,7 +21037,7 @@
         <f>MROUND(G9*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>859</v>
       </c>
@@ -21124,7 +21063,7 @@
         <f>MROUND(G10*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>861</v>
       </c>
@@ -21150,7 +21089,7 @@
         <f>MROUND(G11*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>861</v>
       </c>
@@ -21176,7 +21115,7 @@
         <f>MROUND(G12*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>863</v>
       </c>
@@ -21202,7 +21141,7 @@
         <f>MROUND(G13*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>863</v>
       </c>
@@ -21228,7 +21167,7 @@
         <f>MROUND(G14*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>865</v>
       </c>
@@ -21254,7 +21193,7 @@
         <f>MROUND(G15*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>865</v>
       </c>
@@ -21280,7 +21219,7 @@
         <f>MROUND(G16*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>865</v>
       </c>
@@ -21306,7 +21245,7 @@
         <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>867</v>
       </c>
@@ -21332,7 +21271,7 @@
         <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>867</v>
       </c>
@@ -21358,7 +21297,7 @@
         <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>867</v>
       </c>
@@ -21384,7 +21323,7 @@
         <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>869</v>
       </c>
@@ -21410,7 +21349,7 @@
         <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>869</v>
       </c>
@@ -21436,7 +21375,7 @@
         <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>871</v>
       </c>
@@ -24235,7 +24174,7 @@
         <v>147</v>
       </c>
       <c r="G57" s="5">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="H57" s="6">
         <f>MROUND(G57*1.03, 0.5)</f>
@@ -24261,7 +24200,7 @@
         <v>147</v>
       </c>
       <c r="G58" s="5">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H58" s="6">
         <f>MROUND(G58*1.03, 0.5)</f>
@@ -24287,7 +24226,7 @@
         <v>11</v>
       </c>
       <c r="G59" s="5">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="H59" s="5">
         <f>MROUND(G59*1.03, 0.5)</f>
@@ -27482,7 +27421,7 @@
         <v>147</v>
       </c>
       <c r="G88" s="5">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="H88" s="6">
         <f>MROUND(G88*1.03, 0.5)</f>
@@ -27508,7 +27447,7 @@
         <v>11</v>
       </c>
       <c r="G89" s="6">
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
       <c r="H89" s="6">
         <f>MROUND(G89*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="1127">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3387,6 +3387,9 @@
   </si>
   <si>
     <t>MACADAMIA TORRADA S/SAL</t>
+  </si>
+  <si>
+    <t>X1.1KG</t>
   </si>
   <si>
     <t>mix-de-castanhas</t>
@@ -10317,7 +10320,7 @@
         <v>11</v>
       </c>
       <c r="G108" s="5">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H108" s="6">
         <f>MROUND(G109*1.03, 0.5)</f>
@@ -10343,7 +10346,7 @@
         <v>11</v>
       </c>
       <c r="G109" s="5">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H109" s="6">
         <f>MROUND(G110*1.03, 0.5)</f>
@@ -10369,7 +10372,7 @@
         <v>11</v>
       </c>
       <c r="G110" s="5">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H110" s="6">
         <f>MROUND(G111*1.03, 0.5)</f>
@@ -16057,7 +16060,7 @@
         <f>MROUND(G15*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>1047</v>
       </c>
@@ -16083,7 +16086,7 @@
         <f>MROUND(G16*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>1047</v>
       </c>
@@ -16109,7 +16112,7 @@
         <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>1049</v>
       </c>
@@ -16135,7 +16138,7 @@
         <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>1049</v>
       </c>
@@ -16161,7 +16164,7 @@
         <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>1051</v>
       </c>
@@ -16187,7 +16190,7 @@
         <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>1051</v>
       </c>
@@ -16213,7 +16216,7 @@
         <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>1053</v>
       </c>
@@ -16239,7 +16242,7 @@
         <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>1053</v>
       </c>
@@ -16265,7 +16268,7 @@
         <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>1055</v>
       </c>
@@ -16291,7 +16294,7 @@
         <f>MROUND(G24*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>1055</v>
       </c>
@@ -16317,7 +16320,7 @@
         <f>MROUND(G25*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>1057</v>
       </c>
@@ -16343,7 +16346,7 @@
         <f>MROUND(G26*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
         <v>1059</v>
       </c>
@@ -16369,7 +16372,7 @@
         <f>MROUND(G27*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
         <v>1061</v>
       </c>
@@ -16395,7 +16398,7 @@
         <f>MROUND(G28*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
         <v>1063</v>
       </c>
@@ -16421,7 +16424,7 @@
         <f>MROUND(G29*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4" t="s">
         <v>1065</v>
       </c>
@@ -16447,7 +16450,7 @@
         <f>MROUND(G30*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4" t="s">
         <v>1067</v>
       </c>
@@ -16473,7 +16476,7 @@
         <f>MROUND(G31*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="4" t="s">
         <v>1067</v>
       </c>
@@ -16499,7 +16502,7 @@
         <f>MROUND(G32*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
         <v>1069</v>
       </c>
@@ -16525,7 +16528,7 @@
         <f>MROUND(G33*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
         <v>1069</v>
       </c>
@@ -16551,7 +16554,7 @@
         <f>MROUND(G34*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
         <v>1071</v>
       </c>
@@ -16577,7 +16580,7 @@
         <f>MROUND(G35*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
         <v>1073</v>
       </c>
@@ -16603,7 +16606,7 @@
         <f>MROUND(G36*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
         <v>1075</v>
       </c>
@@ -16629,7 +16632,7 @@
         <f>MROUND(G37*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="4" t="s">
         <v>1075</v>
       </c>
@@ -16655,7 +16658,7 @@
         <f>MROUND(G38*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="4" t="s">
         <v>1077</v>
       </c>
@@ -16675,7 +16678,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="5">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H39" s="6">
         <f>MROUND(G39*1.03, 0.5)</f>
@@ -16701,7 +16704,7 @@
         <v>147</v>
       </c>
       <c r="G40" s="5">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H40" s="6">
         <f>MROUND(G40*1.03, 0.5)</f>
@@ -16727,7 +16730,7 @@
         <v>11</v>
       </c>
       <c r="G41" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H41" s="5">
         <f>MROUND(G41*1.03, 0.5)</f>
@@ -16753,7 +16756,7 @@
         <v>11</v>
       </c>
       <c r="G42" s="5">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H42" s="6">
         <f>MROUND(G42*1.03, 0.5)</f>
@@ -16779,7 +16782,7 @@
         <v>147</v>
       </c>
       <c r="G43" s="5">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H43" s="6">
         <f>MROUND(G43*1.03, 0.5)</f>
@@ -16805,7 +16808,7 @@
         <v>11</v>
       </c>
       <c r="G44" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H44" s="5">
         <f>MROUND(G44*1.03, 0.5)</f>
@@ -17732,7 +17735,7 @@
         <v>4021</v>
       </c>
       <c r="D80" s="5">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>30</v>
@@ -17741,7 +17744,7 @@
         <v>11</v>
       </c>
       <c r="G80" s="5">
-        <v>125</v>
+        <v>116.5</v>
       </c>
       <c r="H80" s="5">
         <f>MROUND(G78*1.03, 0.5)</f>
@@ -17758,16 +17761,16 @@
         <v>4135</v>
       </c>
       <c r="D81" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>30</v>
+        <v>1118</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G81" s="5">
-        <v>1250</v>
+        <v>1398</v>
       </c>
       <c r="H81" s="6">
         <f>MROUND(G79*1.03, 0.5)</f>
@@ -17775,10 +17778,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C82" s="5">
         <v>2852</v>
@@ -17801,10 +17804,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C83" s="5">
         <v>3601</v>
@@ -17827,10 +17830,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C84" s="5">
         <v>263</v>
@@ -17853,10 +17856,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C85" s="5">
         <v>2632</v>
@@ -17879,10 +17882,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C86" s="5">
         <v>2330</v>
@@ -17905,10 +17908,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C87" s="5">
         <v>2385</v>
@@ -17931,10 +17934,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C88" s="5">
         <v>2384</v>
@@ -17957,10 +17960,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C89" s="5">
         <v>3851</v>
@@ -17983,10 +17986,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C90" s="5">
         <v>2424</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="1129">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3408,6 +3408,12 @@
   </si>
   <si>
     <t>NOZES QUARTOS</t>
+  </si>
+  <si>
+    <t>nozes-moscada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOZ MOSCADA EM PÓ </t>
   </si>
   <si>
     <t>xerem-de-amendoim</t>
@@ -5025,7 +5031,7 @@
         <v>147</v>
       </c>
       <c r="G6" s="5">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H6" s="5">
         <f>MROUND(G6*1.03, 0.5)</f>
@@ -5493,7 +5499,7 @@
         <v>147</v>
       </c>
       <c r="G24" s="5">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H24" s="5">
         <f>MROUND(G23*1.03, 0.5)</f>
@@ -5519,7 +5525,7 @@
         <v>147</v>
       </c>
       <c r="G25" s="5">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H25" s="5">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -5727,7 +5733,7 @@
         <v>147</v>
       </c>
       <c r="G33" s="5">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H33" s="5">
         <f>MROUND(G32*1.03, 0.5)</f>
@@ -5753,7 +5759,7 @@
         <v>11</v>
       </c>
       <c r="G34" s="5">
-        <v>37</v>
+        <v>38.5</v>
       </c>
       <c r="H34" s="5">
         <f>MROUND(G33*1.03, 0.5)</f>
@@ -5779,7 +5785,7 @@
         <v>147</v>
       </c>
       <c r="G35" s="5">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H35" s="5">
         <f>MROUND(G34*1.03, 0.5)</f>
@@ -5805,7 +5811,7 @@
         <v>11</v>
       </c>
       <c r="G36" s="5">
-        <v>37</v>
+        <v>38.5</v>
       </c>
       <c r="H36" s="5">
         <f>MROUND(G35*1.03, 0.5)</f>
@@ -15657,7 +15663,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -16684,7 +16690,7 @@
         <f>MROUND(G39*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
         <v>1077</v>
       </c>
@@ -16710,7 +16716,7 @@
         <f>MROUND(G40*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="4" t="s">
         <v>1077</v>
       </c>
@@ -16736,7 +16742,7 @@
         <f>MROUND(G41*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
         <v>1079</v>
       </c>
@@ -16762,7 +16768,7 @@
         <f>MROUND(G42*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="4" t="s">
         <v>1079</v>
       </c>
@@ -16788,7 +16794,7 @@
         <f>MROUND(G43*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="4" t="s">
         <v>1079</v>
       </c>
@@ -16814,7 +16820,7 @@
         <f>MROUND(G44*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
         <v>1081</v>
       </c>
@@ -16840,7 +16846,7 @@
         <f>MROUND(G45*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="4" t="s">
         <v>1083</v>
       </c>
@@ -16866,7 +16872,7 @@
         <f>MROUND(G46*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="4" t="s">
         <v>1081</v>
       </c>
@@ -16892,7 +16898,7 @@
         <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
         <v>1085</v>
       </c>
@@ -16918,7 +16924,7 @@
         <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="4" t="s">
         <v>1085</v>
       </c>
@@ -16944,7 +16950,7 @@
         <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="4" t="s">
         <v>1087</v>
       </c>
@@ -16970,7 +16976,7 @@
         <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="4" t="s">
         <v>1087</v>
       </c>
@@ -16996,7 +17002,7 @@
         <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="4" t="s">
         <v>1089</v>
       </c>
@@ -17022,7 +17028,7 @@
         <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="4" t="s">
         <v>1089</v>
       </c>
@@ -17048,7 +17054,7 @@
         <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="4" t="s">
         <v>1091</v>
       </c>
@@ -17940,73 +17946,99 @@
         <v>1126</v>
       </c>
       <c r="C88" s="5">
-        <v>2384</v>
+        <v>4540</v>
       </c>
       <c r="D88" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G88" s="6">
-        <v>187.5</v>
-      </c>
-      <c r="H88" s="5">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G88" s="5">
+        <v>650</v>
+      </c>
+      <c r="H88" s="6">
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C89" s="5">
-        <v>3851</v>
+        <v>2384</v>
       </c>
       <c r="D89" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G89" s="5">
-        <v>75</v>
-      </c>
-      <c r="H89" s="6">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <v>16</v>
+      </c>
+      <c r="G89" s="6">
+        <v>187.5</v>
+      </c>
+      <c r="H89" s="5">
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C90" s="5">
+        <v>3851</v>
+      </c>
+      <c r="D90" s="5">
+        <v>10</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G90" s="5">
+        <v>75</v>
+      </c>
+      <c r="H90" s="6">
+        <f>MROUND(G88*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C91" s="5">
         <v>2424</v>
       </c>
-      <c r="D90" s="5">
-        <v>5</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="6">
+      <c r="D91" s="5">
+        <v>5</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="6">
         <v>39.5</v>
       </c>
-      <c r="H90" s="6">
+      <c r="H91" s="6">
         <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
@@ -19165,7 +19197,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H16" s="6">
         <f>MROUND(G16*1.03, 0.5)</f>
@@ -19191,7 +19223,7 @@
         <v>11</v>
       </c>
       <c r="G17" s="5">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="H17" s="5">
         <f>MROUND(G17*1.03, 0.5)</f>
@@ -19321,7 +19353,7 @@
         <v>147</v>
       </c>
       <c r="G22" s="5">
-        <v>530</v>
+        <v>440</v>
       </c>
       <c r="H22" s="5">
         <f>MROUND(G22*1.03, 0.5)</f>
@@ -19347,7 +19379,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="5">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H23" s="6">
         <f>MROUND(G23*1.03, 0.5)</f>
@@ -19971,7 +20003,7 @@
         <v>147</v>
       </c>
       <c r="G47" s="5">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="H47" s="6">
         <f>MROUND(G47*1.03, 0.5)</f>
@@ -19997,7 +20029,7 @@
         <v>147</v>
       </c>
       <c r="G48" s="5">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="H48" s="6">
         <f>MROUND(G47*1.03, 0.5)</f>
@@ -20023,7 +20055,7 @@
         <v>11</v>
       </c>
       <c r="G49" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H49" s="5">
         <f>MROUND(G48*1.03, 0.5)</f>
@@ -22688,7 +22720,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -23871,7 +23903,7 @@
         <f>MROUND(G45*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
         <v>803</v>
       </c>
@@ -23879,10 +23911,10 @@
         <v>804</v>
       </c>
       <c r="C46" s="5">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D46" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>30</v>
@@ -23891,7 +23923,7 @@
         <v>147</v>
       </c>
       <c r="G46" s="6">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="H46" s="6">
         <f>MROUND(G46*1.03, 0.5)</f>
@@ -23905,10 +23937,10 @@
         <v>804</v>
       </c>
       <c r="C47" s="5">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D47" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>30</v>
@@ -23916,25 +23948,25 @@
       <c r="F47" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G47" s="5">
-        <v>26</v>
-      </c>
-      <c r="H47" s="5">
-        <f>MROUND(G47*1.03, 0.5)</f>
+      <c r="G47" s="6">
+        <v>115</v>
+      </c>
+      <c r="H47" s="6">
+        <f>MROUND(G46*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C48" s="5">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D48" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>30</v>
@@ -23943,10 +23975,10 @@
         <v>147</v>
       </c>
       <c r="G48" s="5">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="H48" s="5">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -23957,48 +23989,48 @@
         <v>806</v>
       </c>
       <c r="C49" s="5">
+        <v>3025</v>
+      </c>
+      <c r="D49" s="5">
+        <v>30</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G49" s="5">
+        <v>170</v>
+      </c>
+      <c r="H49" s="5">
+        <f>MROUND(G48*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+      <c r="A50" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C50" s="5">
         <v>2543</v>
       </c>
-      <c r="D49" s="5">
-        <v>5</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="6">
+      <c r="D50" s="5">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="6">
         <v>31.5</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H50" s="6">
         <f>MROUND(G49*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="C50" s="5">
-        <v>98</v>
-      </c>
-      <c r="D50" s="5">
-        <v>30</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G50" s="5">
-        <v>320</v>
-      </c>
-      <c r="H50" s="6">
-        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -24009,10 +24041,10 @@
         <v>808</v>
       </c>
       <c r="C51" s="5">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D51" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>30</v>
@@ -24020,25 +24052,25 @@
       <c r="F51" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G51" s="6">
-        <v>55.5</v>
-      </c>
-      <c r="H51" s="5">
-        <f>MROUND(G51*1.03, 0.5)</f>
+      <c r="G51" s="5">
+        <v>320</v>
+      </c>
+      <c r="H51" s="6">
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C52" s="5">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D52" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>30</v>
@@ -24047,10 +24079,10 @@
         <v>147</v>
       </c>
       <c r="G52" s="6">
-        <v>362.5</v>
-      </c>
-      <c r="H52" s="6">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <v>55.5</v>
+      </c>
+      <c r="H52" s="5">
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -24061,51 +24093,51 @@
         <v>810</v>
       </c>
       <c r="C53" s="5">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D53" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G53" s="6">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
       <c r="H53" s="6">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C54" s="5">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D54" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="5">
-        <v>255</v>
+        <v>11</v>
+      </c>
+      <c r="G54" s="6">
+        <v>74.5</v>
       </c>
       <c r="H54" s="6">
-        <f>MROUND(G54*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
+        <f>MROUND(G53*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
         <v>811</v>
       </c>
@@ -24113,10 +24145,10 @@
         <v>812</v>
       </c>
       <c r="C55" s="5">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D55" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>30</v>
@@ -24124,11 +24156,11 @@
       <c r="F55" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="6">
-        <v>212.5</v>
-      </c>
-      <c r="H55" s="5">
-        <f>MROUND(G55*1.03, 0.5)</f>
+      <c r="G55" s="5">
+        <v>255</v>
+      </c>
+      <c r="H55" s="6">
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
@@ -24139,48 +24171,48 @@
         <v>812</v>
       </c>
       <c r="C56" s="5">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D56" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G56" s="6">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
       <c r="H56" s="5">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="4" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C57" s="5">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D57" s="5">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G57" s="5">
-        <v>350</v>
-      </c>
-      <c r="H57" s="6">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G57" s="6">
+        <v>44.5</v>
+      </c>
+      <c r="H57" s="5">
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -24191,10 +24223,10 @@
         <v>814</v>
       </c>
       <c r="C58" s="5">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D58" s="5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>30</v>
@@ -24203,10 +24235,10 @@
         <v>147</v>
       </c>
       <c r="G58" s="5">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="H58" s="6">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -24217,48 +24249,48 @@
         <v>814</v>
       </c>
       <c r="C59" s="5">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D59" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G59" s="5">
-        <v>32</v>
-      </c>
-      <c r="H59" s="5">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <v>175</v>
+      </c>
+      <c r="H59" s="6">
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C60" s="5">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D60" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G60" s="5">
-        <v>275</v>
-      </c>
-      <c r="H60" s="6">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <v>32</v>
+      </c>
+      <c r="H60" s="5">
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
@@ -24269,48 +24301,48 @@
         <v>816</v>
       </c>
       <c r="C61" s="5">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D61" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G61" s="5">
-        <v>57</v>
+        <v>275</v>
       </c>
       <c r="H61" s="6">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="4" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C62" s="5">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D62" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G62" s="5">
-        <v>280</v>
+        <v>57</v>
       </c>
       <c r="H62" s="6">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
@@ -24321,10 +24353,10 @@
         <v>818</v>
       </c>
       <c r="C63" s="5">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D63" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>30</v>
@@ -24332,25 +24364,25 @@
       <c r="F63" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G63" s="6">
-        <v>48.5</v>
-      </c>
-      <c r="H63" s="5">
-        <f>MROUND(G63*1.03, 0.5)</f>
+      <c r="G63" s="5">
+        <v>280</v>
+      </c>
+      <c r="H63" s="6">
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="4" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C64" s="5">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D64" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>30</v>
@@ -24358,11 +24390,11 @@
       <c r="F64" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G64" s="5">
-        <v>375</v>
-      </c>
-      <c r="H64" s="6">
-        <f>MROUND(G64*1.03, 0.5)</f>
+      <c r="G64" s="6">
+        <v>48.5</v>
+      </c>
+      <c r="H64" s="5">
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
@@ -24373,48 +24405,48 @@
         <v>820</v>
       </c>
       <c r="C65" s="5">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D65" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" s="6">
-        <v>64.5</v>
+        <v>147</v>
+      </c>
+      <c r="G65" s="5">
+        <v>375</v>
       </c>
       <c r="H65" s="6">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="4" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C66" s="5">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D66" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G66" s="5">
-        <v>330</v>
-      </c>
-      <c r="H66" s="5">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G66" s="6">
+        <v>64.5</v>
+      </c>
+      <c r="H66" s="6">
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
@@ -24425,48 +24457,48 @@
         <v>822</v>
       </c>
       <c r="C67" s="5">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D67" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G67" s="5">
-        <v>57</v>
-      </c>
-      <c r="H67" s="6">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <v>330</v>
+      </c>
+      <c r="H67" s="5">
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="4" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C68" s="5">
-        <v>3740</v>
+        <v>2468</v>
       </c>
       <c r="D68" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G68" s="5">
-        <v>237.5</v>
-      </c>
-      <c r="H68" s="5">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <v>57</v>
+      </c>
+      <c r="H68" s="6">
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
@@ -24477,48 +24509,48 @@
         <v>824</v>
       </c>
       <c r="C69" s="5">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D69" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="6">
-        <v>50.5</v>
-      </c>
-      <c r="H69" s="6">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <v>147</v>
+      </c>
+      <c r="G69" s="5">
+        <v>237.5</v>
+      </c>
+      <c r="H69" s="5">
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C70" s="5">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D70" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G70" s="6">
-        <v>312.5</v>
-      </c>
-      <c r="H70" s="5">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <v>50.5</v>
+      </c>
+      <c r="H70" s="6">
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
@@ -24529,48 +24561,48 @@
         <v>826</v>
       </c>
       <c r="C71" s="5">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D71" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G71" s="6">
-        <v>64.5</v>
-      </c>
-      <c r="H71" s="6">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <v>312.5</v>
+      </c>
+      <c r="H71" s="5">
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C72" s="5">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D72" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G72" s="5">
-        <v>300</v>
-      </c>
-      <c r="H72" s="5">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <v>11</v>
+      </c>
+      <c r="G72" s="6">
+        <v>64.5</v>
+      </c>
+      <c r="H72" s="6">
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
@@ -24581,48 +24613,48 @@
         <v>828</v>
       </c>
       <c r="C73" s="5">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D73" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G73" s="5">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="H73" s="5">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="4" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C74" s="5">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D74" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G74" s="5">
-        <v>180</v>
-      </c>
-      <c r="H74" s="6">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <v>62</v>
+      </c>
+      <c r="H74" s="5">
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
@@ -24633,48 +24665,48 @@
         <v>830</v>
       </c>
       <c r="C75" s="5">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D75" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G75" s="5">
-        <v>38</v>
-      </c>
-      <c r="H75" s="5">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <v>180</v>
+      </c>
+      <c r="H75" s="6">
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C76" s="5">
-        <v>211</v>
-      </c>
-      <c r="D76" s="6">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D76" s="5">
+        <v>5</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G76" s="6">
-        <v>179</v>
+        <v>11</v>
+      </c>
+      <c r="G76" s="5">
+        <v>38</v>
       </c>
       <c r="H76" s="5">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
@@ -24685,10 +24717,10 @@
         <v>832</v>
       </c>
       <c r="C77" s="5">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D77" s="6">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>30</v>
@@ -24696,11 +24728,11 @@
       <c r="F77" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G77" s="5">
-        <v>358</v>
-      </c>
-      <c r="H77" s="6">
-        <f>MROUND(G77*1.03, 0.5)</f>
+      <c r="G77" s="6">
+        <v>179</v>
+      </c>
+      <c r="H77" s="5">
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
@@ -24711,48 +24743,48 @@
         <v>832</v>
       </c>
       <c r="C78" s="5">
+        <v>41</v>
+      </c>
+      <c r="D78" s="6">
+        <v>45.36</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G78" s="5">
+        <v>358</v>
+      </c>
+      <c r="H78" s="6">
+        <f>MROUND(G77*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
+      <c r="A79" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C79" s="5">
         <v>2322</v>
       </c>
-      <c r="D78" s="5">
-        <v>5</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" s="6">
+      <c r="D79" s="5">
+        <v>5</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="6">
         <v>42.5</v>
       </c>
-      <c r="H78" s="5">
+      <c r="H79" s="5">
         <f>MROUND(G78*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="4" t="s">
-        <v>833</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="C79" s="5">
-        <v>67</v>
-      </c>
-      <c r="D79" s="6">
-        <v>45.36</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G79" s="5">
-        <v>544</v>
-      </c>
-      <c r="H79" s="6">
-        <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
@@ -24763,10 +24795,10 @@
         <v>834</v>
       </c>
       <c r="C80" s="5">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D80" s="6">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>30</v>
@@ -24775,10 +24807,10 @@
         <v>147</v>
       </c>
       <c r="G80" s="5">
-        <v>272</v>
-      </c>
-      <c r="H80" s="5">
-        <f>MROUND(G80*1.03, 0.5)</f>
+        <v>544</v>
+      </c>
+      <c r="H80" s="6">
+        <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -24789,74 +24821,74 @@
         <v>834</v>
       </c>
       <c r="C81" s="5">
-        <v>2488</v>
-      </c>
-      <c r="D81" s="5">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D81" s="6">
+        <v>22.68</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G81" s="5">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="H81" s="5">
-        <f>MROUND(G81*1.03, 0.5)</f>
+        <f>MROUND(G80*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C82" s="5">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D82" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G82" s="5">
-        <v>52</v>
-      </c>
-      <c r="H82" s="6">
-        <f>MROUND(G82*1.03, 0.5)</f>
+        <v>63</v>
+      </c>
+      <c r="H82" s="5">
+        <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C83" s="5">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D83" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G83" s="5">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="H83" s="6">
-        <f>MROUND(G83*1.03, 0.5)</f>
+        <f>MROUND(G82*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -24867,22 +24899,22 @@
         <v>838</v>
       </c>
       <c r="C84" s="5">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D84" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G84" s="5">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="H84" s="6">
-        <f>MROUND(G84*1.03, 0.5)</f>
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -24893,10 +24925,10 @@
         <v>838</v>
       </c>
       <c r="C85" s="5">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D85" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
@@ -24905,10 +24937,10 @@
         <v>147</v>
       </c>
       <c r="G85" s="5">
-        <v>700</v>
-      </c>
-      <c r="H85" s="5">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <v>350</v>
+      </c>
+      <c r="H85" s="6">
+        <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -24919,62 +24951,62 @@
         <v>838</v>
       </c>
       <c r="C86" s="5">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D86" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G86" s="5">
-        <v>106</v>
+        <v>700</v>
       </c>
       <c r="H86" s="5">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C87" s="5">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D87" s="5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G87" s="5">
-        <v>87</v>
-      </c>
-      <c r="H87" s="6">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <v>106</v>
+      </c>
+      <c r="H87" s="5">
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C88" s="5">
-        <v>135</v>
-      </c>
-      <c r="D88" s="6">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D88" s="5">
+        <v>25</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
@@ -24983,24 +25015,24 @@
         <v>147</v>
       </c>
       <c r="G88" s="5">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H88" s="6">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C89" s="5">
-        <v>2463</v>
-      </c>
-      <c r="D89" s="5">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D89" s="6">
+        <v>22.68</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
@@ -25009,24 +25041,24 @@
         <v>147</v>
       </c>
       <c r="G89" s="5">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H89" s="6">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C90" s="5">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D90" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -25035,10 +25067,10 @@
         <v>147</v>
       </c>
       <c r="G90" s="5">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="H90" s="6">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -25049,10 +25081,10 @@
         <v>846</v>
       </c>
       <c r="C91" s="5">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D91" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>30</v>
@@ -25061,24 +25093,24 @@
         <v>147</v>
       </c>
       <c r="G91" s="5">
-        <v>24</v>
-      </c>
-      <c r="H91" s="5">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <v>105</v>
+      </c>
+      <c r="H91" s="6">
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C92" s="5">
-        <v>4223</v>
+        <v>51</v>
       </c>
       <c r="D92" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>30</v>
@@ -25087,10 +25119,10 @@
         <v>147</v>
       </c>
       <c r="G92" s="5">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="H92" s="5">
-        <f>MROUND(G93*1.03, 0.5)</f>
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -25101,21 +25133,47 @@
         <v>848</v>
       </c>
       <c r="C93" s="5">
+        <v>4223</v>
+      </c>
+      <c r="D93" s="5">
+        <v>25</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G93" s="5">
+        <v>125</v>
+      </c>
+      <c r="H93" s="5">
+        <f>MROUND(G93*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C94" s="5">
         <v>4224</v>
       </c>
-      <c r="D93" s="5">
-        <v>5</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93" s="5">
+      <c r="D94" s="5">
+        <v>5</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="5">
         <v>27</v>
       </c>
-      <c r="H93" s="5">
+      <c r="H94" s="5">
         <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
@@ -25500,7 +25558,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H14" s="6">
         <f>MROUND(G14*1.03, 0.5)</f>
@@ -25526,7 +25584,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="5">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="H15" s="6">
         <f>MROUND(G15*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -6715,7 +6715,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="6">
-        <v>64.5</v>
+        <v>67.5</v>
       </c>
       <c r="H5" s="6">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -6741,7 +6741,7 @@
         <v>147</v>
       </c>
       <c r="G6" s="6">
-        <v>312.5</v>
+        <v>322.5</v>
       </c>
       <c r="H6" s="5">
         <f>MROUND(G6*1.03, 0.5)</f>
@@ -17730,7 +17730,7 @@
         <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="4" t="s">
         <v>1116</v>
       </c>
@@ -17756,7 +17756,7 @@
         <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="4" t="s">
         <v>1116</v>
       </c>
@@ -17782,7 +17782,7 @@
         <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="4" t="s">
         <v>1119</v>
       </c>
@@ -17808,7 +17808,7 @@
         <f>MROUND(G80*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="4" t="s">
         <v>1119</v>
       </c>
@@ -17834,7 +17834,7 @@
         <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="4" t="s">
         <v>1121</v>
       </c>
@@ -17860,7 +17860,7 @@
         <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
       <c r="A85" s="4" t="s">
         <v>1121</v>
       </c>
@@ -17886,7 +17886,7 @@
         <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="4" t="s">
         <v>1123</v>
       </c>
@@ -17912,7 +17912,7 @@
         <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="4" t="s">
         <v>1123</v>
       </c>
@@ -19197,7 +19197,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="6">
         <f>MROUND(G16*1.03, 0.5)</f>
@@ -19223,7 +19223,7 @@
         <v>11</v>
       </c>
       <c r="G17" s="5">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="H17" s="5">
         <f>MROUND(G17*1.03, 0.5)</f>
@@ -22831,7 +22831,7 @@
         <v>147</v>
       </c>
       <c r="G4" s="5">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="H4" s="5">
         <f>MROUND(G4*1.03, 0.5)</f>
@@ -22857,7 +22857,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="5">
-        <v>24.5</v>
+        <v>31.5</v>
       </c>
       <c r="H5" s="6">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -25093,7 +25093,7 @@
         <v>147</v>
       </c>
       <c r="G91" s="5">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H91" s="6">
         <f>MROUND(G90*1.03, 0.5)</f>
@@ -25119,7 +25119,7 @@
         <v>147</v>
       </c>
       <c r="G92" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H92" s="5">
         <f>MROUND(G91*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -7131,7 +7131,7 @@
         <v>147</v>
       </c>
       <c r="G21" s="5">
-        <v>95</v>
+        <v>122.5</v>
       </c>
       <c r="H21" s="5">
         <f>MROUND(G21*1.03, 0.5)</f>
@@ -7157,7 +7157,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H22" s="6">
         <f>MROUND(G22*1.03, 0.5)</f>
@@ -7443,7 +7443,7 @@
         <v>147</v>
       </c>
       <c r="G33" s="6">
-        <v>312.5</v>
+        <v>275</v>
       </c>
       <c r="H33" s="5">
         <f>MROUND(G33*1.03, 0.5)</f>
@@ -7469,7 +7469,7 @@
         <v>11</v>
       </c>
       <c r="G34" s="6">
-        <v>66.5</v>
+        <v>58</v>
       </c>
       <c r="H34" s="6">
         <f>MROUND(G34*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -13587,7 +13587,7 @@
         <v>11</v>
       </c>
       <c r="G61" s="5">
-        <v>48</v>
+        <v>52.5</v>
       </c>
       <c r="H61" s="6">
         <f>MROUND(G61*1.03, 0.5)</f>
@@ -13613,7 +13613,7 @@
         <v>11</v>
       </c>
       <c r="G62" s="5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H62" s="5">
         <f>MROUND(G62*1.03, 0.5)</f>
@@ -13665,7 +13665,7 @@
         <v>11</v>
       </c>
       <c r="G64" s="5">
-        <v>48</v>
+        <v>52.5</v>
       </c>
       <c r="H64" s="6">
         <f>MROUND(G64*1.03, 0.5)</f>
@@ -13691,7 +13691,7 @@
         <v>11</v>
       </c>
       <c r="G65" s="5">
-        <v>48</v>
+        <v>52.5</v>
       </c>
       <c r="H65" s="6">
         <f>MROUND(G65*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="17"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -13333,7 +13333,7 @@
         <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="4" t="s">
         <v>141</v>
       </c>
@@ -13359,7 +13359,7 @@
         <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="4" t="s">
         <v>141</v>
       </c>
@@ -13385,7 +13385,7 @@
         <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="4" t="s">
         <v>143</v>
       </c>
@@ -13411,7 +13411,7 @@
         <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="4" t="s">
         <v>145</v>
       </c>
@@ -13697,7 +13697,7 @@
         <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="4" t="s">
         <v>170</v>
       </c>
@@ -19431,7 +19431,7 @@
         <v>147</v>
       </c>
       <c r="G25" s="5">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="H25" s="5">
         <f>MROUND(G25*1.03, 0.5)</f>
@@ -19457,7 +19457,7 @@
         <v>11</v>
       </c>
       <c r="G26" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="6">
         <f>MROUND(G26*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4178,10 +4178,10 @@
         <v>147</v>
       </c>
       <c r="G13" s="6">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H13" s="6">
-        <v>113.5</v>
+        <v>129</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -4204,10 +4204,10 @@
         <v>147</v>
       </c>
       <c r="G14" s="6">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H14" s="6">
-        <v>102</v>
+        <v>115.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -4334,10 +4334,10 @@
         <v>147</v>
       </c>
       <c r="G19" s="5">
-        <v>287.5</v>
+        <v>275</v>
       </c>
       <c r="H19" s="6">
-        <v>296</v>
+        <v>283</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -4360,10 +4360,10 @@
         <v>11</v>
       </c>
       <c r="G20" s="5">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="H20" s="5">
-        <v>62.5</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -19489,7 +19489,7 @@
         <f>MROUND(G27*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
         <v>947</v>
       </c>
@@ -19515,7 +19515,7 @@
         <f>MROUND(G28*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
         <v>949</v>
       </c>
@@ -24625,7 +24625,7 @@
         <v>147</v>
       </c>
       <c r="G73" s="5">
-        <v>300</v>
+        <v>262.5</v>
       </c>
       <c r="H73" s="5">
         <f>MROUND(G72*1.03, 0.5)</f>
@@ -24651,7 +24651,7 @@
         <v>11</v>
       </c>
       <c r="G74" s="5">
-        <v>62</v>
+        <v>55.5</v>
       </c>
       <c r="H74" s="5">
         <f>MROUND(G73*1.03, 0.5)</f>
@@ -24677,7 +24677,7 @@
         <v>147</v>
       </c>
       <c r="G75" s="5">
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="H75" s="6">
         <f>MROUND(G74*1.03, 0.5)</f>
@@ -24703,7 +24703,7 @@
         <v>11</v>
       </c>
       <c r="G76" s="5">
-        <v>38</v>
+        <v>35.5</v>
       </c>
       <c r="H76" s="5">
         <f>MROUND(G75*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1130">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -4267,10 +4267,10 @@
         <v>29</v>
       </c>
       <c r="G16" s="3">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5354,7 +5354,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="3">
-        <f>MROUND(G17*1.03, 0.5)</f>
+        <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5380,7 +5380,7 @@
         <v>55</v>
       </c>
       <c r="H19" s="3">
-        <f>MROUND(G18*1.03, 0.5)</f>
+        <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5406,7 +5406,7 @@
         <v>530</v>
       </c>
       <c r="H20" s="3">
-        <f>MROUND(G19*1.03, 0.5)</f>
+        <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5432,7 +5432,7 @@
         <v>275</v>
       </c>
       <c r="H21" s="3">
-        <f>MROUND(G20*1.03, 0.5)</f>
+        <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5458,7 +5458,7 @@
         <v>940</v>
       </c>
       <c r="H22" s="3">
-        <f>MROUND(G21*1.03, 0.5)</f>
+        <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5484,7 +5484,7 @@
         <v>237</v>
       </c>
       <c r="H23" s="3">
-        <f>MROUND(G22*1.03, 0.5)</f>
+        <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5510,7 +5510,7 @@
         <v>140</v>
       </c>
       <c r="H24" s="3">
-        <f>MROUND(G23*1.03, 0.5)</f>
+        <f>MROUND(G24*1.03, 0.5)</f>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5536,7 +5536,7 @@
         <v>140</v>
       </c>
       <c r="H25" s="3">
-        <f>MROUND(G24*1.03, 0.5)</f>
+        <f>MROUND(G25*1.03, 0.5)</f>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5562,7 +5562,7 @@
         <v>209</v>
       </c>
       <c r="H26" s="3">
-        <f>MROUND(G25*1.03, 0.5)</f>
+        <f>MROUND(G26*1.03, 0.5)</f>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5588,7 +5588,7 @@
         <v>119</v>
       </c>
       <c r="H27" s="3">
-        <f>MROUND(G26*1.03, 0.5)</f>
+        <f>MROUND(G27*1.03, 0.5)</f>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5614,7 +5614,7 @@
         <v>119</v>
       </c>
       <c r="H28" s="3">
-        <f>MROUND(G27*1.03, 0.5)</f>
+        <f>MROUND(G28*1.03, 0.5)</f>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5640,7 +5640,7 @@
         <v>158.5</v>
       </c>
       <c r="H29" s="3">
-        <f>MROUND(G28*1.03, 0.5)</f>
+        <f>MROUND(G29*1.03, 0.5)</f>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5666,7 +5666,7 @@
         <v>119</v>
       </c>
       <c r="H30" s="3">
-        <f>MROUND(G29*1.03, 0.5)</f>
+        <f>MROUND(G30*1.03, 0.5)</f>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5692,7 +5692,7 @@
         <v>158.5</v>
       </c>
       <c r="H31" s="3">
-        <f>MROUND(G30*1.03, 0.5)</f>
+        <f>MROUND(G31*1.03, 0.5)</f>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5718,7 +5718,7 @@
         <v>153.5</v>
       </c>
       <c r="H32" s="3">
-        <f>MROUND(G31*1.03, 0.5)</f>
+        <f>MROUND(G32*1.03, 0.5)</f>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5744,7 +5744,7 @@
         <v>177</v>
       </c>
       <c r="H33" s="3">
-        <f>MROUND(G32*1.03, 0.5)</f>
+        <f>MROUND(G33*1.03, 0.5)</f>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>38.5</v>
       </c>
       <c r="H34" s="3">
-        <f>MROUND(G33*1.03, 0.5)</f>
+        <f>MROUND(G34*1.03, 0.5)</f>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5796,7 +5796,7 @@
         <v>177</v>
       </c>
       <c r="H35" s="3">
-        <f>MROUND(G34*1.03, 0.5)</f>
+        <f>MROUND(G35*1.03, 0.5)</f>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5822,7 +5822,7 @@
         <v>38.5</v>
       </c>
       <c r="H36" s="3">
-        <f>MROUND(G35*1.03, 0.5)</f>
+        <f>MROUND(G36*1.03, 0.5)</f>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5848,7 +5848,7 @@
         <v>164</v>
       </c>
       <c r="H37" s="3">
-        <f>MROUND(G36*1.03, 0.5)</f>
+        <f>MROUND(G37*1.03, 0.5)</f>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5874,7 +5874,7 @@
         <v>125</v>
       </c>
       <c r="H38" s="3">
-        <f>MROUND(G37*1.03, 0.5)</f>
+        <f>MROUND(G38*1.03, 0.5)</f>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
         <v>28</v>
       </c>
       <c r="H39" s="3">
-        <f>MROUND(G38*1.03, 0.5)</f>
+        <f>MROUND(G39*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -6310,7 +6310,7 @@
         <v>280</v>
       </c>
       <c r="H15" s="3">
-        <f>MROUND(G14*1.03, 0.5)</f>
+        <f>MROUND(G15*1.03, 0.5)</f>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6336,7 +6336,7 @@
         <v>580</v>
       </c>
       <c r="H16" s="3">
-        <f>MROUND(G15*1.03, 0.5)</f>
+        <f>MROUND(G16*1.03, 0.5)</f>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6362,7 +6362,7 @@
         <v>290</v>
       </c>
       <c r="H17" s="3">
-        <f>MROUND(G16*1.03, 0.5)</f>
+        <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6388,7 +6388,7 @@
         <v>675.5</v>
       </c>
       <c r="H18" s="3">
-        <f>MROUND(G17*1.03, 0.5)</f>
+        <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6414,7 +6414,7 @@
         <v>337.5</v>
       </c>
       <c r="H19" s="3">
-        <f>MROUND(G18*1.03, 0.5)</f>
+        <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6440,7 +6440,7 @@
         <v>275</v>
       </c>
       <c r="H20" s="3">
-        <f>MROUND(G19*1.03, 0.5)</f>
+        <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>245</v>
       </c>
       <c r="H21" s="3">
-        <f>MROUND(G20*1.03, 0.5)</f>
+        <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6492,7 +6492,7 @@
         <v>147</v>
       </c>
       <c r="H22" s="3">
-        <f>MROUND(G21*1.03, 0.5)</f>
+        <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6518,7 +6518,7 @@
         <v>142</v>
       </c>
       <c r="H23" s="3">
-        <f>MROUND(G22*1.03, 0.5)</f>
+        <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6541,10 +6541,10 @@
         <v>29</v>
       </c>
       <c r="G24" s="3">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="H24" s="3">
-        <f>MROUND(G23*1.03, 0.5)</f>
+        <f>MROUND(G24*1.03, 0.5)</f>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6567,10 +6567,10 @@
         <v>29</v>
       </c>
       <c r="G25" s="3">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="H25" s="3">
-        <f>MROUND(G24*1.03, 0.5)</f>
+        <f>MROUND(G25*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -9260,7 +9260,7 @@
         <v>11</v>
       </c>
       <c r="G67" s="3">
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="H67" s="3">
         <f>MROUND(G67*1.03, 0.5)</f>
@@ -9286,7 +9286,7 @@
         <v>12</v>
       </c>
       <c r="G68" s="3">
-        <v>182</v>
+        <v>198.5</v>
       </c>
       <c r="H68" s="3">
         <f>MROUND(G68*1.03, 0.5)</f>
@@ -9783,7 +9783,7 @@
         <v>430</v>
       </c>
       <c r="H87" s="3">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9809,7 +9809,7 @@
         <v>43</v>
       </c>
       <c r="H88" s="3">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9835,7 +9835,7 @@
         <v>350</v>
       </c>
       <c r="H89" s="3">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9861,7 +9861,7 @@
         <v>72</v>
       </c>
       <c r="H90" s="3">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9887,7 +9887,7 @@
         <v>158</v>
       </c>
       <c r="H91" s="3">
-        <f>MROUND(G92*1.03, 0.5)</f>
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9913,7 +9913,7 @@
         <v>216.5</v>
       </c>
       <c r="H92" s="3">
-        <f>MROUND(G93*1.03, 0.5)</f>
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9939,7 +9939,7 @@
         <v>132</v>
       </c>
       <c r="H93" s="3">
-        <f>MROUND(G94*1.03, 0.5)</f>
+        <f>MROUND(G93*1.03, 0.5)</f>
       </c>
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9965,7 +9965,7 @@
         <v>132</v>
       </c>
       <c r="H94" s="3">
-        <f>MROUND(G95*1.03, 0.5)</f>
+        <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9991,7 +9991,7 @@
         <v>375</v>
       </c>
       <c r="H95" s="3">
-        <f>MROUND(G96*1.03, 0.5)</f>
+        <f>MROUND(G95*1.03, 0.5)</f>
       </c>
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10017,7 +10017,7 @@
         <v>150</v>
       </c>
       <c r="H96" s="3">
-        <f>MROUND(G97*1.03, 0.5)</f>
+        <f>MROUND(G96*1.03, 0.5)</f>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10043,7 +10043,7 @@
         <v>46</v>
       </c>
       <c r="H97" s="3">
-        <f>MROUND(G98*1.03, 0.5)</f>
+        <f>MROUND(G97*1.03, 0.5)</f>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10069,7 +10069,7 @@
         <v>350</v>
       </c>
       <c r="H98" s="3">
-        <f>MROUND(G99*1.03, 0.5)</f>
+        <f>MROUND(G98*1.03, 0.5)</f>
       </c>
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10095,7 +10095,7 @@
         <v>178.5</v>
       </c>
       <c r="H99" s="3">
-        <f>MROUND(G100*1.03, 0.5)</f>
+        <f>MROUND(G99*1.03, 0.5)</f>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10121,7 +10121,7 @@
         <v>54</v>
       </c>
       <c r="H100" s="3">
-        <f>MROUND(G101*1.03, 0.5)</f>
+        <f>MROUND(G100*1.03, 0.5)</f>
       </c>
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10147,7 +10147,7 @@
         <v>169</v>
       </c>
       <c r="H101" s="3">
-        <f>MROUND(G102*1.03, 0.5)</f>
+        <f>MROUND(G101*1.03, 0.5)</f>
       </c>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>269.5</v>
       </c>
       <c r="H102" s="3">
-        <f>MROUND(G103*1.03, 0.5)</f>
+        <f>MROUND(G102*1.03, 0.5)</f>
       </c>
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10199,7 +10199,7 @@
         <v>222</v>
       </c>
       <c r="H103" s="3">
-        <f>MROUND(G104*1.03, 0.5)</f>
+        <f>MROUND(G103*1.03, 0.5)</f>
       </c>
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10225,7 +10225,7 @@
         <v>210</v>
       </c>
       <c r="H104" s="3">
-        <f>MROUND(G105*1.03, 0.5)</f>
+        <f>MROUND(G104*1.03, 0.5)</f>
       </c>
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10251,7 +10251,7 @@
         <v>575</v>
       </c>
       <c r="H105" s="3">
-        <f>MROUND(G106*1.03, 0.5)</f>
+        <f>MROUND(G105*1.03, 0.5)</f>
       </c>
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10277,7 +10277,7 @@
         <v>118.5</v>
       </c>
       <c r="H106" s="3">
-        <f>MROUND(G107*1.03, 0.5)</f>
+        <f>MROUND(G106*1.03, 0.5)</f>
       </c>
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10303,7 +10303,7 @@
         <v>510</v>
       </c>
       <c r="H107" s="3">
-        <f>MROUND(G108*1.03, 0.5)</f>
+        <f>MROUND(G107*1.03, 0.5)</f>
       </c>
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10329,7 +10329,7 @@
         <v>255</v>
       </c>
       <c r="H108" s="3">
-        <f>MROUND(G109*1.03, 0.5)</f>
+        <f>MROUND(G108*1.03, 0.5)</f>
       </c>
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10355,7 +10355,7 @@
         <v>255</v>
       </c>
       <c r="H109" s="3">
-        <f>MROUND(G110*1.03, 0.5)</f>
+        <f>MROUND(G109*1.03, 0.5)</f>
       </c>
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>255</v>
       </c>
       <c r="H110" s="3">
-        <f>MROUND(G111*1.03, 0.5)</f>
+        <f>MROUND(G110*1.03, 0.5)</f>
       </c>
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10407,7 +10407,7 @@
         <v>53</v>
       </c>
       <c r="H111" s="3">
-        <f>MROUND(G112*1.03, 0.5)</f>
+        <f>MROUND(G111*1.03, 0.5)</f>
       </c>
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10433,7 +10433,7 @@
         <v>81.5</v>
       </c>
       <c r="H112" s="3">
-        <f>MROUND(G113*1.03, 0.5)</f>
+        <f>MROUND(G112*1.03, 0.5)</f>
       </c>
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10459,7 +10459,7 @@
         <v>70</v>
       </c>
       <c r="H113" s="3">
-        <f>MROUND(G114*1.03, 0.5)</f>
+        <f>MROUND(G113*1.03, 0.5)</f>
       </c>
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10485,7 +10485,7 @@
         <v>150</v>
       </c>
       <c r="H114" s="3">
-        <f>MROUND(G115*1.03, 0.5)</f>
+        <f>MROUND(G114*1.03, 0.5)</f>
       </c>
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10511,7 +10511,7 @@
         <v>252</v>
       </c>
       <c r="H115" s="3">
-        <f>MROUND(G116*1.03, 0.5)</f>
+        <f>MROUND(G115*1.03, 0.5)</f>
       </c>
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10537,7 +10537,7 @@
         <v>450</v>
       </c>
       <c r="H116" s="3">
-        <f>MROUND(G117*1.03, 0.5)</f>
+        <f>MROUND(G116*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -13705,7 +13705,7 @@
         <v>30</v>
       </c>
       <c r="H66" s="3">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13757,7 +13757,7 @@
         <v>64</v>
       </c>
       <c r="H68" s="3">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13783,7 +13783,7 @@
         <v>57</v>
       </c>
       <c r="H69" s="3">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13809,7 +13809,7 @@
         <v>77</v>
       </c>
       <c r="H70" s="3">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13835,7 +13835,7 @@
         <v>77</v>
       </c>
       <c r="H71" s="3">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13861,7 +13861,7 @@
         <v>77</v>
       </c>
       <c r="H72" s="3">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13887,7 +13887,7 @@
         <v>72</v>
       </c>
       <c r="H73" s="3">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13913,7 +13913,7 @@
         <v>144</v>
       </c>
       <c r="H74" s="3">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13939,7 +13939,7 @@
         <v>77</v>
       </c>
       <c r="H75" s="3">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13965,7 +13965,7 @@
         <v>123.5</v>
       </c>
       <c r="H76" s="3">
-        <f>MROUND(G77*1.03, 0.5)</f>
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13991,7 +13991,7 @@
         <v>77</v>
       </c>
       <c r="H77" s="3">
-        <f>MROUND(G78*1.03, 0.5)</f>
+        <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14017,7 +14017,7 @@
         <v>68.5</v>
       </c>
       <c r="H78" s="3">
-        <f>MROUND(G79*1.03, 0.5)</f>
+        <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14043,7 +14043,7 @@
         <v>68.5</v>
       </c>
       <c r="H79" s="3">
-        <f>MROUND(G80*1.03, 0.5)</f>
+        <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14069,7 +14069,7 @@
         <v>177</v>
       </c>
       <c r="H80" s="3">
-        <f>MROUND(G81*1.03, 0.5)</f>
+        <f>MROUND(G80*1.03, 0.5)</f>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14095,7 +14095,7 @@
         <v>75.5</v>
       </c>
       <c r="H81" s="3">
-        <f>MROUND(G82*1.03, 0.5)</f>
+        <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14121,7 +14121,7 @@
         <v>496</v>
       </c>
       <c r="H82" s="3">
-        <f>MROUND(G83*1.03, 0.5)</f>
+        <f>MROUND(G82*1.03, 0.5)</f>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14147,7 +14147,7 @@
         <v>101</v>
       </c>
       <c r="H83" s="3">
-        <f>MROUND(G84*1.03, 0.5)</f>
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14173,7 +14173,7 @@
         <v>424</v>
       </c>
       <c r="H84" s="3">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14199,7 +14199,7 @@
         <v>88</v>
       </c>
       <c r="H85" s="3">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14225,7 +14225,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="3">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14251,7 +14251,7 @@
         <v>79.5</v>
       </c>
       <c r="H87" s="3">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14277,7 +14277,7 @@
         <v>79.5</v>
       </c>
       <c r="H88" s="3">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14303,7 +14303,7 @@
         <v>79.5</v>
       </c>
       <c r="H89" s="3">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14329,7 +14329,7 @@
         <v>79.5</v>
       </c>
       <c r="H90" s="3">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14355,7 +14355,7 @@
         <v>79.5</v>
       </c>
       <c r="H91" s="3">
-        <f>MROUND(G92*1.03, 0.5)</f>
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14381,7 +14381,7 @@
         <v>79.5</v>
       </c>
       <c r="H92" s="3">
-        <f>MROUND(G93*1.03, 0.5)</f>
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14407,7 +14407,7 @@
         <v>79.5</v>
       </c>
       <c r="H93" s="3">
-        <f>MROUND(G94*1.03, 0.5)</f>
+        <f>MROUND(G93*1.03, 0.5)</f>
       </c>
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14433,7 +14433,7 @@
         <v>79.5</v>
       </c>
       <c r="H94" s="3">
-        <f>MROUND(G95*1.03, 0.5)</f>
+        <f>MROUND(G94*1.03, 0.5)</f>
       </c>
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14459,7 +14459,7 @@
         <v>79</v>
       </c>
       <c r="H95" s="3">
-        <f>MROUND(G96*1.03, 0.5)</f>
+        <f>MROUND(G95*1.03, 0.5)</f>
       </c>
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14485,7 +14485,7 @@
         <v>45</v>
       </c>
       <c r="H96" s="3">
-        <f>MROUND(G97*1.03, 0.5)</f>
+        <f>MROUND(G96*1.03, 0.5)</f>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14511,7 +14511,7 @@
         <v>60</v>
       </c>
       <c r="H97" s="3">
-        <f>MROUND(G98*1.03, 0.5)</f>
+        <f>MROUND(G97*1.03, 0.5)</f>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14537,7 +14537,7 @@
         <v>81</v>
       </c>
       <c r="H98" s="3">
-        <f>MROUND(G99*1.03, 0.5)</f>
+        <f>MROUND(G98*1.03, 0.5)</f>
       </c>
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14563,7 +14563,7 @@
         <v>81</v>
       </c>
       <c r="H99" s="3">
-        <f>MROUND(G100*1.03, 0.5)</f>
+        <f>MROUND(G99*1.03, 0.5)</f>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14589,7 +14589,7 @@
         <v>30</v>
       </c>
       <c r="H100" s="3">
-        <f>MROUND(G101*1.03, 0.5)</f>
+        <f>MROUND(G100*1.03, 0.5)</f>
       </c>
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14615,7 +14615,7 @@
         <v>25.5</v>
       </c>
       <c r="H101" s="3">
-        <f>MROUND(G102*1.03, 0.5)</f>
+        <f>MROUND(G101*1.03, 0.5)</f>
       </c>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14641,7 +14641,7 @@
         <v>27</v>
       </c>
       <c r="H102" s="3">
-        <f>MROUND(G103*1.03, 0.5)</f>
+        <f>MROUND(G102*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -15643,7 +15643,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -16900,7 +16900,7 @@
         <v>476</v>
       </c>
       <c r="H48" s="3">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16926,7 +16926,7 @@
         <v>213.5</v>
       </c>
       <c r="H49" s="3">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16952,7 +16952,7 @@
         <v>850.5</v>
       </c>
       <c r="H50" s="3">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16978,7 +16978,7 @@
         <v>378.5</v>
       </c>
       <c r="H51" s="3">
-        <f>MROUND(G49*1.03, 0.5)</f>
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17004,7 +17004,7 @@
         <v>850.5</v>
       </c>
       <c r="H52" s="3">
-        <f>MROUND(G50*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17030,7 +17030,7 @@
         <v>378.5</v>
       </c>
       <c r="H53" s="3">
-        <f>MROUND(G51*1.03, 0.5)</f>
+        <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17056,7 +17056,7 @@
         <v>833.5</v>
       </c>
       <c r="H54" s="3">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17082,7 +17082,7 @@
         <v>1667</v>
       </c>
       <c r="H55" s="3">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17108,7 +17108,7 @@
         <v>371</v>
       </c>
       <c r="H56" s="3">
-        <f>MROUND(G54*1.03, 0.5)</f>
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17134,7 +17134,7 @@
         <v>833.5</v>
       </c>
       <c r="H57" s="3">
-        <f>MROUND(G55*1.03, 0.5)</f>
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17160,7 +17160,7 @@
         <v>1667</v>
       </c>
       <c r="H58" s="3">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17186,7 +17186,7 @@
         <v>371</v>
       </c>
       <c r="H59" s="3">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17212,7 +17212,7 @@
         <v>1950</v>
       </c>
       <c r="H60" s="3">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17238,7 +17238,7 @@
         <v>458</v>
       </c>
       <c r="H61" s="3">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17264,7 +17264,7 @@
         <v>1780</v>
       </c>
       <c r="H62" s="3">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17290,7 +17290,7 @@
         <v>448.5</v>
       </c>
       <c r="H63" s="3">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17316,7 +17316,7 @@
         <v>433.5</v>
       </c>
       <c r="H64" s="3">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17342,7 +17342,7 @@
         <v>1720</v>
       </c>
       <c r="H65" s="3">
-        <f>MROUND(G63*1.03, 0.5)</f>
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17368,7 +17368,7 @@
         <v>1460</v>
       </c>
       <c r="H66" s="3">
-        <f>MROUND(G64*1.03, 0.5)</f>
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17394,7 +17394,7 @@
         <v>368.5</v>
       </c>
       <c r="H67" s="3">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17420,7 +17420,7 @@
         <v>145</v>
       </c>
       <c r="H68" s="3">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17446,7 +17446,7 @@
         <v>75.5</v>
       </c>
       <c r="H69" s="3">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17472,7 +17472,7 @@
         <v>75.5</v>
       </c>
       <c r="H70" s="3">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17498,7 +17498,7 @@
         <v>145</v>
       </c>
       <c r="H71" s="3">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17524,7 +17524,7 @@
         <v>145</v>
       </c>
       <c r="H72" s="3">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17550,7 +17550,7 @@
         <v>75.5</v>
       </c>
       <c r="H73" s="3">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17576,7 +17576,7 @@
         <v>166</v>
       </c>
       <c r="H74" s="3">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17602,7 +17602,7 @@
         <v>83</v>
       </c>
       <c r="H75" s="3">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17628,7 +17628,7 @@
         <v>145</v>
       </c>
       <c r="H76" s="3">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17654,7 +17654,7 @@
         <v>75.5</v>
       </c>
       <c r="H77" s="3">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17680,7 +17680,7 @@
         <v>145</v>
       </c>
       <c r="H78" s="3">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17706,7 +17706,7 @@
         <v>75.5</v>
       </c>
       <c r="H79" s="3">
-        <f>MROUND(G77*1.03, 0.5)</f>
+        <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17732,7 +17732,7 @@
         <v>116.5</v>
       </c>
       <c r="H80" s="3">
-        <f>MROUND(G78*1.03, 0.5)</f>
+        <f>MROUND(G80*1.03, 0.5)</f>
       </c>
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17758,7 +17758,7 @@
         <v>1398</v>
       </c>
       <c r="H81" s="3">
-        <f>MROUND(G79*1.03, 0.5)</f>
+        <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17784,7 +17784,7 @@
         <v>325</v>
       </c>
       <c r="H82" s="3">
-        <f>MROUND(G80*1.03, 0.5)</f>
+        <f>MROUND(G82*1.03, 0.5)</f>
       </c>
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17810,7 +17810,7 @@
         <v>650</v>
       </c>
       <c r="H83" s="3">
-        <f>MROUND(G81*1.03, 0.5)</f>
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17836,10 +17836,10 @@
         <v>580</v>
       </c>
       <c r="H84" s="3">
-        <f>MROUND(G83*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row r="85" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>MROUND(G84*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>134</v>
       </c>
@@ -17862,10 +17862,10 @@
         <v>293.5</v>
       </c>
       <c r="H85" s="3">
-        <f>MROUND(G84*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>MROUND(G85*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>136</v>
       </c>
@@ -17873,10 +17873,10 @@
         <v>137</v>
       </c>
       <c r="C86" s="3">
-        <v>2330</v>
+        <v>4291</v>
       </c>
       <c r="D86" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>10</v>
@@ -17885,10 +17885,10 @@
         <v>29</v>
       </c>
       <c r="G86" s="3">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="H86" s="3">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17899,74 +17899,74 @@
         <v>137</v>
       </c>
       <c r="C87" s="3">
+        <v>2330</v>
+      </c>
+      <c r="D87" s="3">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="3">
+        <v>480</v>
+      </c>
+      <c r="H87" s="3">
+        <f>MROUND(G87*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="88" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" s="3">
         <v>2385</v>
       </c>
-      <c r="D87" s="3">
-        <v>5</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="3">
+      <c r="D88" s="3">
+        <v>5</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="3">
         <v>242</v>
       </c>
-      <c r="H87" s="3">
-        <f>MROUND(G86*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C88" s="3">
-        <v>4540</v>
-      </c>
-      <c r="D88" s="3">
-        <v>10</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="3">
-        <v>650</v>
-      </c>
       <c r="H88" s="3">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C89" s="3">
-        <v>2384</v>
+        <v>4540</v>
       </c>
       <c r="D89" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G89" s="3">
-        <v>187.5</v>
+        <v>650</v>
       </c>
       <c r="H89" s="3">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17977,22 +17977,22 @@
         <v>141</v>
       </c>
       <c r="C90" s="3">
-        <v>3851</v>
+        <v>2384</v>
       </c>
       <c r="D90" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G90" s="3">
-        <v>75</v>
+        <v>187.5</v>
       </c>
       <c r="H90" s="3">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -18003,22 +18003,48 @@
         <v>141</v>
       </c>
       <c r="C91" s="3">
+        <v>3851</v>
+      </c>
+      <c r="D91" s="3">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="3">
+        <v>75</v>
+      </c>
+      <c r="H91" s="3">
+        <f>MROUND(G91*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92" s="3">
         <v>2424</v>
       </c>
-      <c r="D91" s="3">
-        <v>5</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="D92" s="3">
+        <v>5</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="3">
         <v>39.5</v>
       </c>
-      <c r="H91" s="3">
-        <f>MROUND(G89*1.03, 0.5)</f>
+      <c r="H92" s="3">
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -20002,7 +20028,7 @@
         <v>480</v>
       </c>
       <c r="H48" s="3">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20028,7 +20054,7 @@
         <v>24</v>
       </c>
       <c r="H49" s="3">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20054,7 +20080,7 @@
         <v>775</v>
       </c>
       <c r="H50" s="3">
-        <f>MROUND(G49*1.03, 0.5)</f>
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20080,7 +20106,7 @@
         <v>62</v>
       </c>
       <c r="H51" s="3">
-        <f>MROUND(G50*1.03, 0.5)</f>
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20106,7 +20132,7 @@
         <v>250</v>
       </c>
       <c r="H52" s="3">
-        <f>MROUND(G51*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20132,7 +20158,7 @@
         <v>127</v>
       </c>
       <c r="H53" s="3">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20158,7 +20184,7 @@
         <v>150</v>
       </c>
       <c r="H54" s="3">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20184,7 +20210,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3">
-        <f>MROUND(G54*1.03, 0.5)</f>
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20210,7 +20236,7 @@
         <v>33</v>
       </c>
       <c r="H56" s="3">
-        <f>MROUND(G55*1.03, 0.5)</f>
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20236,7 +20262,7 @@
         <v>550</v>
       </c>
       <c r="H57" s="3">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20262,7 +20288,7 @@
         <v>55</v>
       </c>
       <c r="H58" s="3">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20288,7 +20314,7 @@
         <v>380</v>
       </c>
       <c r="H59" s="3">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20314,7 +20340,7 @@
         <v>19</v>
       </c>
       <c r="H60" s="3">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20340,7 +20366,7 @@
         <v>380</v>
       </c>
       <c r="H61" s="3">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20366,7 +20392,7 @@
         <v>190</v>
       </c>
       <c r="H62" s="3">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20392,7 +20418,7 @@
         <v>30</v>
       </c>
       <c r="H63" s="3">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20418,7 +20444,7 @@
         <v>750</v>
       </c>
       <c r="H64" s="3">
-        <f>MROUND(G63*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20444,7 +20470,7 @@
         <v>420</v>
       </c>
       <c r="H65" s="3">
-        <f>MROUND(G64*1.03, 0.5)</f>
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20470,7 +20496,7 @@
         <v>210</v>
       </c>
       <c r="H66" s="3">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20496,7 +20522,7 @@
         <v>21</v>
       </c>
       <c r="H67" s="3">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20522,7 +20548,7 @@
         <v>19</v>
       </c>
       <c r="H68" s="3">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20548,7 +20574,7 @@
         <v>780</v>
       </c>
       <c r="H69" s="3">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20574,7 +20600,7 @@
         <v>390</v>
       </c>
       <c r="H70" s="3">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20600,7 +20626,7 @@
         <v>39</v>
       </c>
       <c r="H71" s="3">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20626,7 +20652,7 @@
         <v>300</v>
       </c>
       <c r="H72" s="3">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20652,7 +20678,7 @@
         <v>600</v>
       </c>
       <c r="H73" s="3">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20678,7 +20704,7 @@
         <v>24</v>
       </c>
       <c r="H74" s="3">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20704,7 +20730,7 @@
         <v>400</v>
       </c>
       <c r="H75" s="3">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20730,7 +20756,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20756,7 +20782,7 @@
         <v>35</v>
       </c>
       <c r="H77" s="3">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -20782,7 +20808,7 @@
         <v>350</v>
       </c>
       <c r="H78" s="3">
-        <f>MROUND(G77*1.03, 0.5)</f>
+        <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -21608,7 +21634,7 @@
         <v>270</v>
       </c>
       <c r="H31" s="3">
-        <f>MROUND(G30*1.03, 0.5)</f>
+        <f>MROUND(G31*1.03, 0.5)</f>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21634,7 +21660,7 @@
         <v>138.5</v>
       </c>
       <c r="H32" s="3">
-        <f>MROUND(G31*1.03, 0.5)</f>
+        <f>MROUND(G32*1.03, 0.5)</f>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21660,7 +21686,7 @@
         <v>100</v>
       </c>
       <c r="H33" s="3">
-        <f>MROUND(G32*1.03, 0.5)</f>
+        <f>MROUND(G33*1.03, 0.5)</f>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21686,7 +21712,7 @@
         <v>52</v>
       </c>
       <c r="H34" s="3">
-        <f>MROUND(G33*1.03, 0.5)</f>
+        <f>MROUND(G34*1.03, 0.5)</f>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21712,7 +21738,7 @@
         <v>168</v>
       </c>
       <c r="H35" s="3">
-        <f>MROUND(G34*1.03, 0.5)</f>
+        <f>MROUND(G35*1.03, 0.5)</f>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21738,7 +21764,7 @@
         <v>86</v>
       </c>
       <c r="H36" s="3">
-        <f>MROUND(G35*1.03, 0.5)</f>
+        <f>MROUND(G36*1.03, 0.5)</f>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21764,7 +21790,7 @@
         <v>160</v>
       </c>
       <c r="H37" s="3">
-        <f>MROUND(G36*1.03, 0.5)</f>
+        <f>MROUND(G37*1.03, 0.5)</f>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21790,7 +21816,7 @@
         <v>35</v>
       </c>
       <c r="H38" s="3">
-        <f>MROUND(G37*1.03, 0.5)</f>
+        <f>MROUND(G38*1.03, 0.5)</f>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21816,7 +21842,7 @@
         <v>104.5</v>
       </c>
       <c r="H39" s="3">
-        <f>MROUND(G38*1.03, 0.5)</f>
+        <f>MROUND(G39*1.03, 0.5)</f>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21842,7 +21868,7 @@
         <v>205</v>
       </c>
       <c r="H40" s="3">
-        <f>MROUND(G39*1.03, 0.5)</f>
+        <f>MROUND(G40*1.03, 0.5)</f>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21868,7 +21894,7 @@
         <v>66</v>
       </c>
       <c r="H41" s="3">
-        <f>MROUND(G40*1.03, 0.5)</f>
+        <f>MROUND(G41*1.03, 0.5)</f>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21894,7 +21920,7 @@
         <v>128</v>
       </c>
       <c r="H42" s="3">
-        <f>MROUND(G41*1.03, 0.5)</f>
+        <f>MROUND(G42*1.03, 0.5)</f>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21920,7 +21946,7 @@
         <v>105</v>
       </c>
       <c r="H43" s="3">
-        <f>MROUND(G42*1.03, 0.5)</f>
+        <f>MROUND(G43*1.03, 0.5)</f>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21946,7 +21972,7 @@
         <v>90</v>
       </c>
       <c r="H44" s="3">
-        <f>MROUND(G43*1.03, 0.5)</f>
+        <f>MROUND(G44*1.03, 0.5)</f>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21972,7 +21998,7 @@
         <v>83</v>
       </c>
       <c r="H45" s="3">
-        <f>MROUND(G44*1.03, 0.5)</f>
+        <f>MROUND(G45*1.03, 0.5)</f>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -21998,7 +22024,7 @@
         <v>18.5</v>
       </c>
       <c r="H46" s="3">
-        <f>MROUND(G45*1.03, 0.5)</f>
+        <f>MROUND(G46*1.03, 0.5)</f>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22024,7 +22050,7 @@
         <v>67</v>
       </c>
       <c r="H47" s="3">
-        <f>MROUND(G46*1.03, 0.5)</f>
+        <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22050,7 +22076,7 @@
         <v>11.5</v>
       </c>
       <c r="H48" s="3">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22076,7 +22102,7 @@
         <v>96</v>
       </c>
       <c r="H49" s="3">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22102,7 +22128,7 @@
         <v>22.5</v>
       </c>
       <c r="H50" s="3">
-        <f>MROUND(G49*1.03, 0.5)</f>
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22128,7 +22154,7 @@
         <v>170</v>
       </c>
       <c r="H51" s="3">
-        <f>MROUND(G50*1.03, 0.5)</f>
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22154,7 +22180,7 @@
         <v>88</v>
       </c>
       <c r="H52" s="3">
-        <f>MROUND(G51*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22180,7 +22206,7 @@
         <v>168</v>
       </c>
       <c r="H53" s="3">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22206,7 +22232,7 @@
         <v>192</v>
       </c>
       <c r="H54" s="3">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22232,7 +22258,7 @@
         <v>48</v>
       </c>
       <c r="H55" s="3">
-        <f>MROUND(G54*1.03, 0.5)</f>
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22258,7 +22284,7 @@
         <v>300</v>
       </c>
       <c r="H56" s="3">
-        <f>MROUND(G55*1.03, 0.5)</f>
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22284,7 +22310,7 @@
         <v>324</v>
       </c>
       <c r="H57" s="3">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22310,7 +22336,7 @@
         <v>77</v>
       </c>
       <c r="H58" s="3">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22336,7 +22362,7 @@
         <v>29</v>
       </c>
       <c r="H59" s="3">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22362,7 +22388,7 @@
         <v>130</v>
       </c>
       <c r="H60" s="3">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22388,7 +22414,7 @@
         <v>117</v>
       </c>
       <c r="H61" s="3">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22414,7 +22440,7 @@
         <v>119</v>
       </c>
       <c r="H62" s="3">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22440,7 +22466,7 @@
         <v>26</v>
       </c>
       <c r="H63" s="3">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22466,7 +22492,7 @@
         <v>180</v>
       </c>
       <c r="H64" s="3">
-        <f>MROUND(G63*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22492,7 +22518,7 @@
         <v>38</v>
       </c>
       <c r="H65" s="3">
-        <f>MROUND(G64*1.03, 0.5)</f>
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22518,7 +22544,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="3">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22544,7 +22570,7 @@
         <v>190</v>
       </c>
       <c r="H67" s="3">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22570,7 +22596,7 @@
         <v>40</v>
       </c>
       <c r="H68" s="3">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22596,7 +22622,7 @@
         <v>240</v>
       </c>
       <c r="H69" s="3">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22622,7 +22648,7 @@
         <v>123.5</v>
       </c>
       <c r="H70" s="3">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22648,7 +22674,7 @@
         <v>360</v>
       </c>
       <c r="H71" s="3">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -22674,7 +22700,7 @@
         <v>183.5</v>
       </c>
       <c r="H72" s="3">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -23916,7 +23942,7 @@
         <v>115</v>
       </c>
       <c r="H47" s="3">
-        <f>MROUND(G46*1.03, 0.5)</f>
+        <f>MROUND(G47*1.03, 0.5)</f>
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -23942,7 +23968,7 @@
         <v>26</v>
       </c>
       <c r="H48" s="3">
-        <f>MROUND(G47*1.03, 0.5)</f>
+        <f>MROUND(G48*1.03, 0.5)</f>
       </c>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -23968,7 +23994,7 @@
         <v>170</v>
       </c>
       <c r="H49" s="3">
-        <f>MROUND(G48*1.03, 0.5)</f>
+        <f>MROUND(G49*1.03, 0.5)</f>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -23994,7 +24020,7 @@
         <v>31.5</v>
       </c>
       <c r="H50" s="3">
-        <f>MROUND(G49*1.03, 0.5)</f>
+        <f>MROUND(G50*1.03, 0.5)</f>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24020,7 +24046,7 @@
         <v>320</v>
       </c>
       <c r="H51" s="3">
-        <f>MROUND(G50*1.03, 0.5)</f>
+        <f>MROUND(G51*1.03, 0.5)</f>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24046,7 +24072,7 @@
         <v>55.5</v>
       </c>
       <c r="H52" s="3">
-        <f>MROUND(G51*1.03, 0.5)</f>
+        <f>MROUND(G52*1.03, 0.5)</f>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24072,7 +24098,7 @@
         <v>362.5</v>
       </c>
       <c r="H53" s="3">
-        <f>MROUND(G52*1.03, 0.5)</f>
+        <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24098,7 +24124,7 @@
         <v>74.5</v>
       </c>
       <c r="H54" s="3">
-        <f>MROUND(G53*1.03, 0.5)</f>
+        <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24124,7 +24150,7 @@
         <v>255</v>
       </c>
       <c r="H55" s="3">
-        <f>MROUND(G54*1.03, 0.5)</f>
+        <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24150,7 +24176,7 @@
         <v>212.5</v>
       </c>
       <c r="H56" s="3">
-        <f>MROUND(G55*1.03, 0.5)</f>
+        <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24176,7 +24202,7 @@
         <v>44.5</v>
       </c>
       <c r="H57" s="3">
-        <f>MROUND(G56*1.03, 0.5)</f>
+        <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24202,7 +24228,7 @@
         <v>350</v>
       </c>
       <c r="H58" s="3">
-        <f>MROUND(G57*1.03, 0.5)</f>
+        <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24228,7 +24254,7 @@
         <v>175</v>
       </c>
       <c r="H59" s="3">
-        <f>MROUND(G58*1.03, 0.5)</f>
+        <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24254,7 +24280,7 @@
         <v>32</v>
       </c>
       <c r="H60" s="3">
-        <f>MROUND(G59*1.03, 0.5)</f>
+        <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24280,7 +24306,7 @@
         <v>275</v>
       </c>
       <c r="H61" s="3">
-        <f>MROUND(G60*1.03, 0.5)</f>
+        <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24306,7 +24332,7 @@
         <v>57</v>
       </c>
       <c r="H62" s="3">
-        <f>MROUND(G61*1.03, 0.5)</f>
+        <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24332,7 +24358,7 @@
         <v>280</v>
       </c>
       <c r="H63" s="3">
-        <f>MROUND(G62*1.03, 0.5)</f>
+        <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24358,7 +24384,7 @@
         <v>48.5</v>
       </c>
       <c r="H64" s="3">
-        <f>MROUND(G63*1.03, 0.5)</f>
+        <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24384,7 +24410,7 @@
         <v>375</v>
       </c>
       <c r="H65" s="3">
-        <f>MROUND(G64*1.03, 0.5)</f>
+        <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24410,7 +24436,7 @@
         <v>64.5</v>
       </c>
       <c r="H66" s="3">
-        <f>MROUND(G65*1.03, 0.5)</f>
+        <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24436,7 +24462,7 @@
         <v>330</v>
       </c>
       <c r="H67" s="3">
-        <f>MROUND(G66*1.03, 0.5)</f>
+        <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24462,7 +24488,7 @@
         <v>57</v>
       </c>
       <c r="H68" s="3">
-        <f>MROUND(G67*1.03, 0.5)</f>
+        <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24488,7 +24514,7 @@
         <v>237.5</v>
       </c>
       <c r="H69" s="3">
-        <f>MROUND(G68*1.03, 0.5)</f>
+        <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24514,7 +24540,7 @@
         <v>50.5</v>
       </c>
       <c r="H70" s="3">
-        <f>MROUND(G69*1.03, 0.5)</f>
+        <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24540,7 +24566,7 @@
         <v>312.5</v>
       </c>
       <c r="H71" s="3">
-        <f>MROUND(G70*1.03, 0.5)</f>
+        <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24566,7 +24592,7 @@
         <v>64.5</v>
       </c>
       <c r="H72" s="3">
-        <f>MROUND(G71*1.03, 0.5)</f>
+        <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24592,7 +24618,7 @@
         <v>262.5</v>
       </c>
       <c r="H73" s="3">
-        <f>MROUND(G72*1.03, 0.5)</f>
+        <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24618,7 +24644,7 @@
         <v>55.5</v>
       </c>
       <c r="H74" s="3">
-        <f>MROUND(G73*1.03, 0.5)</f>
+        <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24644,7 +24670,7 @@
         <v>162.5</v>
       </c>
       <c r="H75" s="3">
-        <f>MROUND(G74*1.03, 0.5)</f>
+        <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24670,7 +24696,7 @@
         <v>35.5</v>
       </c>
       <c r="H76" s="3">
-        <f>MROUND(G75*1.03, 0.5)</f>
+        <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24696,7 +24722,7 @@
         <v>179</v>
       </c>
       <c r="H77" s="3">
-        <f>MROUND(G76*1.03, 0.5)</f>
+        <f>MROUND(G77*1.03, 0.5)</f>
       </c>
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24722,7 +24748,7 @@
         <v>358</v>
       </c>
       <c r="H78" s="3">
-        <f>MROUND(G77*1.03, 0.5)</f>
+        <f>MROUND(G78*1.03, 0.5)</f>
       </c>
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24748,7 +24774,7 @@
         <v>42.5</v>
       </c>
       <c r="H79" s="3">
-        <f>MROUND(G78*1.03, 0.5)</f>
+        <f>MROUND(G79*1.03, 0.5)</f>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24774,7 +24800,7 @@
         <v>544</v>
       </c>
       <c r="H80" s="3">
-        <f>MROUND(G79*1.03, 0.5)</f>
+        <f>MROUND(G80*1.03, 0.5)</f>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24800,7 +24826,7 @@
         <v>272</v>
       </c>
       <c r="H81" s="3">
-        <f>MROUND(G80*1.03, 0.5)</f>
+        <f>MROUND(G81*1.03, 0.5)</f>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24826,7 +24852,7 @@
         <v>63</v>
       </c>
       <c r="H82" s="3">
-        <f>MROUND(G81*1.03, 0.5)</f>
+        <f>MROUND(G82*1.03, 0.5)</f>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24852,7 +24878,7 @@
         <v>52</v>
       </c>
       <c r="H83" s="3">
-        <f>MROUND(G82*1.03, 0.5)</f>
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24878,7 +24904,7 @@
         <v>182</v>
       </c>
       <c r="H84" s="3">
-        <f>MROUND(G83*1.03, 0.5)</f>
+        <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24904,7 +24930,7 @@
         <v>350</v>
       </c>
       <c r="H85" s="3">
-        <f>MROUND(G84*1.03, 0.5)</f>
+        <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24930,7 +24956,7 @@
         <v>700</v>
       </c>
       <c r="H86" s="3">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24956,7 +24982,7 @@
         <v>106</v>
       </c>
       <c r="H87" s="3">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -24982,7 +25008,7 @@
         <v>87</v>
       </c>
       <c r="H88" s="3">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25008,7 +25034,7 @@
         <v>85</v>
       </c>
       <c r="H89" s="3">
-        <f>MROUND(G88*1.03, 0.5)</f>
+        <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25034,7 +25060,7 @@
         <v>21</v>
       </c>
       <c r="H90" s="3">
-        <f>MROUND(G89*1.03, 0.5)</f>
+        <f>MROUND(G90*1.03, 0.5)</f>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25060,7 +25086,7 @@
         <v>110</v>
       </c>
       <c r="H91" s="3">
-        <f>MROUND(G90*1.03, 0.5)</f>
+        <f>MROUND(G91*1.03, 0.5)</f>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25086,7 +25112,7 @@
         <v>25</v>
       </c>
       <c r="H92" s="3">
-        <f>MROUND(G91*1.03, 0.5)</f>
+        <f>MROUND(G92*1.03, 0.5)</f>
       </c>
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25727,7 +25753,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="3">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="H22" s="3">
         <f>MROUND(G22*1.03, 0.5)</f>
@@ -28018,7 +28044,7 @@
         <v>170</v>
       </c>
       <c r="H110" s="3">
-        <f>MROUND(G108*1.03, 0.5)</f>
+        <f>MROUND(G110*1.03, 0.5)</f>
       </c>
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28044,7 +28070,7 @@
         <v>88</v>
       </c>
       <c r="H111" s="3">
-        <f>MROUND(G108*1.03, 0.5)</f>
+        <f>MROUND(G111*1.03, 0.5)</f>
       </c>
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28070,7 +28096,7 @@
         <v>1175</v>
       </c>
       <c r="H112" s="3">
-        <f>MROUND(G110*1.03, 0.5)</f>
+        <f>MROUND(G112*1.03, 0.5)</f>
       </c>
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28096,7 +28122,7 @@
         <v>235</v>
       </c>
       <c r="H113" s="3">
-        <f>MROUND(G111*1.03, 0.5)</f>
+        <f>MROUND(G113*1.03, 0.5)</f>
       </c>
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28122,7 +28148,7 @@
         <v>73.5</v>
       </c>
       <c r="H114" s="3">
-        <f>MROUND(G112*1.03, 0.5)</f>
+        <f>MROUND(G114*1.03, 0.5)</f>
       </c>
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28148,7 +28174,7 @@
         <v>200</v>
       </c>
       <c r="H115" s="3">
-        <f>MROUND(G113*1.03, 0.5)</f>
+        <f>MROUND(G115*1.03, 0.5)</f>
       </c>
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28174,7 +28200,7 @@
         <v>20</v>
       </c>
       <c r="H116" s="3">
-        <f>MROUND(G114*1.03, 0.5)</f>
+        <f>MROUND(G116*1.03, 0.5)</f>
       </c>
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28200,7 +28226,7 @@
         <v>90</v>
       </c>
       <c r="H117" s="3">
-        <f>MROUND(G115*1.03, 0.5)</f>
+        <f>MROUND(G117*1.03, 0.5)</f>
       </c>
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -28226,7 +28252,7 @@
         <v>84</v>
       </c>
       <c r="H118" s="3">
-        <f>MROUND(G116*1.03, 0.5)</f>
+        <f>MROUND(G118*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="1131">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -1698,6 +1698,9 @@
   </si>
   <si>
     <t>tempero-pimenta-calabresa-po</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPERO PIMENTA CALABRESA EM PÓ </t>
   </si>
   <si>
     <t>pimenta-do-reino-em-gros</t>
@@ -4917,10 +4920,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C2" s="3">
         <v>8</v>
@@ -4943,10 +4946,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C3" s="3">
         <v>2391</v>
@@ -4969,10 +4972,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C4" s="3">
         <v>2529</v>
@@ -5047,10 +5050,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C7" s="3">
         <v>3649</v>
@@ -5073,10 +5076,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C8" s="3">
         <v>3650</v>
@@ -5099,10 +5102,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C9" s="3">
         <v>3386</v>
@@ -5125,10 +5128,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C10" s="3">
         <v>3385</v>
@@ -5151,10 +5154,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="3">
         <v>460</v>
@@ -5177,10 +5180,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C12" s="3">
         <v>2473</v>
@@ -5203,10 +5206,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C13" s="3">
         <v>128</v>
@@ -5229,10 +5232,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C14" s="3">
         <v>2474</v>
@@ -5255,10 +5258,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C15" s="3">
         <v>3085</v>
@@ -5281,10 +5284,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C16" s="3">
         <v>3086</v>
@@ -5307,10 +5310,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C17" s="3">
         <v>4558</v>
@@ -5319,7 +5322,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>273</v>
@@ -5333,10 +5336,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C18" s="3">
         <v>4697</v>
@@ -5359,10 +5362,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C19" s="3">
         <v>4048</v>
@@ -5371,7 +5374,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>273</v>
@@ -5385,10 +5388,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C20" s="3">
         <v>2519</v>
@@ -5411,10 +5414,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C21" s="3">
         <v>2525</v>
@@ -5437,10 +5440,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C22" s="3">
         <v>3433</v>
@@ -5463,10 +5466,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C23" s="3">
         <v>3394</v>
@@ -5489,10 +5492,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C24" s="3">
         <v>47</v>
@@ -5515,10 +5518,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C25" s="3">
         <v>46</v>
@@ -5541,10 +5544,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C26" s="3">
         <v>3100</v>
@@ -5567,10 +5570,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C27" s="3">
         <v>3746</v>
@@ -5593,10 +5596,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C28" s="3">
         <v>3639</v>
@@ -5619,10 +5622,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C29" s="3">
         <v>2415</v>
@@ -5645,10 +5648,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C30" s="3">
         <v>3747</v>
@@ -5671,10 +5674,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C31" s="3">
         <v>3640</v>
@@ -5697,10 +5700,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C32" s="3">
         <v>2416</v>
@@ -5723,10 +5726,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C33" s="3">
         <v>50</v>
@@ -5749,10 +5752,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C34" s="3">
         <v>2533</v>
@@ -5775,10 +5778,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C35" s="3">
         <v>52</v>
@@ -5801,10 +5804,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C36" s="3">
         <v>2470</v>
@@ -5827,10 +5830,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C37" s="3">
         <v>4671</v>
@@ -5853,10 +5856,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C38" s="3">
         <v>53</v>
@@ -5879,10 +5882,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C39" s="3">
         <v>2435</v>
@@ -5911,7 +5914,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5951,10 +5954,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C2" s="3">
         <v>3051</v>
@@ -5977,10 +5980,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C3" s="3">
         <v>2675</v>
@@ -6003,10 +6006,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C4" s="3">
         <v>2791</v>
@@ -6029,10 +6032,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C5" s="3">
         <v>3090</v>
@@ -6055,10 +6058,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C6" s="3">
         <v>2414</v>
@@ -6081,10 +6084,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C7" s="3">
         <v>2418</v>
@@ -6107,10 +6110,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C8" s="3">
         <v>2272</v>
@@ -6133,10 +6136,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C9" s="3">
         <v>3651</v>
@@ -6159,10 +6162,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C10" s="3">
         <v>4206</v>
@@ -6185,10 +6188,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C11" s="3">
         <v>3652</v>
@@ -6211,10 +6214,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C12" s="3">
         <v>4136</v>
@@ -6237,10 +6240,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C13" s="3">
         <v>4585</v>
@@ -6249,7 +6252,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>29</v>
@@ -6263,10 +6266,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C14" s="3">
         <v>4584</v>
@@ -6289,10 +6292,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C15" s="3">
         <v>4700</v>
@@ -6315,10 +6318,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C16" s="3">
         <v>2756</v>
@@ -6327,7 +6330,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>12</v>
@@ -6341,10 +6344,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C17" s="3">
         <v>2757</v>
@@ -6367,10 +6370,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C18" s="3">
         <v>4491</v>
@@ -6379,7 +6382,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>29</v>
@@ -6393,10 +6396,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C19" s="3">
         <v>4492</v>
@@ -6445,10 +6448,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C21" s="3">
         <v>4674</v>
@@ -6471,10 +6474,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C22" s="3">
         <v>2362</v>
@@ -6497,10 +6500,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C23" s="3">
         <v>4403</v>
@@ -6521,18 +6524,18 @@
         <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C24" s="3">
         <v>2406</v>
       </c>
       <c r="D24" s="3">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>10</v>
@@ -6544,18 +6547,18 @@
         <v>400</v>
       </c>
       <c r="H24" s="3">
-        <f>MROUND(G24*1.03, 0.5)</f>
+        <f>MROUND(G25*1.03, 0.5)</f>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>647</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>31</v>
+        <v>648</v>
       </c>
       <c r="C25" s="3">
-        <v>2229</v>
+        <v>3111</v>
       </c>
       <c r="D25" s="3">
         <v>10</v>
@@ -6567,10 +6570,36 @@
         <v>29</v>
       </c>
       <c r="G25" s="3">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="H25" s="3">
         <f>MROUND(G25*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2229</v>
+      </c>
+      <c r="D26" s="3">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="3">
+        <v>130</v>
+      </c>
+      <c r="H26" s="3">
+        <f>MROUND(G26*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -6621,10 +6650,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C2" s="3">
         <v>189</v>
@@ -6647,10 +6676,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C3" s="3">
         <v>9</v>
@@ -6673,10 +6702,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C4" s="3">
         <v>2553</v>
@@ -6699,10 +6728,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C5" s="3">
         <v>521</v>
@@ -6725,10 +6754,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C6" s="3">
         <v>99</v>
@@ -6751,10 +6780,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C7" s="3">
         <v>2613</v>
@@ -6777,10 +6806,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C8" s="3">
         <v>3365</v>
@@ -6803,10 +6832,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C9" s="3">
         <v>2556</v>
@@ -6829,10 +6858,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C10" s="3">
         <v>2555</v>
@@ -6855,10 +6884,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C11" s="3">
         <v>4045</v>
@@ -6881,10 +6910,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C12" s="3">
         <v>3669</v>
@@ -6907,10 +6936,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C13" s="3">
         <v>38</v>
@@ -6933,10 +6962,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C14" s="3">
         <v>2479</v>
@@ -6959,10 +6988,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C15" s="3">
         <v>105</v>
@@ -6985,10 +7014,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C16" s="3">
         <v>212</v>
@@ -7011,10 +7040,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C17" s="3">
         <v>2848</v>
@@ -7037,10 +7066,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C18" s="3">
         <v>2851</v>
@@ -7063,10 +7092,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C19" s="3">
         <v>4202</v>
@@ -7089,10 +7118,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C20" s="3">
         <v>4201</v>
@@ -7101,7 +7130,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>29</v>
@@ -7115,10 +7144,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C21" s="3">
         <v>653</v>
@@ -7141,10 +7170,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C22" s="3">
         <v>2484</v>
@@ -7167,10 +7196,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C23" s="3">
         <v>3417</v>
@@ -7193,10 +7222,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C24" s="3">
         <v>2716</v>
@@ -7219,10 +7248,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C25" s="3">
         <v>2478</v>
@@ -7245,10 +7274,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C26" s="3">
         <v>2606</v>
@@ -7271,10 +7300,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C27" s="3">
         <v>2338</v>
@@ -7297,10 +7326,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C28" s="3">
         <v>2425</v>
@@ -7323,10 +7352,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C29" s="3">
         <v>2579</v>
@@ -7349,10 +7378,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C30" s="3">
         <v>2243</v>
@@ -7479,10 +7508,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C35" s="3">
         <v>3754</v>
@@ -7552,10 +7581,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C2" s="3">
         <v>4336</v>
@@ -7578,10 +7607,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C3" s="3">
         <v>2618</v>
@@ -7604,10 +7633,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C4" s="3">
         <v>2398</v>
@@ -7630,10 +7659,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C5" s="3">
         <v>2297</v>
@@ -7656,10 +7685,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C6" s="3">
         <v>3653</v>
@@ -7682,10 +7711,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C7" s="3">
         <v>2339</v>
@@ -7708,10 +7737,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C8" s="3">
         <v>2223</v>
@@ -7734,10 +7763,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C9" s="3">
         <v>3707</v>
@@ -7746,7 +7775,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>273</v>
@@ -7760,10 +7789,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C10" s="3">
         <v>4090</v>
@@ -7786,10 +7815,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C11" s="3">
         <v>4279</v>
@@ -7838,10 +7867,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C13" s="3">
         <v>3540</v>
@@ -7864,10 +7893,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C14" s="3">
         <v>3541</v>
@@ -7968,10 +7997,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C18" s="3">
         <v>4639</v>
@@ -7994,10 +8023,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C19" s="3">
         <v>2336</v>
@@ -8020,10 +8049,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C20" s="3">
         <v>2421</v>
@@ -8046,10 +8075,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C21" s="3">
         <v>2568</v>
@@ -8072,10 +8101,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C22" s="3">
         <v>3009</v>
@@ -8098,10 +8127,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C23" s="3">
         <v>2778</v>
@@ -8124,10 +8153,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C24" s="3">
         <v>3106</v>
@@ -8150,10 +8179,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C25" s="3">
         <v>3489</v>
@@ -8176,10 +8205,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C26" s="3">
         <v>2783</v>
@@ -8202,10 +8231,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C27" s="3">
         <v>3755</v>
@@ -8228,10 +8257,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C28" s="3">
         <v>3487</v>
@@ -8254,10 +8283,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C29" s="3">
         <v>3486</v>
@@ -8280,10 +8309,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C30" s="3">
         <v>4488</v>
@@ -8306,10 +8335,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C31" s="3">
         <v>4333</v>
@@ -8332,10 +8361,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C32" s="3">
         <v>4650</v>
@@ -8358,10 +8387,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C33" s="3">
         <v>4388</v>
@@ -8384,10 +8413,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C34" s="3">
         <v>4389</v>
@@ -8410,10 +8439,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C35" s="3">
         <v>3488</v>
@@ -8436,10 +8465,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C36" s="3">
         <v>3400</v>
@@ -8462,10 +8491,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C37" s="3">
         <v>2257</v>
@@ -8488,10 +8517,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C38" s="3">
         <v>565</v>
@@ -8514,10 +8543,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C39" s="3">
         <v>4474</v>
@@ -8540,10 +8569,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C40" s="3">
         <v>4473</v>
@@ -8566,10 +8595,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C41" s="3">
         <v>2658</v>
@@ -8592,10 +8621,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C42" s="3">
         <v>2657</v>
@@ -8618,10 +8647,10 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C43" s="3">
         <v>4640</v>
@@ -8644,10 +8673,10 @@
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C44" s="3">
         <v>3537</v>
@@ -8670,10 +8699,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C45" s="3">
         <v>2732</v>
@@ -8696,10 +8725,10 @@
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C46" s="3">
         <v>2733</v>
@@ -8722,10 +8751,10 @@
     </row>
     <row r="47" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C47" s="3">
         <v>2584</v>
@@ -8748,10 +8777,10 @@
     </row>
     <row r="48" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C48" s="3">
         <v>2677</v>
@@ -8774,10 +8803,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C49" s="3">
         <v>2495</v>
@@ -8800,10 +8829,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C50" s="3">
         <v>2678</v>
@@ -8826,10 +8855,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C51" s="3">
         <v>4498</v>
@@ -8852,10 +8881,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C52" s="3">
         <v>4253</v>
@@ -8878,10 +8907,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C53" s="3">
         <v>4500</v>
@@ -8904,10 +8933,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C54" s="3">
         <v>4249</v>
@@ -8930,10 +8959,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C55" s="3">
         <v>3724</v>
@@ -8956,10 +8985,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C56" s="3">
         <v>3736</v>
@@ -8982,10 +9011,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C57" s="3">
         <v>4499</v>
@@ -9008,10 +9037,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C58" s="3">
         <v>3536</v>
@@ -9034,10 +9063,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C59" s="3">
         <v>2494</v>
@@ -9060,10 +9089,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C60" s="3">
         <v>2679</v>
@@ -9086,10 +9115,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C61" s="3">
         <v>4497</v>
@@ -9112,10 +9141,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C62" s="3">
         <v>2493</v>
@@ -9138,10 +9167,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C63" s="3">
         <v>3535</v>
@@ -9164,10 +9193,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C64" s="3">
         <v>2498</v>
@@ -9190,10 +9219,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C65" s="3">
         <v>2806</v>
@@ -9216,10 +9245,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C66" s="3">
         <v>2807</v>
@@ -9242,10 +9271,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C67" s="3">
         <v>4556</v>
@@ -9268,10 +9297,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C68" s="3">
         <v>4557</v>
@@ -9294,10 +9323,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C69" s="3">
         <v>4018</v>
@@ -9320,10 +9349,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C70" s="3">
         <v>2652</v>
@@ -9346,10 +9375,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C71" s="3">
         <v>4049</v>
@@ -9372,10 +9401,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C72" s="3">
         <v>3737</v>
@@ -9398,10 +9427,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C73" s="3">
         <v>4301</v>
@@ -9424,10 +9453,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C74" s="3">
         <v>4334</v>
@@ -9450,10 +9479,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C75" s="3">
         <v>195</v>
@@ -9476,10 +9505,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C76" s="3">
         <v>54</v>
@@ -9502,10 +9531,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C77" s="3">
         <v>63</v>
@@ -9528,10 +9557,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C78" s="3">
         <v>2483</v>
@@ -9554,10 +9583,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C79" s="3">
         <v>2974</v>
@@ -9580,10 +9609,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C80" s="3">
         <v>2831</v>
@@ -9606,10 +9635,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C81" s="3">
         <v>4137</v>
@@ -9632,10 +9661,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C82" s="3">
         <v>4380</v>
@@ -9658,10 +9687,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C83" s="3">
         <v>4566</v>
@@ -9684,10 +9713,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C84" s="3">
         <v>4567</v>
@@ -9710,10 +9739,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C85" s="3">
         <v>4204</v>
@@ -9736,10 +9765,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C86" s="3">
         <v>4205</v>
@@ -9762,10 +9791,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C87" s="3">
         <v>4378</v>
@@ -9788,10 +9817,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C88" s="3">
         <v>4379</v>
@@ -9814,10 +9843,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C89" s="3">
         <v>3524</v>
@@ -9829,7 +9858,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G89" s="3">
         <v>350</v>
@@ -9840,10 +9869,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C90" s="3">
         <v>3523</v>
@@ -9855,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G90" s="3">
         <v>72</v>
@@ -9866,10 +9895,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C91" s="3">
         <v>3521</v>
@@ -9878,7 +9907,7 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -9892,10 +9921,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C92" s="3">
         <v>3522</v>
@@ -9904,7 +9933,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>29</v>
@@ -9918,10 +9947,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C93" s="3">
         <v>64</v>
@@ -9944,10 +9973,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C94" s="3">
         <v>90</v>
@@ -9970,10 +9999,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C95" s="3">
         <v>3637</v>
@@ -9996,10 +10025,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C96" s="3">
         <v>2805</v>
@@ -10022,10 +10051,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C97" s="3">
         <v>2427</v>
@@ -10048,10 +10077,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C98" s="3">
         <v>3437</v>
@@ -10074,10 +10103,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C99" s="3">
         <v>3396</v>
@@ -10100,10 +10129,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C100" s="3">
         <v>3395</v>
@@ -10112,7 +10141,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>29</v>
@@ -10126,10 +10155,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C101" s="3">
         <v>3490</v>
@@ -10138,7 +10167,7 @@
         <v>12</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>29</v>
@@ -10152,10 +10181,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C102" s="3">
         <v>458</v>
@@ -10164,7 +10193,7 @@
         <v>12</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>29</v>
@@ -10178,10 +10207,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C103" s="3">
         <v>2641</v>
@@ -10190,7 +10219,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>29</v>
@@ -10204,10 +10233,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C104" s="3">
         <v>4293</v>
@@ -10216,7 +10245,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>29</v>
@@ -10230,10 +10259,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C105" s="3">
         <v>2396</v>
@@ -10256,10 +10285,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C106" s="3">
         <v>2426</v>
@@ -10282,10 +10311,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C107" s="3">
         <v>4335</v>
@@ -10308,10 +10337,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C108" s="3">
         <v>4477</v>
@@ -10334,10 +10363,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C109" s="3">
         <v>4479</v>
@@ -10360,10 +10389,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C110" s="3">
         <v>4478</v>
@@ -10386,10 +10415,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C111" s="3">
         <v>2646</v>
@@ -10398,7 +10427,7 @@
         <v>12</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>273</v>
@@ -10412,10 +10441,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C112" s="3">
         <v>2645</v>
@@ -10424,7 +10453,7 @@
         <v>6</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>273</v>
@@ -10438,10 +10467,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C113" s="3">
         <v>2638</v>
@@ -10450,7 +10479,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>273</v>
@@ -10464,10 +10493,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C114" s="3">
         <v>4294</v>
@@ -10476,7 +10505,7 @@
         <v>18</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>273</v>
@@ -10490,10 +10519,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C115" s="3">
         <v>4314</v>
@@ -10502,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>29</v>
@@ -10516,10 +10545,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C116" s="3">
         <v>4315</v>
@@ -10528,7 +10557,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>29</v>
@@ -10588,10 +10617,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C2" s="3">
         <v>3402</v>
@@ -10600,7 +10629,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10614,10 +10643,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C3" s="3">
         <v>3401</v>
@@ -10626,7 +10655,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10640,10 +10669,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C4" s="3">
         <v>3403</v>
@@ -10652,7 +10681,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10666,10 +10695,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C5" s="3">
         <v>4032</v>
@@ -10678,7 +10707,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -10692,10 +10721,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C6" s="3">
         <v>4460</v>
@@ -10704,7 +10733,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>273</v>
@@ -10718,10 +10747,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C7" s="3">
         <v>4260</v>
@@ -10730,7 +10759,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -10744,10 +10773,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C8" s="3">
         <v>2551</v>
@@ -10756,7 +10785,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -10770,10 +10799,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C9" s="3">
         <v>2550</v>
@@ -10782,7 +10811,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>273</v>
@@ -10796,10 +10825,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C10" s="3">
         <v>4383</v>
@@ -10808,7 +10837,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>273</v>
@@ -10868,10 +10897,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C2" s="3">
         <v>3644</v>
@@ -10880,7 +10909,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10894,10 +10923,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C3" s="3">
         <v>3644</v>
@@ -10906,7 +10935,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10920,10 +10949,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C4" s="3">
         <v>3641</v>
@@ -10932,7 +10961,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10946,10 +10975,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C5" s="3">
         <v>3645</v>
@@ -10958,7 +10987,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -10972,10 +11001,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C6" s="3">
         <v>3852</v>
@@ -10984,7 +11013,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>12</v>
@@ -10998,10 +11027,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C7" s="3">
         <v>3647</v>
@@ -11010,7 +11039,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -11024,10 +11053,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C8" s="3">
         <v>3648</v>
@@ -11036,7 +11065,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -11096,10 +11125,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C2" s="3">
         <v>3056</v>
@@ -11122,10 +11151,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C3" s="3">
         <v>3083</v>
@@ -11134,7 +11163,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -11148,10 +11177,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C4" s="3">
         <v>2264</v>
@@ -11174,10 +11203,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C5" s="3">
         <v>2355</v>
@@ -11186,7 +11215,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>29</v>
@@ -11200,10 +11229,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C6" s="3">
         <v>573</v>
@@ -11226,10 +11255,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C7" s="3">
         <v>572</v>
@@ -11238,7 +11267,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -11252,10 +11281,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C8" s="3">
         <v>4411</v>
@@ -11278,10 +11307,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C9" s="3">
         <v>4410</v>
@@ -11290,7 +11319,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>29</v>
@@ -11350,10 +11379,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C2" s="3">
         <v>4044</v>
@@ -11362,7 +11391,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -11376,10 +11405,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C3" s="3">
         <v>4672</v>
@@ -11388,7 +11417,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -11402,10 +11431,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C4" s="3">
         <v>4043</v>
@@ -11428,10 +11457,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C5" s="3">
         <v>3531</v>
@@ -11454,10 +11483,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C6" s="3">
         <v>3974</v>
@@ -11480,10 +11509,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C7" s="3">
         <v>3530</v>
@@ -11506,10 +11535,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C8" s="3">
         <v>4282</v>
@@ -11532,10 +11561,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C9" s="3">
         <v>3870</v>
@@ -11544,7 +11573,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>12</v>
@@ -11558,10 +11587,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C10" s="3">
         <v>3701</v>
@@ -11570,7 +11599,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
@@ -11584,10 +11613,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C11" s="3">
         <v>3800</v>
@@ -11596,7 +11625,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>12</v>
@@ -11610,10 +11639,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C12" s="3">
         <v>3725</v>
@@ -11622,7 +11651,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>12</v>
@@ -11636,10 +11665,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C13" s="3">
         <v>3871</v>
@@ -11648,7 +11677,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>12</v>
@@ -11662,10 +11691,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C14" s="3">
         <v>2825</v>
@@ -11688,10 +11717,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C15" s="3">
         <v>2828</v>
@@ -11714,10 +11743,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C16" s="3">
         <v>2826</v>
@@ -11740,10 +11769,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C17" s="3">
         <v>3058</v>
@@ -11766,10 +11795,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C18" s="3">
         <v>3059</v>
@@ -11792,10 +11821,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C19" s="3">
         <v>2829</v>
@@ -11818,10 +11847,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C20" s="3">
         <v>4126</v>
@@ -11844,10 +11873,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C21" s="3">
         <v>2827</v>
@@ -11870,10 +11899,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C22" s="3">
         <v>3801</v>
@@ -11882,7 +11911,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>12</v>
@@ -11896,10 +11925,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C23" s="3">
         <v>3833</v>
@@ -11908,7 +11937,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>12</v>
@@ -11922,10 +11951,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C24" s="3">
         <v>3897</v>
@@ -11948,10 +11977,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C25" s="3">
         <v>3764</v>
@@ -12072,10 +12101,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C4" s="3">
         <v>3443</v>
@@ -12098,10 +12127,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C5" s="3">
         <v>3019</v>
@@ -12124,10 +12153,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C6" s="3">
         <v>4489</v>
@@ -12150,10 +12179,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C7" s="3">
         <v>4490</v>
@@ -12176,10 +12205,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C8" s="3">
         <v>3476</v>
@@ -12202,10 +12231,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C9" s="3">
         <v>3477</v>
@@ -12228,10 +12257,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C10" s="3">
         <v>4344</v>
@@ -12306,10 +12335,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C13" s="3">
         <v>3719</v>
@@ -12332,10 +12361,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C14" s="3">
         <v>3720</v>
@@ -12358,10 +12387,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C15" s="3">
         <v>3765</v>
@@ -12384,10 +12413,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C16" s="3">
         <v>3766</v>
@@ -12410,10 +12439,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C17" s="3">
         <v>3126</v>
@@ -12436,10 +12465,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C18" s="3">
         <v>3127</v>
@@ -12462,10 +12491,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C19" s="3">
         <v>3435</v>
@@ -12488,10 +12517,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C20" s="3">
         <v>3436</v>
@@ -12514,10 +12543,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C21" s="3">
         <v>3128</v>
@@ -12540,10 +12569,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C22" s="3">
         <v>3129</v>
@@ -12566,10 +12595,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C23" s="3">
         <v>4158</v>
@@ -12592,10 +12621,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C24" s="3">
         <v>4159</v>
@@ -12618,10 +12647,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C25" s="3">
         <v>4561</v>
@@ -12644,10 +12673,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C26" s="3">
         <v>4562</v>
@@ -12774,10 +12803,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C31" s="3">
         <v>4346</v>
@@ -12800,10 +12829,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C32" s="3">
         <v>4345</v>
@@ -12826,10 +12855,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C33" s="3">
         <v>4347</v>
@@ -12852,10 +12881,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C34" s="3">
         <v>4446</v>
@@ -12878,10 +12907,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C35" s="3">
         <v>4476</v>
@@ -12893,7 +12922,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G35" s="3">
         <v>33.5</v>
@@ -12904,10 +12933,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C36" s="3">
         <v>4348</v>
@@ -12930,10 +12959,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C37" s="3">
         <v>4456</v>
@@ -12942,7 +12971,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>273</v>
@@ -12956,10 +12985,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C38" s="3">
         <v>4051</v>
@@ -12982,10 +13011,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C39" s="3">
         <v>2833</v>
@@ -13008,10 +13037,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C40" s="3">
         <v>3125</v>
@@ -13034,10 +13063,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C41" s="3">
         <v>3752</v>
@@ -13060,10 +13089,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C42" s="3">
         <v>3753</v>
@@ -13086,10 +13115,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C43" s="3">
         <v>2511</v>
@@ -13112,10 +13141,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C44" s="3">
         <v>4311</v>
@@ -13138,10 +13167,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C45" s="3">
         <v>4046</v>
@@ -13164,10 +13193,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C46" s="3">
         <v>4047</v>
@@ -13190,10 +13219,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C47" s="3">
         <v>4312</v>
@@ -13216,10 +13245,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C48" s="3">
         <v>4310</v>
@@ -13242,10 +13271,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C49" s="3">
         <v>4074</v>
@@ -13254,7 +13283,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>12</v>
@@ -13268,10 +13297,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C50" s="3">
         <v>4076</v>
@@ -13280,10 +13309,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G50" s="3">
         <v>32.5</v>
@@ -13294,10 +13323,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C51" s="3">
         <v>4133</v>
@@ -13306,10 +13335,10 @@
         <v>10</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G51" s="3">
         <v>72</v>
@@ -13320,10 +13349,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C52" s="3">
         <v>3068</v>
@@ -13346,10 +13375,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C53" s="3">
         <v>3087</v>
@@ -13372,10 +13401,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C54" s="3">
         <v>4560</v>
@@ -13398,10 +13427,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C55" s="3">
         <v>4531</v>
@@ -13424,10 +13453,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C56" s="3">
         <v>4532</v>
@@ -13450,10 +13479,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C57" s="3">
         <v>4559</v>
@@ -13462,7 +13491,7 @@
         <v>12</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>12</v>
@@ -13476,10 +13505,10 @@
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C58" s="3">
         <v>4493</v>
@@ -13502,10 +13531,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C59" s="3">
         <v>4102</v>
@@ -13514,7 +13543,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>12</v>
@@ -13528,10 +13557,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C60" s="3">
         <v>4103</v>
@@ -13540,7 +13569,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>273</v>
@@ -13554,10 +13583,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C61" s="3">
         <v>4624</v>
@@ -13566,7 +13595,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>12</v>
@@ -13580,10 +13609,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C62" s="3">
         <v>4627</v>
@@ -13592,7 +13621,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>12</v>
@@ -13606,10 +13635,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C63" s="3">
         <v>4628</v>
@@ -13618,7 +13647,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>12</v>
@@ -13632,10 +13661,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C64" s="3">
         <v>4625</v>
@@ -13644,7 +13673,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>12</v>
@@ -13658,10 +13687,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C65" s="3">
         <v>4626</v>
@@ -13670,7 +13699,7 @@
         <v>21</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>12</v>
@@ -13684,10 +13713,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C66" s="3">
         <v>4699</v>
@@ -13696,7 +13725,7 @@
         <v>50</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>273</v>
@@ -13710,10 +13739,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C67" s="3">
         <v>4643</v>
@@ -13722,7 +13751,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>29</v>
@@ -13736,10 +13765,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C68" s="3">
         <v>4687</v>
@@ -13748,7 +13777,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>29</v>
@@ -13762,10 +13791,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C69" s="3">
         <v>4644</v>
@@ -13774,7 +13803,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>29</v>
@@ -13788,10 +13817,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C70" s="3">
         <v>4547</v>
@@ -13800,7 +13829,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>273</v>
@@ -13814,10 +13843,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C71" s="3">
         <v>4104</v>
@@ -13826,7 +13855,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>273</v>
@@ -13840,10 +13869,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C72" s="3">
         <v>4101</v>
@@ -13852,7 +13881,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>273</v>
@@ -13866,10 +13895,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C73" s="3">
         <v>4641</v>
@@ -13878,7 +13907,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>12</v>
@@ -13892,10 +13921,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C74" s="3">
         <v>4583</v>
@@ -13904,7 +13933,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>29</v>
@@ -13918,10 +13947,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C75" s="3">
         <v>4105</v>
@@ -13930,7 +13959,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>273</v>
@@ -13944,10 +13973,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C76" s="3">
         <v>3705</v>
@@ -13956,7 +13985,7 @@
         <v>12</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>273</v>
@@ -13970,10 +13999,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C77" s="3">
         <v>3823</v>
@@ -13982,7 +14011,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>29</v>
@@ -13996,10 +14025,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C78" s="3">
         <v>4308</v>
@@ -14008,7 +14037,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>12</v>
@@ -14022,10 +14051,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C79" s="3">
         <v>4309</v>
@@ -14034,10 +14063,10 @@
         <v>10</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G79" s="3">
         <v>68.5</v>
@@ -14048,10 +14077,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C80" s="3">
         <v>4635</v>
@@ -14060,10 +14089,10 @@
         <v>10</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G80" s="3">
         <v>177</v>
@@ -14074,10 +14103,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C81" s="3">
         <v>4412</v>
@@ -14089,7 +14118,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G81" s="3">
         <v>75.5</v>
@@ -14100,10 +14129,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C82" s="3">
         <v>4413</v>
@@ -14126,10 +14155,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C83" s="3">
         <v>4414</v>
@@ -14152,10 +14181,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C84" s="3">
         <v>4415</v>
@@ -14178,10 +14207,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C85" s="3">
         <v>4416</v>
@@ -14204,10 +14233,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C86" s="3">
         <v>4475</v>
@@ -14216,7 +14245,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>12</v>
@@ -14230,10 +14259,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C87" s="3">
         <v>4354</v>
@@ -14242,10 +14271,10 @@
         <v>12</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G87" s="3">
         <v>79.5</v>
@@ -14256,10 +14285,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C88" s="3">
         <v>4445</v>
@@ -14268,7 +14297,7 @@
         <v>12</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>29</v>
@@ -14282,10 +14311,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C89" s="3">
         <v>4353</v>
@@ -14294,7 +14323,7 @@
         <v>12</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>29</v>
@@ -14308,10 +14337,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C90" s="3">
         <v>4350</v>
@@ -14320,7 +14349,7 @@
         <v>12</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>29</v>
@@ -14334,10 +14363,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C91" s="3">
         <v>4352</v>
@@ -14346,7 +14375,7 @@
         <v>12</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -14360,10 +14389,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C92" s="3">
         <v>4349</v>
@@ -14372,7 +14401,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>29</v>
@@ -14386,10 +14415,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C93" s="3">
         <v>4351</v>
@@ -14398,7 +14427,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>29</v>
@@ -14412,10 +14441,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C94" s="3">
         <v>4581</v>
@@ -14424,7 +14453,7 @@
         <v>12</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>29</v>
@@ -14438,10 +14467,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C95" s="3">
         <v>4096</v>
@@ -14464,10 +14493,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C96" s="3">
         <v>4582</v>
@@ -14476,7 +14505,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>12</v>
@@ -14490,10 +14519,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C97" s="3">
         <v>4123</v>
@@ -14502,7 +14531,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>12</v>
@@ -14516,10 +14545,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C98" s="3">
         <v>4306</v>
@@ -14528,10 +14557,10 @@
         <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G98" s="3">
         <v>81</v>
@@ -14542,10 +14571,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C99" s="3">
         <v>4307</v>
@@ -14554,10 +14583,10 @@
         <v>10</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G99" s="3">
         <v>81</v>
@@ -14568,10 +14597,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C100" s="3">
         <v>2659</v>
@@ -14580,7 +14609,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>273</v>
@@ -14594,10 +14623,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C101" s="3">
         <v>2621</v>
@@ -14606,7 +14635,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>273</v>
@@ -14620,10 +14649,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C102" s="3">
         <v>3656</v>
@@ -14632,7 +14661,7 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>273</v>
@@ -14694,10 +14723,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C2" s="3">
         <v>4408</v>
@@ -14720,10 +14749,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C3" s="3">
         <v>4341</v>
@@ -14746,10 +14775,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C4" s="3">
         <v>4265</v>
@@ -14772,10 +14801,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C5" s="3">
         <v>4266</v>
@@ -14798,10 +14827,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C6" s="3">
         <v>4269</v>
@@ -14824,10 +14853,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C7" s="3">
         <v>4273</v>
@@ -14850,10 +14879,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C8" s="3">
         <v>4406</v>
@@ -14876,10 +14905,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C9" s="3">
         <v>4267</v>
@@ -14902,10 +14931,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C10" s="3">
         <v>4271</v>
@@ -14928,10 +14957,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C11" s="3">
         <v>4276</v>
@@ -14954,10 +14983,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C12" s="3">
         <v>2205</v>
@@ -14980,10 +15009,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C13" s="3">
         <v>4342</v>
@@ -15006,10 +15035,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C14" s="3">
         <v>4270</v>
@@ -15032,10 +15061,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C15" s="3">
         <v>4275</v>
@@ -15058,10 +15087,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C16" s="3">
         <v>4404</v>
@@ -15084,10 +15113,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C17" s="3">
         <v>4264</v>
@@ -15110,10 +15139,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C18" s="3">
         <v>4407</v>
@@ -15136,10 +15165,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C19" s="3">
         <v>4397</v>
@@ -15162,10 +15191,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C20" s="3">
         <v>4343</v>
@@ -15188,10 +15217,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C21" s="3">
         <v>4268</v>
@@ -15273,10 +15302,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C2" s="3">
         <v>3459</v>
@@ -15285,7 +15314,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -15299,10 +15328,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C3" s="3">
         <v>3803</v>
@@ -15311,7 +15340,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -15325,10 +15354,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C4" s="3">
         <v>3425</v>
@@ -15337,10 +15366,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G4" s="3">
         <v>29</v>
@@ -15351,10 +15380,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C5" s="3">
         <v>3426</v>
@@ -15363,7 +15392,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>29</v>
@@ -15377,10 +15406,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C6" s="3">
         <v>3427</v>
@@ -15389,10 +15418,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G6" s="3">
         <v>62.5</v>
@@ -15403,10 +15432,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C7" s="3">
         <v>3428</v>
@@ -15415,7 +15444,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>29</v>
@@ -15429,10 +15458,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C8" s="3">
         <v>3429</v>
@@ -15441,10 +15470,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G8" s="3">
         <v>76.5</v>
@@ -15455,10 +15484,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C9" s="3">
         <v>3430</v>
@@ -15467,7 +15496,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>29</v>
@@ -15481,10 +15510,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C10" s="3">
         <v>3913</v>
@@ -15493,10 +15522,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G10" s="3">
         <v>68</v>
@@ -15507,10 +15536,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C11" s="3">
         <v>3872</v>
@@ -15519,7 +15548,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>29</v>
@@ -15533,10 +15562,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C12" s="3">
         <v>3422</v>
@@ -15545,10 +15574,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G12" s="3">
         <v>20</v>
@@ -15559,10 +15588,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C13" s="3">
         <v>3423</v>
@@ -15571,7 +15600,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>29</v>
@@ -15585,10 +15614,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C14" s="3">
         <v>3431</v>
@@ -15597,10 +15626,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G14" s="3">
         <v>115</v>
@@ -15611,10 +15640,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C15" s="3">
         <v>3432</v>
@@ -15623,7 +15652,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>29</v>
@@ -17873,7 +17902,7 @@
         <v>137</v>
       </c>
       <c r="C86" s="3">
-        <v>4291</v>
+        <v>4179</v>
       </c>
       <c r="D86" s="3">
         <v>11</v>
@@ -27989,7 +28018,7 @@
         <v>11</v>
       </c>
       <c r="G108" s="3">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="H108" s="3">
         <f>MROUND(G108*1.03, 0.5)</f>
@@ -28015,7 +28044,7 @@
         <v>12</v>
       </c>
       <c r="G109" s="3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H109" s="3">
         <f>MROUND(G109*1.03, 0.5)</f>
@@ -28026,7 +28055,7 @@
         <v>555</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C110" s="3">
         <v>4702</v>
@@ -28052,7 +28081,7 @@
         <v>555</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C111" s="3">
         <v>4701</v>
@@ -28075,10 +28104,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C112" s="3">
         <v>1515</v>
@@ -28101,10 +28130,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C113" s="3">
         <v>2552</v>
@@ -28127,10 +28156,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C114" s="3">
         <v>3092</v>
@@ -28153,10 +28182,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C115" s="3">
         <v>2589</v>
@@ -28179,10 +28208,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C116" s="3">
         <v>2588</v>
@@ -28205,10 +28234,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C117" s="3">
         <v>2688</v>
@@ -28231,10 +28260,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C118" s="3">
         <v>2599</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="1133">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2057,6 +2057,9 @@
     <t>QUINOA EM GRÃOS</t>
   </si>
   <si>
+    <t>323.50</t>
+  </si>
+  <si>
     <t>semente-de-sucupira</t>
   </si>
   <si>
@@ -2406,6 +2409,9 @@
   </si>
   <si>
     <t>PSYLLIUM HUSK</t>
+  </si>
+  <si>
+    <t>262.50</t>
   </si>
   <si>
     <t>tribulus-terrestres-da-folha</t>
@@ -7422,7 +7428,7 @@
         <v>11</v>
       </c>
       <c r="G31" s="3">
-        <v>1725</v>
+        <v>1600</v>
       </c>
       <c r="H31" s="3">
         <f>MROUND(G31*1.03, 0.5)</f>
@@ -7447,8 +7453,8 @@
       <c r="F32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="3">
-        <v>348.5</v>
+      <c r="G32" s="3" t="s">
+        <v>675</v>
       </c>
       <c r="H32" s="3">
         <f>MROUND(G32*1.03, 0.5)</f>
@@ -7508,10 +7514,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C35" s="3">
         <v>3754</v>
@@ -7581,10 +7587,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C2" s="3">
         <v>4336</v>
@@ -7607,10 +7613,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C3" s="3">
         <v>2618</v>
@@ -7633,10 +7639,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C4" s="3">
         <v>2398</v>
@@ -7659,10 +7665,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C5" s="3">
         <v>2297</v>
@@ -7685,10 +7691,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C6" s="3">
         <v>3653</v>
@@ -7711,10 +7717,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C7" s="3">
         <v>2339</v>
@@ -7737,10 +7743,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C8" s="3">
         <v>2223</v>
@@ -7763,10 +7769,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C9" s="3">
         <v>3707</v>
@@ -7789,10 +7795,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C10" s="3">
         <v>4090</v>
@@ -7815,10 +7821,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C11" s="3">
         <v>4279</v>
@@ -7867,10 +7873,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C13" s="3">
         <v>3540</v>
@@ -7893,10 +7899,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C14" s="3">
         <v>3541</v>
@@ -7997,10 +8003,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C18" s="3">
         <v>4639</v>
@@ -8023,10 +8029,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C19" s="3">
         <v>2336</v>
@@ -8049,10 +8055,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C20" s="3">
         <v>2421</v>
@@ -8075,10 +8081,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C21" s="3">
         <v>2568</v>
@@ -8101,10 +8107,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C22" s="3">
         <v>3009</v>
@@ -8127,10 +8133,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C23" s="3">
         <v>2778</v>
@@ -8153,10 +8159,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C24" s="3">
         <v>3106</v>
@@ -8179,10 +8185,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C25" s="3">
         <v>3489</v>
@@ -8205,10 +8211,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C26" s="3">
         <v>2783</v>
@@ -8231,10 +8237,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C27" s="3">
         <v>3755</v>
@@ -8257,10 +8263,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C28" s="3">
         <v>3487</v>
@@ -8283,10 +8289,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C29" s="3">
         <v>3486</v>
@@ -8309,10 +8315,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C30" s="3">
         <v>4488</v>
@@ -8335,10 +8341,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C31" s="3">
         <v>4333</v>
@@ -8361,10 +8367,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C32" s="3">
         <v>4650</v>
@@ -8387,10 +8393,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C33" s="3">
         <v>4388</v>
@@ -8413,10 +8419,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C34" s="3">
         <v>4389</v>
@@ -8439,10 +8445,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C35" s="3">
         <v>3488</v>
@@ -8465,10 +8471,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C36" s="3">
         <v>3400</v>
@@ -8491,10 +8497,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C37" s="3">
         <v>2257</v>
@@ -8517,10 +8523,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C38" s="3">
         <v>565</v>
@@ -8543,10 +8549,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C39" s="3">
         <v>4474</v>
@@ -8569,10 +8575,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C40" s="3">
         <v>4473</v>
@@ -8595,10 +8601,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C41" s="3">
         <v>2658</v>
@@ -8621,10 +8627,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C42" s="3">
         <v>2657</v>
@@ -8647,7 +8653,7 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>587</v>
@@ -8673,10 +8679,10 @@
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C44" s="3">
         <v>3537</v>
@@ -8699,10 +8705,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C45" s="3">
         <v>2732</v>
@@ -8725,10 +8731,10 @@
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C46" s="3">
         <v>2733</v>
@@ -8751,10 +8757,10 @@
     </row>
     <row r="47" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C47" s="3">
         <v>2584</v>
@@ -8777,10 +8783,10 @@
     </row>
     <row r="48" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C48" s="3">
         <v>2677</v>
@@ -8803,10 +8809,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C49" s="3">
         <v>2495</v>
@@ -8829,10 +8835,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C50" s="3">
         <v>2678</v>
@@ -8855,10 +8861,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C51" s="3">
         <v>4498</v>
@@ -8881,10 +8887,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C52" s="3">
         <v>4253</v>
@@ -8907,10 +8913,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C53" s="3">
         <v>4500</v>
@@ -8933,10 +8939,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C54" s="3">
         <v>4249</v>
@@ -8959,10 +8965,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C55" s="3">
         <v>3724</v>
@@ -8985,10 +8991,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C56" s="3">
         <v>3736</v>
@@ -9011,10 +9017,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C57" s="3">
         <v>4499</v>
@@ -9037,10 +9043,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C58" s="3">
         <v>3536</v>
@@ -9063,10 +9069,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C59" s="3">
         <v>2494</v>
@@ -9089,10 +9095,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C60" s="3">
         <v>2679</v>
@@ -9115,10 +9121,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C61" s="3">
         <v>4497</v>
@@ -9141,10 +9147,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C62" s="3">
         <v>2493</v>
@@ -9167,10 +9173,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C63" s="3">
         <v>3535</v>
@@ -9193,10 +9199,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C64" s="3">
         <v>2498</v>
@@ -9219,10 +9225,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C65" s="3">
         <v>2806</v>
@@ -9245,10 +9251,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C66" s="3">
         <v>2807</v>
@@ -9271,10 +9277,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C67" s="3">
         <v>4556</v>
@@ -9297,10 +9303,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C68" s="3">
         <v>4557</v>
@@ -9323,10 +9329,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C69" s="3">
         <v>4018</v>
@@ -9349,10 +9355,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C70" s="3">
         <v>2652</v>
@@ -9375,10 +9381,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C71" s="3">
         <v>4049</v>
@@ -9401,10 +9407,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C72" s="3">
         <v>3737</v>
@@ -9427,10 +9433,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C73" s="3">
         <v>4301</v>
@@ -9453,10 +9459,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C74" s="3">
         <v>4334</v>
@@ -9479,10 +9485,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C75" s="3">
         <v>195</v>
@@ -9505,10 +9511,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C76" s="3">
         <v>54</v>
@@ -9531,10 +9537,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C77" s="3">
         <v>63</v>
@@ -9557,10 +9563,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C78" s="3">
         <v>2483</v>
@@ -9583,10 +9589,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C79" s="3">
         <v>2974</v>
@@ -9609,10 +9615,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C80" s="3">
         <v>2831</v>
@@ -9635,10 +9641,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C81" s="3">
         <v>4137</v>
@@ -9661,10 +9667,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C82" s="3">
         <v>4380</v>
@@ -9687,10 +9693,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C83" s="3">
         <v>4566</v>
@@ -9713,10 +9719,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C84" s="3">
         <v>4567</v>
@@ -9739,10 +9745,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C85" s="3">
         <v>4204</v>
@@ -9765,10 +9771,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C86" s="3">
         <v>4205</v>
@@ -9791,10 +9797,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C87" s="3">
         <v>4378</v>
@@ -9817,10 +9823,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C88" s="3">
         <v>4379</v>
@@ -9843,10 +9849,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C89" s="3">
         <v>3524</v>
@@ -9858,7 +9864,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G89" s="3">
         <v>350</v>
@@ -9869,10 +9875,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C90" s="3">
         <v>3523</v>
@@ -9884,7 +9890,7 @@
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G90" s="3">
         <v>72</v>
@@ -9895,10 +9901,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C91" s="3">
         <v>3521</v>
@@ -9907,7 +9913,7 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -9921,10 +9927,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C92" s="3">
         <v>3522</v>
@@ -9947,10 +9953,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C93" s="3">
         <v>64</v>
@@ -9973,10 +9979,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C94" s="3">
         <v>90</v>
@@ -9999,10 +10005,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C95" s="3">
         <v>3637</v>
@@ -10016,8 +10022,8 @@
       <c r="F95" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G95" s="3">
-        <v>375</v>
+      <c r="G95" s="3" t="s">
+        <v>793</v>
       </c>
       <c r="H95" s="3">
         <f>MROUND(G95*1.03, 0.5)</f>
@@ -10025,10 +10031,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C96" s="3">
         <v>2805</v>
@@ -10043,7 +10049,7 @@
         <v>11</v>
       </c>
       <c r="G96" s="3">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="H96" s="3">
         <f>MROUND(G96*1.03, 0.5)</f>
@@ -10051,10 +10057,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C97" s="3">
         <v>2427</v>
@@ -10069,7 +10075,7 @@
         <v>12</v>
       </c>
       <c r="G97" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H97" s="3">
         <f>MROUND(G97*1.03, 0.5)</f>
@@ -10077,10 +10083,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C98" s="3">
         <v>3437</v>
@@ -10103,10 +10109,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C99" s="3">
         <v>3396</v>
@@ -10129,10 +10135,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C100" s="3">
         <v>3395</v>
@@ -10141,7 +10147,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>29</v>
@@ -10155,10 +10161,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C101" s="3">
         <v>3490</v>
@@ -10167,7 +10173,7 @@
         <v>12</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>29</v>
@@ -10181,10 +10187,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C102" s="3">
         <v>458</v>
@@ -10193,7 +10199,7 @@
         <v>12</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>29</v>
@@ -10207,10 +10213,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C103" s="3">
         <v>2641</v>
@@ -10219,7 +10225,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>29</v>
@@ -10233,10 +10239,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C104" s="3">
         <v>4293</v>
@@ -10245,7 +10251,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>29</v>
@@ -10259,10 +10265,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C105" s="3">
         <v>2396</v>
@@ -10285,10 +10291,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C106" s="3">
         <v>2426</v>
@@ -10311,10 +10317,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C107" s="3">
         <v>4335</v>
@@ -10337,10 +10343,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C108" s="3">
         <v>4477</v>
@@ -10363,10 +10369,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C109" s="3">
         <v>4479</v>
@@ -10389,10 +10395,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C110" s="3">
         <v>4478</v>
@@ -10415,10 +10421,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C111" s="3">
         <v>2646</v>
@@ -10427,7 +10433,7 @@
         <v>12</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>273</v>
@@ -10441,10 +10447,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C112" s="3">
         <v>2645</v>
@@ -10453,7 +10459,7 @@
         <v>6</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>273</v>
@@ -10467,10 +10473,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C113" s="3">
         <v>2638</v>
@@ -10479,7 +10485,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>273</v>
@@ -10493,10 +10499,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C114" s="3">
         <v>4294</v>
@@ -10505,7 +10511,7 @@
         <v>18</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>273</v>
@@ -10519,10 +10525,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C115" s="3">
         <v>4314</v>
@@ -10545,10 +10551,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C116" s="3">
         <v>4315</v>
@@ -10557,7 +10563,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>29</v>
@@ -10617,10 +10623,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C2" s="3">
         <v>3402</v>
@@ -10629,7 +10635,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10643,10 +10649,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C3" s="3">
         <v>3401</v>
@@ -10655,7 +10661,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10669,10 +10675,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C4" s="3">
         <v>3403</v>
@@ -10681,7 +10687,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10695,10 +10701,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C5" s="3">
         <v>4032</v>
@@ -10707,7 +10713,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -10721,10 +10727,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C6" s="3">
         <v>4460</v>
@@ -10733,7 +10739,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>273</v>
@@ -10747,10 +10753,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C7" s="3">
         <v>4260</v>
@@ -10759,7 +10765,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -10773,10 +10779,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C8" s="3">
         <v>2551</v>
@@ -10785,7 +10791,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -10799,10 +10805,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C9" s="3">
         <v>2550</v>
@@ -10811,7 +10817,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>273</v>
@@ -10825,10 +10831,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C10" s="3">
         <v>4383</v>
@@ -10837,7 +10843,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>273</v>
@@ -10897,10 +10903,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C2" s="3">
         <v>3644</v>
@@ -10909,7 +10915,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10923,10 +10929,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C3" s="3">
         <v>3644</v>
@@ -10935,7 +10941,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10949,10 +10955,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C4" s="3">
         <v>3641</v>
@@ -10961,7 +10967,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10975,10 +10981,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C5" s="3">
         <v>3645</v>
@@ -10987,7 +10993,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -11001,10 +11007,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C6" s="3">
         <v>3852</v>
@@ -11013,7 +11019,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>12</v>
@@ -11027,10 +11033,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C7" s="3">
         <v>3647</v>
@@ -11039,7 +11045,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -11053,10 +11059,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C8" s="3">
         <v>3648</v>
@@ -11065,7 +11071,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -11125,10 +11131,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C2" s="3">
         <v>3056</v>
@@ -11151,10 +11157,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C3" s="3">
         <v>3083</v>
@@ -11177,10 +11183,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C4" s="3">
         <v>2264</v>
@@ -11203,10 +11209,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C5" s="3">
         <v>2355</v>
@@ -11229,10 +11235,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C6" s="3">
         <v>573</v>
@@ -11255,10 +11261,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C7" s="3">
         <v>572</v>
@@ -11281,10 +11287,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C8" s="3">
         <v>4411</v>
@@ -11307,10 +11313,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C9" s="3">
         <v>4410</v>
@@ -11379,10 +11385,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C2" s="3">
         <v>4044</v>
@@ -11391,7 +11397,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -11405,10 +11411,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C3" s="3">
         <v>4672</v>
@@ -11417,7 +11423,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -11431,10 +11437,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C4" s="3">
         <v>4043</v>
@@ -11457,10 +11463,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C5" s="3">
         <v>3531</v>
@@ -11483,10 +11489,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C6" s="3">
         <v>3974</v>
@@ -11509,10 +11515,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C7" s="3">
         <v>3530</v>
@@ -11535,10 +11541,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C8" s="3">
         <v>4282</v>
@@ -11561,10 +11567,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C9" s="3">
         <v>3870</v>
@@ -11573,7 +11579,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>12</v>
@@ -11587,10 +11593,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C10" s="3">
         <v>3701</v>
@@ -11599,7 +11605,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
@@ -11613,10 +11619,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C11" s="3">
         <v>3800</v>
@@ -11625,7 +11631,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>12</v>
@@ -11639,10 +11645,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C12" s="3">
         <v>3725</v>
@@ -11651,7 +11657,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>12</v>
@@ -11665,10 +11671,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C13" s="3">
         <v>3871</v>
@@ -11677,7 +11683,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>12</v>
@@ -11691,10 +11697,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C14" s="3">
         <v>2825</v>
@@ -11717,10 +11723,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C15" s="3">
         <v>2828</v>
@@ -11743,10 +11749,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C16" s="3">
         <v>2826</v>
@@ -11769,10 +11775,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C17" s="3">
         <v>3058</v>
@@ -11795,10 +11801,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C18" s="3">
         <v>3059</v>
@@ -11821,10 +11827,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C19" s="3">
         <v>2829</v>
@@ -11847,10 +11853,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C20" s="3">
         <v>4126</v>
@@ -11873,10 +11879,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C21" s="3">
         <v>2827</v>
@@ -11899,10 +11905,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C22" s="3">
         <v>3801</v>
@@ -11911,7 +11917,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>12</v>
@@ -11925,10 +11931,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C23" s="3">
         <v>3833</v>
@@ -11937,7 +11943,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>12</v>
@@ -11951,10 +11957,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C24" s="3">
         <v>3897</v>
@@ -11977,10 +11983,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C25" s="3">
         <v>3764</v>
@@ -12101,10 +12107,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C4" s="3">
         <v>3443</v>
@@ -12127,10 +12133,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C5" s="3">
         <v>3019</v>
@@ -12153,10 +12159,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C6" s="3">
         <v>4489</v>
@@ -12179,10 +12185,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C7" s="3">
         <v>4490</v>
@@ -12205,10 +12211,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C8" s="3">
         <v>3476</v>
@@ -12231,10 +12237,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C9" s="3">
         <v>3477</v>
@@ -12257,10 +12263,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C10" s="3">
         <v>4344</v>
@@ -12335,10 +12341,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C13" s="3">
         <v>3719</v>
@@ -12361,10 +12367,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C14" s="3">
         <v>3720</v>
@@ -12387,10 +12393,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C15" s="3">
         <v>3765</v>
@@ -12413,10 +12419,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C16" s="3">
         <v>3766</v>
@@ -12439,10 +12445,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C17" s="3">
         <v>3126</v>
@@ -12465,10 +12471,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C18" s="3">
         <v>3127</v>
@@ -12491,10 +12497,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C19" s="3">
         <v>3435</v>
@@ -12517,10 +12523,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C20" s="3">
         <v>3436</v>
@@ -12543,10 +12549,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C21" s="3">
         <v>3128</v>
@@ -12569,10 +12575,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C22" s="3">
         <v>3129</v>
@@ -12595,10 +12601,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C23" s="3">
         <v>4158</v>
@@ -12621,10 +12627,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C24" s="3">
         <v>4159</v>
@@ -12647,10 +12653,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C25" s="3">
         <v>4561</v>
@@ -12673,10 +12679,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C26" s="3">
         <v>4562</v>
@@ -12803,10 +12809,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C31" s="3">
         <v>4346</v>
@@ -12829,10 +12835,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C32" s="3">
         <v>4345</v>
@@ -12855,10 +12861,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C33" s="3">
         <v>4347</v>
@@ -12881,10 +12887,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C34" s="3">
         <v>4446</v>
@@ -12907,10 +12913,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C35" s="3">
         <v>4476</v>
@@ -12922,7 +12928,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G35" s="3">
         <v>33.5</v>
@@ -12933,10 +12939,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C36" s="3">
         <v>4348</v>
@@ -12959,10 +12965,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C37" s="3">
         <v>4456</v>
@@ -12985,10 +12991,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C38" s="3">
         <v>4051</v>
@@ -13011,10 +13017,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C39" s="3">
         <v>2833</v>
@@ -13037,10 +13043,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C40" s="3">
         <v>3125</v>
@@ -13063,10 +13069,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C41" s="3">
         <v>3752</v>
@@ -13089,10 +13095,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C42" s="3">
         <v>3753</v>
@@ -13115,10 +13121,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C43" s="3">
         <v>2511</v>
@@ -13141,10 +13147,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C44" s="3">
         <v>4311</v>
@@ -13167,10 +13173,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C45" s="3">
         <v>4046</v>
@@ -13193,10 +13199,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C46" s="3">
         <v>4047</v>
@@ -13219,10 +13225,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C47" s="3">
         <v>4312</v>
@@ -13245,10 +13251,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C48" s="3">
         <v>4310</v>
@@ -13271,10 +13277,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C49" s="3">
         <v>4074</v>
@@ -13283,7 +13289,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>12</v>
@@ -13297,10 +13303,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C50" s="3">
         <v>4076</v>
@@ -13309,10 +13315,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G50" s="3">
         <v>32.5</v>
@@ -13323,10 +13329,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C51" s="3">
         <v>4133</v>
@@ -13338,7 +13344,7 @@
         <v>585</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G51" s="3">
         <v>72</v>
@@ -13349,10 +13355,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C52" s="3">
         <v>3068</v>
@@ -13375,10 +13381,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C53" s="3">
         <v>3087</v>
@@ -13401,10 +13407,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C54" s="3">
         <v>4560</v>
@@ -13427,10 +13433,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C55" s="3">
         <v>4531</v>
@@ -13453,10 +13459,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C56" s="3">
         <v>4532</v>
@@ -13479,10 +13485,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C57" s="3">
         <v>4559</v>
@@ -13505,10 +13511,10 @@
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C58" s="3">
         <v>4493</v>
@@ -13531,10 +13537,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C59" s="3">
         <v>4102</v>
@@ -13543,7 +13549,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>12</v>
@@ -13557,10 +13563,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C60" s="3">
         <v>4103</v>
@@ -13569,7 +13575,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>273</v>
@@ -13583,10 +13589,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C61" s="3">
         <v>4624</v>
@@ -13595,7 +13601,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>12</v>
@@ -13609,10 +13615,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C62" s="3">
         <v>4627</v>
@@ -13621,7 +13627,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>12</v>
@@ -13635,10 +13641,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C63" s="3">
         <v>4628</v>
@@ -13647,7 +13653,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>12</v>
@@ -13661,10 +13667,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C64" s="3">
         <v>4625</v>
@@ -13673,7 +13679,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>12</v>
@@ -13687,10 +13693,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C65" s="3">
         <v>4626</v>
@@ -13699,7 +13705,7 @@
         <v>21</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>12</v>
@@ -13713,10 +13719,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C66" s="3">
         <v>4699</v>
@@ -13725,7 +13731,7 @@
         <v>50</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>273</v>
@@ -13739,10 +13745,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C67" s="3">
         <v>4643</v>
@@ -13751,7 +13757,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>29</v>
@@ -13765,10 +13771,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C68" s="3">
         <v>4687</v>
@@ -13777,7 +13783,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>29</v>
@@ -13791,10 +13797,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C69" s="3">
         <v>4644</v>
@@ -13803,7 +13809,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>29</v>
@@ -13817,10 +13823,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C70" s="3">
         <v>4547</v>
@@ -13829,7 +13835,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>273</v>
@@ -13843,10 +13849,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C71" s="3">
         <v>4104</v>
@@ -13855,7 +13861,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>273</v>
@@ -13869,10 +13875,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C72" s="3">
         <v>4101</v>
@@ -13881,7 +13887,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>273</v>
@@ -13895,10 +13901,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C73" s="3">
         <v>4641</v>
@@ -13907,7 +13913,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>12</v>
@@ -13921,10 +13927,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C74" s="3">
         <v>4583</v>
@@ -13933,7 +13939,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>29</v>
@@ -13947,10 +13953,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C75" s="3">
         <v>4105</v>
@@ -13959,7 +13965,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>273</v>
@@ -13973,10 +13979,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C76" s="3">
         <v>3705</v>
@@ -13985,7 +13991,7 @@
         <v>12</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>273</v>
@@ -13999,10 +14005,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C77" s="3">
         <v>3823</v>
@@ -14011,7 +14017,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>29</v>
@@ -14025,10 +14031,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C78" s="3">
         <v>4308</v>
@@ -14037,7 +14043,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>12</v>
@@ -14051,10 +14057,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C79" s="3">
         <v>4309</v>
@@ -14063,10 +14069,10 @@
         <v>10</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G79" s="3">
         <v>68.5</v>
@@ -14077,10 +14083,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C80" s="3">
         <v>4635</v>
@@ -14089,10 +14095,10 @@
         <v>10</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G80" s="3">
         <v>177</v>
@@ -14103,10 +14109,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C81" s="3">
         <v>4412</v>
@@ -14118,7 +14124,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G81" s="3">
         <v>75.5</v>
@@ -14129,10 +14135,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C82" s="3">
         <v>4413</v>
@@ -14155,10 +14161,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C83" s="3">
         <v>4414</v>
@@ -14181,10 +14187,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C84" s="3">
         <v>4415</v>
@@ -14207,10 +14213,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C85" s="3">
         <v>4416</v>
@@ -14233,10 +14239,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C86" s="3">
         <v>4475</v>
@@ -14245,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>12</v>
@@ -14259,10 +14265,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C87" s="3">
         <v>4354</v>
@@ -14271,10 +14277,10 @@
         <v>12</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G87" s="3">
         <v>79.5</v>
@@ -14285,10 +14291,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C88" s="3">
         <v>4445</v>
@@ -14297,7 +14303,7 @@
         <v>12</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>29</v>
@@ -14311,10 +14317,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C89" s="3">
         <v>4353</v>
@@ -14323,7 +14329,7 @@
         <v>12</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>29</v>
@@ -14337,10 +14343,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="C90" s="3">
         <v>4350</v>
@@ -14349,7 +14355,7 @@
         <v>12</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>29</v>
@@ -14363,10 +14369,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C91" s="3">
         <v>4352</v>
@@ -14375,7 +14381,7 @@
         <v>12</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -14389,10 +14395,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="C92" s="3">
         <v>4349</v>
@@ -14401,7 +14407,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>29</v>
@@ -14415,10 +14421,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C93" s="3">
         <v>4351</v>
@@ -14427,7 +14433,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>29</v>
@@ -14441,10 +14447,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C94" s="3">
         <v>4581</v>
@@ -14453,7 +14459,7 @@
         <v>12</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>29</v>
@@ -14467,10 +14473,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C95" s="3">
         <v>4096</v>
@@ -14493,10 +14499,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C96" s="3">
         <v>4582</v>
@@ -14505,7 +14511,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>12</v>
@@ -14519,10 +14525,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C97" s="3">
         <v>4123</v>
@@ -14531,7 +14537,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>12</v>
@@ -14545,10 +14551,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C98" s="3">
         <v>4306</v>
@@ -14557,10 +14563,10 @@
         <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G98" s="3">
         <v>81</v>
@@ -14571,10 +14577,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C99" s="3">
         <v>4307</v>
@@ -14583,10 +14589,10 @@
         <v>10</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G99" s="3">
         <v>81</v>
@@ -14597,10 +14603,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C100" s="3">
         <v>2659</v>
@@ -14609,7 +14615,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>273</v>
@@ -14623,10 +14629,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C101" s="3">
         <v>2621</v>
@@ -14635,7 +14641,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>273</v>
@@ -14649,10 +14655,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C102" s="3">
         <v>3656</v>
@@ -14661,7 +14667,7 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>273</v>
@@ -14723,10 +14729,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C2" s="3">
         <v>4408</v>
@@ -14749,10 +14755,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C3" s="3">
         <v>4341</v>
@@ -14775,10 +14781,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="3">
         <v>4265</v>
@@ -14801,10 +14807,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C5" s="3">
         <v>4266</v>
@@ -14827,10 +14833,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C6" s="3">
         <v>4269</v>
@@ -14853,10 +14859,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C7" s="3">
         <v>4273</v>
@@ -14879,10 +14885,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C8" s="3">
         <v>4406</v>
@@ -14905,10 +14911,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C9" s="3">
         <v>4267</v>
@@ -14931,10 +14937,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C10" s="3">
         <v>4271</v>
@@ -14957,10 +14963,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C11" s="3">
         <v>4276</v>
@@ -14983,10 +14989,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C12" s="3">
         <v>2205</v>
@@ -15009,10 +15015,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C13" s="3">
         <v>4342</v>
@@ -15035,10 +15041,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C14" s="3">
         <v>4270</v>
@@ -15061,10 +15067,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C15" s="3">
         <v>4275</v>
@@ -15087,10 +15093,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C16" s="3">
         <v>4404</v>
@@ -15113,10 +15119,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C17" s="3">
         <v>4264</v>
@@ -15139,10 +15145,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C18" s="3">
         <v>4407</v>
@@ -15165,10 +15171,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C19" s="3">
         <v>4397</v>
@@ -15191,10 +15197,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C20" s="3">
         <v>4343</v>
@@ -15217,10 +15223,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C21" s="3">
         <v>4268</v>
@@ -15302,10 +15308,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C2" s="3">
         <v>3459</v>
@@ -15314,7 +15320,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -15328,10 +15334,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C3" s="3">
         <v>3803</v>
@@ -15340,7 +15346,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -15354,10 +15360,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C4" s="3">
         <v>3425</v>
@@ -15366,10 +15372,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G4" s="3">
         <v>29</v>
@@ -15380,10 +15386,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C5" s="3">
         <v>3426</v>
@@ -15392,7 +15398,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>29</v>
@@ -15406,10 +15412,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C6" s="3">
         <v>3427</v>
@@ -15418,10 +15424,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G6" s="3">
         <v>62.5</v>
@@ -15432,10 +15438,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C7" s="3">
         <v>3428</v>
@@ -15444,7 +15450,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>29</v>
@@ -15458,10 +15464,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C8" s="3">
         <v>3429</v>
@@ -15470,10 +15476,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G8" s="3">
         <v>76.5</v>
@@ -15484,10 +15490,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C9" s="3">
         <v>3430</v>
@@ -15496,7 +15502,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>29</v>
@@ -15510,10 +15516,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C10" s="3">
         <v>3913</v>
@@ -15522,10 +15528,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G10" s="3">
         <v>68</v>
@@ -15536,10 +15542,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C11" s="3">
         <v>3872</v>
@@ -15548,7 +15554,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>29</v>
@@ -15562,10 +15568,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C12" s="3">
         <v>3422</v>
@@ -15574,10 +15580,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G12" s="3">
         <v>20</v>
@@ -15588,10 +15594,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C13" s="3">
         <v>3423</v>
@@ -15600,7 +15606,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>29</v>
@@ -15614,10 +15620,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C14" s="3">
         <v>3431</v>
@@ -15626,10 +15632,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G14" s="3">
         <v>115</v>
@@ -15640,10 +15646,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C15" s="3">
         <v>3432</v>
@@ -15652,7 +15658,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>29</v>
@@ -18402,7 +18408,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="3">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="H12" s="3">
         <f>MROUND(G12*1.03, 0.5)</f>
@@ -18428,7 +18434,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="3">
-        <v>133.5</v>
+        <v>138.5</v>
       </c>
       <c r="H13" s="3">
         <f>MROUND(G13*1.03, 0.5)</f>
@@ -25470,7 +25476,7 @@
         <v>273</v>
       </c>
       <c r="G10" s="3">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="H10" s="3">
         <f>MROUND(G10*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -25268,7 +25268,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="3">
-        <v>475</v>
+        <v>412.5</v>
       </c>
       <c r="H2" s="3">
         <f>MROUND(G2*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -7194,7 +7194,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="3">
-        <v>23</v>
+        <v>27.5</v>
       </c>
       <c r="H22" s="3">
         <f>MROUND(G22*1.03, 0.5)</f>
@@ -11149,7 +11149,7 @@
         <v>273</v>
       </c>
       <c r="G2" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2" s="3">
         <f>MROUND(G2*1.03, 0.5)</f>
@@ -11175,7 +11175,7 @@
         <v>273</v>
       </c>
       <c r="G3" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3">
         <f>MROUND(G3*1.03, 0.5)</f>
@@ -11201,7 +11201,7 @@
         <v>29</v>
       </c>
       <c r="G4" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3">
         <f>MROUND(G4*1.03, 0.5)</f>
@@ -11227,7 +11227,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="3">
         <f>MROUND(G5*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="1134">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2325,6 +2325,9 @@
   </si>
   <si>
     <t>LINHAÇA DOURADA</t>
+  </si>
+  <si>
+    <t>312.50</t>
   </si>
   <si>
     <t>linhaa-marrom</t>
@@ -6056,7 +6059,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="3">
-        <v>450</v>
+        <v>415</v>
       </c>
       <c r="H5" s="3">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -9502,8 +9505,8 @@
       <c r="F75" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G75" s="3">
-        <v>300</v>
+      <c r="G75" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="H75" s="3">
         <f>MROUND(G75*1.03, 0.5)</f>
@@ -9529,7 +9532,7 @@
         <v>12</v>
       </c>
       <c r="G76" s="3">
-        <v>63</v>
+        <v>65.5</v>
       </c>
       <c r="H76" s="3">
         <f>MROUND(G76*1.03, 0.5)</f>
@@ -9537,10 +9540,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C77" s="3">
         <v>63</v>
@@ -9563,10 +9566,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C78" s="3">
         <v>2483</v>
@@ -9589,10 +9592,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C79" s="3">
         <v>2974</v>
@@ -9615,10 +9618,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C80" s="3">
         <v>2831</v>
@@ -9641,10 +9644,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C81" s="3">
         <v>4137</v>
@@ -9667,10 +9670,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C82" s="3">
         <v>4380</v>
@@ -9693,10 +9696,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C83" s="3">
         <v>4566</v>
@@ -9719,10 +9722,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C84" s="3">
         <v>4567</v>
@@ -9745,10 +9748,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C85" s="3">
         <v>4204</v>
@@ -9771,10 +9774,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C86" s="3">
         <v>4205</v>
@@ -9797,10 +9800,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C87" s="3">
         <v>4378</v>
@@ -9823,10 +9826,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C88" s="3">
         <v>4379</v>
@@ -9849,10 +9852,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C89" s="3">
         <v>3524</v>
@@ -9864,7 +9867,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G89" s="3">
         <v>350</v>
@@ -9875,10 +9878,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C90" s="3">
         <v>3523</v>
@@ -9890,7 +9893,7 @@
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G90" s="3">
         <v>72</v>
@@ -9901,10 +9904,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C91" s="3">
         <v>3521</v>
@@ -9913,7 +9916,7 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -9927,10 +9930,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C92" s="3">
         <v>3522</v>
@@ -9953,10 +9956,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C93" s="3">
         <v>64</v>
@@ -9979,10 +9982,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C94" s="3">
         <v>90</v>
@@ -10005,10 +10008,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C95" s="3">
         <v>3637</v>
@@ -10023,7 +10026,7 @@
         <v>11</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H95" s="3">
         <f>MROUND(G95*1.03, 0.5)</f>
@@ -10031,10 +10034,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C96" s="3">
         <v>2805</v>
@@ -10057,10 +10060,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C97" s="3">
         <v>2427</v>
@@ -10083,10 +10086,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C98" s="3">
         <v>3437</v>
@@ -10109,10 +10112,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C99" s="3">
         <v>3396</v>
@@ -10135,10 +10138,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C100" s="3">
         <v>3395</v>
@@ -10147,7 +10150,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>29</v>
@@ -10161,10 +10164,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C101" s="3">
         <v>3490</v>
@@ -10173,7 +10176,7 @@
         <v>12</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>29</v>
@@ -10187,10 +10190,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C102" s="3">
         <v>458</v>
@@ -10199,7 +10202,7 @@
         <v>12</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>29</v>
@@ -10213,10 +10216,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C103" s="3">
         <v>2641</v>
@@ -10225,7 +10228,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>29</v>
@@ -10239,10 +10242,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C104" s="3">
         <v>4293</v>
@@ -10251,7 +10254,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>29</v>
@@ -10265,10 +10268,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C105" s="3">
         <v>2396</v>
@@ -10291,10 +10294,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C106" s="3">
         <v>2426</v>
@@ -10317,10 +10320,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C107" s="3">
         <v>4335</v>
@@ -10343,10 +10346,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C108" s="3">
         <v>4477</v>
@@ -10369,10 +10372,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C109" s="3">
         <v>4479</v>
@@ -10395,10 +10398,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C110" s="3">
         <v>4478</v>
@@ -10421,10 +10424,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C111" s="3">
         <v>2646</v>
@@ -10433,7 +10436,7 @@
         <v>12</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>273</v>
@@ -10447,10 +10450,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C112" s="3">
         <v>2645</v>
@@ -10459,7 +10462,7 @@
         <v>6</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>273</v>
@@ -10473,10 +10476,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C113" s="3">
         <v>2638</v>
@@ -10485,7 +10488,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>273</v>
@@ -10499,10 +10502,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C114" s="3">
         <v>4294</v>
@@ -10511,7 +10514,7 @@
         <v>18</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>273</v>
@@ -10525,10 +10528,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C115" s="3">
         <v>4314</v>
@@ -10551,10 +10554,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C116" s="3">
         <v>4315</v>
@@ -10563,7 +10566,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>29</v>
@@ -10623,10 +10626,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C2" s="3">
         <v>3402</v>
@@ -10635,7 +10638,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10649,10 +10652,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C3" s="3">
         <v>3401</v>
@@ -10661,7 +10664,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10675,10 +10678,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C4" s="3">
         <v>3403</v>
@@ -10687,7 +10690,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10701,10 +10704,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C5" s="3">
         <v>4032</v>
@@ -10713,7 +10716,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -10727,10 +10730,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C6" s="3">
         <v>4460</v>
@@ -10739,7 +10742,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>273</v>
@@ -10753,10 +10756,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C7" s="3">
         <v>4260</v>
@@ -10765,7 +10768,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -10779,10 +10782,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C8" s="3">
         <v>2551</v>
@@ -10791,7 +10794,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -10805,10 +10808,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C9" s="3">
         <v>2550</v>
@@ -10817,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>273</v>
@@ -10831,10 +10834,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C10" s="3">
         <v>4383</v>
@@ -10843,7 +10846,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>273</v>
@@ -10903,10 +10906,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C2" s="3">
         <v>3644</v>
@@ -10915,7 +10918,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>273</v>
@@ -10929,10 +10932,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C3" s="3">
         <v>3644</v>
@@ -10941,7 +10944,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>273</v>
@@ -10955,10 +10958,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C4" s="3">
         <v>3641</v>
@@ -10967,7 +10970,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>273</v>
@@ -10981,10 +10984,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C5" s="3">
         <v>3645</v>
@@ -10993,7 +10996,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>273</v>
@@ -11007,10 +11010,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C6" s="3">
         <v>3852</v>
@@ -11019,7 +11022,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>12</v>
@@ -11033,10 +11036,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C7" s="3">
         <v>3647</v>
@@ -11045,7 +11048,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>273</v>
@@ -11059,10 +11062,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C8" s="3">
         <v>3648</v>
@@ -11071,7 +11074,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>273</v>
@@ -11131,10 +11134,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C2" s="3">
         <v>3056</v>
@@ -11157,10 +11160,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C3" s="3">
         <v>3083</v>
@@ -11183,10 +11186,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C4" s="3">
         <v>2264</v>
@@ -11209,10 +11212,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C5" s="3">
         <v>2355</v>
@@ -11235,10 +11238,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C6" s="3">
         <v>573</v>
@@ -11261,10 +11264,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C7" s="3">
         <v>572</v>
@@ -11287,10 +11290,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C8" s="3">
         <v>4411</v>
@@ -11313,10 +11316,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C9" s="3">
         <v>4410</v>
@@ -11385,10 +11388,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C2" s="3">
         <v>4044</v>
@@ -11397,7 +11400,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -11411,10 +11414,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C3" s="3">
         <v>4672</v>
@@ -11423,7 +11426,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -11437,10 +11440,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C4" s="3">
         <v>4043</v>
@@ -11463,10 +11466,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C5" s="3">
         <v>3531</v>
@@ -11489,10 +11492,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C6" s="3">
         <v>3974</v>
@@ -11515,10 +11518,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C7" s="3">
         <v>3530</v>
@@ -11541,10 +11544,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C8" s="3">
         <v>4282</v>
@@ -11567,10 +11570,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C9" s="3">
         <v>3870</v>
@@ -11579,7 +11582,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>12</v>
@@ -11593,10 +11596,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C10" s="3">
         <v>3701</v>
@@ -11605,7 +11608,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
@@ -11619,10 +11622,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C11" s="3">
         <v>3800</v>
@@ -11631,7 +11634,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>12</v>
@@ -11645,10 +11648,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C12" s="3">
         <v>3725</v>
@@ -11657,7 +11660,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>12</v>
@@ -11671,10 +11674,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C13" s="3">
         <v>3871</v>
@@ -11683,7 +11686,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>12</v>
@@ -11697,10 +11700,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C14" s="3">
         <v>2825</v>
@@ -11723,10 +11726,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C15" s="3">
         <v>2828</v>
@@ -11749,10 +11752,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C16" s="3">
         <v>2826</v>
@@ -11775,10 +11778,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C17" s="3">
         <v>3058</v>
@@ -11801,10 +11804,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C18" s="3">
         <v>3059</v>
@@ -11827,10 +11830,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C19" s="3">
         <v>2829</v>
@@ -11853,10 +11856,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C20" s="3">
         <v>4126</v>
@@ -11879,10 +11882,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C21" s="3">
         <v>2827</v>
@@ -11905,10 +11908,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C22" s="3">
         <v>3801</v>
@@ -11917,7 +11920,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>12</v>
@@ -11931,10 +11934,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C23" s="3">
         <v>3833</v>
@@ -11943,7 +11946,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>12</v>
@@ -11957,10 +11960,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C24" s="3">
         <v>3897</v>
@@ -11983,10 +11986,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C25" s="3">
         <v>3764</v>
@@ -12107,10 +12110,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C4" s="3">
         <v>3443</v>
@@ -12133,10 +12136,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C5" s="3">
         <v>3019</v>
@@ -12159,10 +12162,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C6" s="3">
         <v>4489</v>
@@ -12185,10 +12188,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C7" s="3">
         <v>4490</v>
@@ -12211,10 +12214,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C8" s="3">
         <v>3476</v>
@@ -12237,10 +12240,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C9" s="3">
         <v>3477</v>
@@ -12263,10 +12266,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C10" s="3">
         <v>4344</v>
@@ -12341,10 +12344,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C13" s="3">
         <v>3719</v>
@@ -12367,10 +12370,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C14" s="3">
         <v>3720</v>
@@ -12393,10 +12396,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C15" s="3">
         <v>3765</v>
@@ -12419,10 +12422,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C16" s="3">
         <v>3766</v>
@@ -12445,10 +12448,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C17" s="3">
         <v>3126</v>
@@ -12471,10 +12474,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C18" s="3">
         <v>3127</v>
@@ -12497,10 +12500,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C19" s="3">
         <v>3435</v>
@@ -12523,10 +12526,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C20" s="3">
         <v>3436</v>
@@ -12549,10 +12552,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C21" s="3">
         <v>3128</v>
@@ -12575,10 +12578,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C22" s="3">
         <v>3129</v>
@@ -12601,10 +12604,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C23" s="3">
         <v>4158</v>
@@ -12627,10 +12630,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C24" s="3">
         <v>4159</v>
@@ -12653,10 +12656,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C25" s="3">
         <v>4561</v>
@@ -12679,10 +12682,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C26" s="3">
         <v>4562</v>
@@ -12809,10 +12812,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C31" s="3">
         <v>4346</v>
@@ -12835,10 +12838,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C32" s="3">
         <v>4345</v>
@@ -12861,10 +12864,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C33" s="3">
         <v>4347</v>
@@ -12887,10 +12890,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C34" s="3">
         <v>4446</v>
@@ -12913,10 +12916,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C35" s="3">
         <v>4476</v>
@@ -12928,7 +12931,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G35" s="3">
         <v>33.5</v>
@@ -12939,10 +12942,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C36" s="3">
         <v>4348</v>
@@ -12965,10 +12968,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C37" s="3">
         <v>4456</v>
@@ -12991,10 +12994,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C38" s="3">
         <v>4051</v>
@@ -13017,10 +13020,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C39" s="3">
         <v>2833</v>
@@ -13043,10 +13046,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C40" s="3">
         <v>3125</v>
@@ -13069,10 +13072,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C41" s="3">
         <v>3752</v>
@@ -13095,10 +13098,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C42" s="3">
         <v>3753</v>
@@ -13121,10 +13124,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C43" s="3">
         <v>2511</v>
@@ -13147,10 +13150,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C44" s="3">
         <v>4311</v>
@@ -13173,10 +13176,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C45" s="3">
         <v>4046</v>
@@ -13199,10 +13202,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C46" s="3">
         <v>4047</v>
@@ -13225,10 +13228,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C47" s="3">
         <v>4312</v>
@@ -13251,10 +13254,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C48" s="3">
         <v>4310</v>
@@ -13277,10 +13280,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C49" s="3">
         <v>4074</v>
@@ -13289,7 +13292,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>12</v>
@@ -13303,10 +13306,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C50" s="3">
         <v>4076</v>
@@ -13315,10 +13318,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G50" s="3">
         <v>32.5</v>
@@ -13329,10 +13332,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C51" s="3">
         <v>4133</v>
@@ -13344,7 +13347,7 @@
         <v>585</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G51" s="3">
         <v>72</v>
@@ -13355,10 +13358,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C52" s="3">
         <v>3068</v>
@@ -13381,10 +13384,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C53" s="3">
         <v>3087</v>
@@ -13407,10 +13410,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C54" s="3">
         <v>4560</v>
@@ -13433,10 +13436,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C55" s="3">
         <v>4531</v>
@@ -13459,10 +13462,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C56" s="3">
         <v>4532</v>
@@ -13485,10 +13488,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C57" s="3">
         <v>4559</v>
@@ -13511,10 +13514,10 @@
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C58" s="3">
         <v>4493</v>
@@ -13537,10 +13540,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C59" s="3">
         <v>4102</v>
@@ -13549,7 +13552,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>12</v>
@@ -13563,10 +13566,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C60" s="3">
         <v>4103</v>
@@ -13575,7 +13578,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>273</v>
@@ -13589,10 +13592,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C61" s="3">
         <v>4624</v>
@@ -13601,7 +13604,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>12</v>
@@ -13615,10 +13618,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C62" s="3">
         <v>4627</v>
@@ -13627,7 +13630,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>12</v>
@@ -13641,10 +13644,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C63" s="3">
         <v>4628</v>
@@ -13653,7 +13656,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>12</v>
@@ -13667,10 +13670,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C64" s="3">
         <v>4625</v>
@@ -13679,7 +13682,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>12</v>
@@ -13693,10 +13696,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C65" s="3">
         <v>4626</v>
@@ -13705,7 +13708,7 @@
         <v>21</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>12</v>
@@ -13719,10 +13722,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C66" s="3">
         <v>4699</v>
@@ -13731,7 +13734,7 @@
         <v>50</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>273</v>
@@ -13745,10 +13748,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C67" s="3">
         <v>4643</v>
@@ -13757,7 +13760,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>29</v>
@@ -13771,10 +13774,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C68" s="3">
         <v>4687</v>
@@ -13783,7 +13786,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>29</v>
@@ -13797,10 +13800,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C69" s="3">
         <v>4644</v>
@@ -13809,7 +13812,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>29</v>
@@ -13823,10 +13826,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C70" s="3">
         <v>4547</v>
@@ -13835,7 +13838,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>273</v>
@@ -13849,10 +13852,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C71" s="3">
         <v>4104</v>
@@ -13861,7 +13864,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>273</v>
@@ -13875,10 +13878,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C72" s="3">
         <v>4101</v>
@@ -13887,7 +13890,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>273</v>
@@ -13901,10 +13904,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C73" s="3">
         <v>4641</v>
@@ -13913,7 +13916,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>12</v>
@@ -13927,10 +13930,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C74" s="3">
         <v>4583</v>
@@ -13939,7 +13942,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>29</v>
@@ -13953,10 +13956,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C75" s="3">
         <v>4105</v>
@@ -13965,7 +13968,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>273</v>
@@ -13979,10 +13982,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C76" s="3">
         <v>3705</v>
@@ -13991,7 +13994,7 @@
         <v>12</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>273</v>
@@ -14005,10 +14008,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C77" s="3">
         <v>3823</v>
@@ -14017,7 +14020,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>29</v>
@@ -14031,10 +14034,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C78" s="3">
         <v>4308</v>
@@ -14043,7 +14046,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>12</v>
@@ -14057,10 +14060,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C79" s="3">
         <v>4309</v>
@@ -14069,10 +14072,10 @@
         <v>10</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G79" s="3">
         <v>68.5</v>
@@ -14083,10 +14086,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C80" s="3">
         <v>4635</v>
@@ -14095,10 +14098,10 @@
         <v>10</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G80" s="3">
         <v>177</v>
@@ -14109,10 +14112,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C81" s="3">
         <v>4412</v>
@@ -14124,7 +14127,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G81" s="3">
         <v>75.5</v>
@@ -14135,10 +14138,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C82" s="3">
         <v>4413</v>
@@ -14161,10 +14164,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C83" s="3">
         <v>4414</v>
@@ -14187,10 +14190,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C84" s="3">
         <v>4415</v>
@@ -14213,10 +14216,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C85" s="3">
         <v>4416</v>
@@ -14239,10 +14242,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C86" s="3">
         <v>4475</v>
@@ -14251,7 +14254,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>12</v>
@@ -14265,10 +14268,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C87" s="3">
         <v>4354</v>
@@ -14277,10 +14280,10 @@
         <v>12</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G87" s="3">
         <v>79.5</v>
@@ -14291,10 +14294,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C88" s="3">
         <v>4445</v>
@@ -14303,7 +14306,7 @@
         <v>12</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>29</v>
@@ -14317,10 +14320,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C89" s="3">
         <v>4353</v>
@@ -14329,7 +14332,7 @@
         <v>12</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>29</v>
@@ -14343,10 +14346,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C90" s="3">
         <v>4350</v>
@@ -14355,7 +14358,7 @@
         <v>12</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>29</v>
@@ -14369,10 +14372,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C91" s="3">
         <v>4352</v>
@@ -14381,7 +14384,7 @@
         <v>12</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -14395,10 +14398,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C92" s="3">
         <v>4349</v>
@@ -14407,7 +14410,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>29</v>
@@ -14421,10 +14424,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C93" s="3">
         <v>4351</v>
@@ -14433,7 +14436,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>29</v>
@@ -14447,10 +14450,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C94" s="3">
         <v>4581</v>
@@ -14459,7 +14462,7 @@
         <v>12</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>29</v>
@@ -14473,10 +14476,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C95" s="3">
         <v>4096</v>
@@ -14499,10 +14502,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C96" s="3">
         <v>4582</v>
@@ -14511,7 +14514,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>12</v>
@@ -14525,10 +14528,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C97" s="3">
         <v>4123</v>
@@ -14537,7 +14540,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>12</v>
@@ -14551,10 +14554,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C98" s="3">
         <v>4306</v>
@@ -14563,10 +14566,10 @@
         <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G98" s="3">
         <v>81</v>
@@ -14577,10 +14580,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C99" s="3">
         <v>4307</v>
@@ -14589,10 +14592,10 @@
         <v>10</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G99" s="3">
         <v>81</v>
@@ -14603,10 +14606,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C100" s="3">
         <v>2659</v>
@@ -14615,7 +14618,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>273</v>
@@ -14629,10 +14632,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C101" s="3">
         <v>2621</v>
@@ -14641,7 +14644,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>273</v>
@@ -14655,10 +14658,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C102" s="3">
         <v>3656</v>
@@ -14667,7 +14670,7 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>273</v>
@@ -14729,10 +14732,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C2" s="3">
         <v>4408</v>
@@ -14755,10 +14758,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="3">
         <v>4341</v>
@@ -14781,10 +14784,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C4" s="3">
         <v>4265</v>
@@ -14807,10 +14810,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C5" s="3">
         <v>4266</v>
@@ -14833,10 +14836,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C6" s="3">
         <v>4269</v>
@@ -14859,10 +14862,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="3">
         <v>4273</v>
@@ -14885,10 +14888,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C8" s="3">
         <v>4406</v>
@@ -14911,10 +14914,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C9" s="3">
         <v>4267</v>
@@ -14937,10 +14940,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C10" s="3">
         <v>4271</v>
@@ -14963,10 +14966,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C11" s="3">
         <v>4276</v>
@@ -14989,10 +14992,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C12" s="3">
         <v>2205</v>
@@ -15015,10 +15018,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C13" s="3">
         <v>4342</v>
@@ -15041,10 +15044,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C14" s="3">
         <v>4270</v>
@@ -15067,10 +15070,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C15" s="3">
         <v>4275</v>
@@ -15093,10 +15096,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C16" s="3">
         <v>4404</v>
@@ -15119,10 +15122,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C17" s="3">
         <v>4264</v>
@@ -15145,10 +15148,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C18" s="3">
         <v>4407</v>
@@ -15171,10 +15174,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C19" s="3">
         <v>4397</v>
@@ -15197,10 +15200,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C20" s="3">
         <v>4343</v>
@@ -15223,10 +15226,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C21" s="3">
         <v>4268</v>
@@ -15308,10 +15311,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C2" s="3">
         <v>3459</v>
@@ -15320,7 +15323,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -15334,10 +15337,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C3" s="3">
         <v>3803</v>
@@ -15346,7 +15349,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -15360,10 +15363,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C4" s="3">
         <v>3425</v>
@@ -15372,10 +15375,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G4" s="3">
         <v>29</v>
@@ -15386,10 +15389,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C5" s="3">
         <v>3426</v>
@@ -15398,7 +15401,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>29</v>
@@ -15412,10 +15415,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C6" s="3">
         <v>3427</v>
@@ -15424,10 +15427,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G6" s="3">
         <v>62.5</v>
@@ -15438,10 +15441,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C7" s="3">
         <v>3428</v>
@@ -15450,7 +15453,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>29</v>
@@ -15464,10 +15467,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C8" s="3">
         <v>3429</v>
@@ -15476,10 +15479,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G8" s="3">
         <v>76.5</v>
@@ -15490,10 +15493,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C9" s="3">
         <v>3430</v>
@@ -15502,7 +15505,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>29</v>
@@ -15516,10 +15519,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C10" s="3">
         <v>3913</v>
@@ -15528,10 +15531,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G10" s="3">
         <v>68</v>
@@ -15542,10 +15545,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C11" s="3">
         <v>3872</v>
@@ -15554,7 +15557,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>29</v>
@@ -15568,10 +15571,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C12" s="3">
         <v>3422</v>
@@ -15580,10 +15583,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G12" s="3">
         <v>20</v>
@@ -15594,10 +15597,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C13" s="3">
         <v>3423</v>
@@ -15606,7 +15609,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>29</v>
@@ -15620,10 +15623,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C14" s="3">
         <v>3431</v>
@@ -15632,10 +15635,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G14" s="3">
         <v>115</v>
@@ -15646,10 +15649,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C15" s="3">
         <v>3432</v>
@@ -15658,7 +15661,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>29</v>
@@ -25040,7 +25043,7 @@
         <v>11</v>
       </c>
       <c r="G88" s="3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H88" s="3">
         <f>MROUND(G88*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="1138">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2691,6 +2691,18 @@
   </si>
   <si>
     <t>BATATA FRITA SALSA MEXICANA</t>
+  </si>
+  <si>
+    <t>biscoito-polvilho</t>
+  </si>
+  <si>
+    <t>BISCOITO DE POLVILHO C/QUEIJO</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>X180G</t>
   </si>
   <si>
     <t>mix-batata-doce-chips</t>
@@ -11348,7 +11360,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11672,7 +11684,7 @@
         <f>MROUND(G12*1.03, 0.5)</f>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>887</v>
       </c>
@@ -11680,45 +11692,45 @@
         <v>888</v>
       </c>
       <c r="C13" s="3">
-        <v>3871</v>
-      </c>
-      <c r="D13" s="3">
-        <v>500</v>
+        <v>4244</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>889</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="H13" s="3">
-        <f>MROUND(G13*1.03, 0.5)</f>
+        <f>MROUND(G12*1.03, 0.5)</f>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C14" s="3">
-        <v>2825</v>
+        <v>3871</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>10</v>
+        <v>866</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H14" s="3">
         <f>MROUND(G14*1.03, 0.5)</f>
@@ -11726,13 +11738,13 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C15" s="3">
-        <v>2828</v>
+        <v>2825</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -11752,13 +11764,13 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C16" s="3">
-        <v>2826</v>
+        <v>2828</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -11778,13 +11790,13 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C17" s="3">
-        <v>3058</v>
+        <v>2826</v>
       </c>
       <c r="D17" s="3">
         <v>2</v>
@@ -11804,13 +11816,13 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C18" s="3">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D18" s="3">
         <v>2</v>
@@ -11830,13 +11842,13 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C19" s="3">
-        <v>2829</v>
+        <v>3059</v>
       </c>
       <c r="D19" s="3">
         <v>2</v>
@@ -11856,13 +11868,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C20" s="3">
-        <v>4126</v>
+        <v>2829</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -11882,13 +11894,13 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C21" s="3">
-        <v>2827</v>
+        <v>4126</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
@@ -11908,19 +11920,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C22" s="3">
-        <v>3801</v>
+        <v>2827</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>866</v>
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>12</v>
@@ -11934,13 +11946,13 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C23" s="3">
-        <v>3833</v>
+        <v>3801</v>
       </c>
       <c r="D23" s="3">
         <v>500</v>
@@ -11960,25 +11972,25 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C24" s="3">
-        <v>3897</v>
+        <v>3833</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>10</v>
+        <v>866</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H24" s="3">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -11986,13 +11998,13 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C25" s="3">
-        <v>3764</v>
+        <v>3897</v>
       </c>
       <c r="D25" s="3">
         <v>2</v>
@@ -12001,13 +12013,39 @@
         <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G25" s="3">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="H25" s="3">
         <f>MROUND(G25*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C26" s="3">
+        <v>3764</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3">
+        <v>81</v>
+      </c>
+      <c r="H26" s="3">
+        <f>MROUND(G26*1.03, 0.5)</f>
       </c>
     </row>
   </sheetData>
@@ -12110,10 +12148,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C4" s="3">
         <v>3443</v>
@@ -12136,10 +12174,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C5" s="3">
         <v>3019</v>
@@ -12162,10 +12200,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C6" s="3">
         <v>4489</v>
@@ -12188,10 +12226,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C7" s="3">
         <v>4490</v>
@@ -12214,10 +12252,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C8" s="3">
         <v>3476</v>
@@ -12240,10 +12278,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C9" s="3">
         <v>3477</v>
@@ -12266,10 +12304,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C10" s="3">
         <v>4344</v>
@@ -12344,10 +12382,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C13" s="3">
         <v>3719</v>
@@ -12370,10 +12408,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C14" s="3">
         <v>3720</v>
@@ -12396,10 +12434,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C15" s="3">
         <v>3765</v>
@@ -12422,10 +12460,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C16" s="3">
         <v>3766</v>
@@ -12448,10 +12486,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C17" s="3">
         <v>3126</v>
@@ -12474,10 +12512,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C18" s="3">
         <v>3127</v>
@@ -12500,10 +12538,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C19" s="3">
         <v>3435</v>
@@ -12526,10 +12564,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C20" s="3">
         <v>3436</v>
@@ -12552,10 +12590,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C21" s="3">
         <v>3128</v>
@@ -12578,10 +12616,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C22" s="3">
         <v>3129</v>
@@ -12604,10 +12642,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C23" s="3">
         <v>4158</v>
@@ -12630,10 +12668,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C24" s="3">
         <v>4159</v>
@@ -12656,10 +12694,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C25" s="3">
         <v>4561</v>
@@ -12682,10 +12720,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C26" s="3">
         <v>4562</v>
@@ -12812,10 +12850,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="C31" s="3">
         <v>4346</v>
@@ -12838,10 +12876,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C32" s="3">
         <v>4345</v>
@@ -12864,10 +12902,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C33" s="3">
         <v>4347</v>
@@ -12890,10 +12928,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C34" s="3">
         <v>4446</v>
@@ -12916,10 +12954,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C35" s="3">
         <v>4476</v>
@@ -12942,10 +12980,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C36" s="3">
         <v>4348</v>
@@ -12968,10 +13006,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="C37" s="3">
         <v>4456</v>
@@ -12994,10 +13032,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C38" s="3">
         <v>4051</v>
@@ -13020,10 +13058,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C39" s="3">
         <v>2833</v>
@@ -13046,10 +13084,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C40" s="3">
         <v>3125</v>
@@ -13072,10 +13110,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C41" s="3">
         <v>3752</v>
@@ -13098,10 +13136,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C42" s="3">
         <v>3753</v>
@@ -13124,10 +13162,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C43" s="3">
         <v>2511</v>
@@ -13150,10 +13188,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="C44" s="3">
         <v>4311</v>
@@ -13176,10 +13214,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C45" s="3">
         <v>4046</v>
@@ -13202,10 +13240,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C46" s="3">
         <v>4047</v>
@@ -13228,10 +13266,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C47" s="3">
         <v>4312</v>
@@ -13254,10 +13292,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C48" s="3">
         <v>4310</v>
@@ -13280,10 +13318,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C49" s="3">
         <v>4074</v>
@@ -13292,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>12</v>
@@ -13306,10 +13344,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C50" s="3">
         <v>4076</v>
@@ -13318,10 +13356,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G50" s="3">
         <v>32.5</v>
@@ -13332,10 +13370,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C51" s="3">
         <v>4133</v>
@@ -13347,7 +13385,7 @@
         <v>585</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G51" s="3">
         <v>72</v>
@@ -13358,10 +13396,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C52" s="3">
         <v>3068</v>
@@ -13384,10 +13422,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C53" s="3">
         <v>3087</v>
@@ -13410,10 +13448,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C54" s="3">
         <v>4560</v>
@@ -13436,10 +13474,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C55" s="3">
         <v>4531</v>
@@ -13462,10 +13500,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C56" s="3">
         <v>4532</v>
@@ -13488,10 +13526,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C57" s="3">
         <v>4559</v>
@@ -13514,10 +13552,10 @@
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C58" s="3">
         <v>4493</v>
@@ -13540,10 +13578,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C59" s="3">
         <v>4102</v>
@@ -13552,7 +13590,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>12</v>
@@ -13566,10 +13604,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C60" s="3">
         <v>4103</v>
@@ -13578,7 +13616,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>273</v>
@@ -13592,10 +13630,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C61" s="3">
         <v>4624</v>
@@ -13604,7 +13642,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>12</v>
@@ -13618,10 +13656,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C62" s="3">
         <v>4627</v>
@@ -13630,7 +13668,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>12</v>
@@ -13644,10 +13682,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C63" s="3">
         <v>4628</v>
@@ -13656,7 +13694,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>12</v>
@@ -13670,10 +13708,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C64" s="3">
         <v>4625</v>
@@ -13682,7 +13720,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>12</v>
@@ -13696,10 +13734,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="C65" s="3">
         <v>4626</v>
@@ -13708,7 +13746,7 @@
         <v>21</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>12</v>
@@ -13722,10 +13760,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C66" s="3">
         <v>4699</v>
@@ -13734,7 +13772,7 @@
         <v>50</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>273</v>
@@ -13748,10 +13786,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="C67" s="3">
         <v>4643</v>
@@ -13760,7 +13798,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>29</v>
@@ -13774,10 +13812,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C68" s="3">
         <v>4687</v>
@@ -13786,7 +13824,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>29</v>
@@ -13800,10 +13838,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C69" s="3">
         <v>4644</v>
@@ -13812,7 +13850,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>29</v>
@@ -13826,10 +13864,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C70" s="3">
         <v>4547</v>
@@ -13838,7 +13876,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>273</v>
@@ -13852,10 +13890,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C71" s="3">
         <v>4104</v>
@@ -13864,7 +13902,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>273</v>
@@ -13878,10 +13916,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C72" s="3">
         <v>4101</v>
@@ -13890,7 +13928,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>273</v>
@@ -13904,10 +13942,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C73" s="3">
         <v>4641</v>
@@ -13916,7 +13954,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>12</v>
@@ -13930,10 +13968,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C74" s="3">
         <v>4583</v>
@@ -13942,7 +13980,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>29</v>
@@ -13956,10 +13994,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C75" s="3">
         <v>4105</v>
@@ -13968,7 +14006,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>273</v>
@@ -13982,10 +14020,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="C76" s="3">
         <v>3705</v>
@@ -13994,7 +14032,7 @@
         <v>12</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>273</v>
@@ -14008,10 +14046,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C77" s="3">
         <v>3823</v>
@@ -14020,7 +14058,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>29</v>
@@ -14034,10 +14072,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C78" s="3">
         <v>4308</v>
@@ -14046,7 +14084,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>12</v>
@@ -14060,10 +14098,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="C79" s="3">
         <v>4309</v>
@@ -14072,10 +14110,10 @@
         <v>10</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G79" s="3">
         <v>68.5</v>
@@ -14086,10 +14124,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C80" s="3">
         <v>4635</v>
@@ -14098,10 +14136,10 @@
         <v>10</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G80" s="3">
         <v>177</v>
@@ -14112,10 +14150,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C81" s="3">
         <v>4412</v>
@@ -14127,7 +14165,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G81" s="3">
         <v>75.5</v>
@@ -14138,10 +14176,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C82" s="3">
         <v>4413</v>
@@ -14164,10 +14202,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C83" s="3">
         <v>4414</v>
@@ -14190,10 +14228,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C84" s="3">
         <v>4415</v>
@@ -14216,10 +14254,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C85" s="3">
         <v>4416</v>
@@ -14242,10 +14280,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C86" s="3">
         <v>4475</v>
@@ -14254,7 +14292,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>12</v>
@@ -14268,10 +14306,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="C87" s="3">
         <v>4354</v>
@@ -14280,7 +14318,7 @@
         <v>12</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>784</v>
@@ -14294,10 +14332,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C88" s="3">
         <v>4445</v>
@@ -14306,7 +14344,7 @@
         <v>12</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>29</v>
@@ -14320,10 +14358,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C89" s="3">
         <v>4353</v>
@@ -14332,7 +14370,7 @@
         <v>12</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>29</v>
@@ -14346,10 +14384,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C90" s="3">
         <v>4350</v>
@@ -14358,7 +14396,7 @@
         <v>12</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>29</v>
@@ -14372,10 +14410,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C91" s="3">
         <v>4352</v>
@@ -14384,7 +14422,7 @@
         <v>12</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>29</v>
@@ -14398,10 +14436,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C92" s="3">
         <v>4349</v>
@@ -14410,7 +14448,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>29</v>
@@ -14424,10 +14462,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C93" s="3">
         <v>4351</v>
@@ -14436,7 +14474,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>29</v>
@@ -14450,10 +14488,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C94" s="3">
         <v>4581</v>
@@ -14462,7 +14500,7 @@
         <v>12</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>29</v>
@@ -14476,10 +14514,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="C95" s="3">
         <v>4096</v>
@@ -14502,10 +14540,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C96" s="3">
         <v>4582</v>
@@ -14514,7 +14552,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>12</v>
@@ -14528,10 +14566,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C97" s="3">
         <v>4123</v>
@@ -14540,7 +14578,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>12</v>
@@ -14554,10 +14592,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="C98" s="3">
         <v>4306</v>
@@ -14566,10 +14604,10 @@
         <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G98" s="3">
         <v>81</v>
@@ -14580,10 +14618,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C99" s="3">
         <v>4307</v>
@@ -14592,10 +14630,10 @@
         <v>10</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G99" s="3">
         <v>81</v>
@@ -14606,10 +14644,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C100" s="3">
         <v>2659</v>
@@ -14618,7 +14656,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>273</v>
@@ -14632,10 +14670,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C101" s="3">
         <v>2621</v>
@@ -14644,7 +14682,7 @@
         <v>5</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>273</v>
@@ -14658,10 +14696,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C102" s="3">
         <v>3656</v>
@@ -14670,7 +14708,7 @@
         <v>5</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>273</v>
@@ -14732,10 +14770,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C2" s="3">
         <v>4408</v>
@@ -14758,10 +14796,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C3" s="3">
         <v>4341</v>
@@ -14784,10 +14822,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="C4" s="3">
         <v>4265</v>
@@ -14810,10 +14848,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C5" s="3">
         <v>4266</v>
@@ -14836,10 +14874,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="C6" s="3">
         <v>4269</v>
@@ -14862,10 +14900,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C7" s="3">
         <v>4273</v>
@@ -14888,10 +14926,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C8" s="3">
         <v>4406</v>
@@ -14914,10 +14952,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="C9" s="3">
         <v>4267</v>
@@ -14940,10 +14978,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="3">
         <v>4271</v>
@@ -14966,10 +15004,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="C11" s="3">
         <v>4276</v>
@@ -14992,10 +15030,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="C12" s="3">
         <v>2205</v>
@@ -15018,10 +15056,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C13" s="3">
         <v>4342</v>
@@ -15044,10 +15082,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C14" s="3">
         <v>4270</v>
@@ -15070,10 +15108,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="C15" s="3">
         <v>4275</v>
@@ -15096,10 +15134,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C16" s="3">
         <v>4404</v>
@@ -15122,10 +15160,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C17" s="3">
         <v>4264</v>
@@ -15148,10 +15186,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C18" s="3">
         <v>4407</v>
@@ -15174,10 +15212,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C19" s="3">
         <v>4397</v>
@@ -15200,10 +15238,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C20" s="3">
         <v>4343</v>
@@ -15226,10 +15264,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C21" s="3">
         <v>4268</v>
@@ -15311,10 +15349,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C2" s="3">
         <v>3459</v>
@@ -15337,10 +15375,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C3" s="3">
         <v>3803</v>
@@ -15363,10 +15401,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C4" s="3">
         <v>3425</v>
@@ -15389,10 +15427,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C5" s="3">
         <v>3426</v>
@@ -15415,10 +15453,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C6" s="3">
         <v>3427</v>
@@ -15441,10 +15479,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C7" s="3">
         <v>3428</v>
@@ -15467,10 +15505,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C8" s="3">
         <v>3429</v>
@@ -15493,10 +15531,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C9" s="3">
         <v>3430</v>
@@ -15519,10 +15557,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C10" s="3">
         <v>3913</v>
@@ -15545,10 +15583,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C11" s="3">
         <v>3872</v>
@@ -15571,10 +15609,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C12" s="3">
         <v>3422</v>
@@ -15597,10 +15635,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C13" s="3">
         <v>3423</v>
@@ -15609,7 +15647,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>29</v>
@@ -15623,10 +15661,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C14" s="3">
         <v>3431</v>
@@ -15649,10 +15687,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C15" s="3">
         <v>3432</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -6071,7 +6071,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="3">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="H5" s="3">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -9258,7 +9258,7 @@
         <v>273</v>
       </c>
       <c r="G65" s="3">
-        <v>472.5</v>
+        <v>405</v>
       </c>
       <c r="H65" s="3">
         <f>MROUND(G65*1.03, 0.5)</f>
@@ -9284,7 +9284,7 @@
         <v>29</v>
       </c>
       <c r="G66" s="3">
-        <v>159.5</v>
+        <v>138.5</v>
       </c>
       <c r="H66" s="3">
         <f>MROUND(G66*1.03, 0.5)</f>
@@ -9622,7 +9622,7 @@
         <v>11</v>
       </c>
       <c r="G79" s="3">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="H79" s="3">
         <f>MROUND(G79*1.03, 0.5)</f>
@@ -9648,7 +9648,7 @@
         <v>12</v>
       </c>
       <c r="G80" s="3">
-        <v>127</v>
+        <v>113.5</v>
       </c>
       <c r="H80" s="3">
         <f>MROUND(G80*1.03, 0.5)</f>
@@ -9726,7 +9726,7 @@
         <v>12</v>
       </c>
       <c r="G83" s="3">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="H83" s="3">
         <f>MROUND(G83*1.03, 0.5)</f>
@@ -9752,7 +9752,7 @@
         <v>12</v>
       </c>
       <c r="G84" s="3">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="H84" s="3">
         <f>MROUND(G84*1.03, 0.5)</f>
